--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.7%</t>
+          <t>-649.6%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.6%</t>
+          <t>-152.5%</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983739</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.884400512706835</v>
+        <v>3.884400512706836</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.881382342484493</v>
+        <v>-4.880233126318286</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.236533850161721</v>
+        <v>2.236993536628203</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4898904491153769</v>
+        <v>0.4902288030651559</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.483377480938492</v>
+        <v>4.483580493308359</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.6%</t>
+          <t>-650.3%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-152.8%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-330.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.161720411333774</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.314417281679189</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.041547327969275</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.36363235946529</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.906293966639298</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.427821806558721</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.966168793996991</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.38990936701707</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.846348563086153</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.453126628615613</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.848818269547959</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.359782945353333</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.917188455871969</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.25169673230903</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.930976508719016</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.236618219802103</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.986496584611605</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.351441026137269</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.811022324819136</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.426197962046045</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.798263389764238</v>
+        <v>-3.803097950234222</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.407043564829211</v>
+        <v>1.405109740641217</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.791985187194389</v>
+        <v>-3.796819747664373</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.3380931592586</v>
+        <v>1.336159335070607</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8176560300468725</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.732132567990666</v>
+        <v>-3.73696712846065</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.372206593372222</v>
+        <v>1.370272769184228</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8176560300468725</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.645889104964288</v>
+        <v>-3.650723665434272</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.401650249156633</v>
+        <v>1.39971642496864</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8176560300468725</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.691195924363268</v>
+        <v>-3.696030484833252</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.375303296841567</v>
+        <v>1.373369472653573</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7768458670376417</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.72022902906557</v>
+        <v>-3.725063589535554</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.364241927993748</v>
+        <v>1.362308103805754</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7768458670376417</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.62741854761471</v>
+        <v>-3.632253108084694</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.330638812465457</v>
+        <v>1.328704988277464</v>
       </c>
       <c r="F1946" t="n">
         <v>0.869656348488501</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.671808016944138</v>
+        <v>-3.676642577414122</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.314756500658287</v>
+        <v>1.312822676470293</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8252668791590734</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.788349622049481</v>
+        <v>-3.793184182519465</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.263215567127873</v>
+        <v>1.261281742939879</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7087252740537306</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.828273716632053</v>
+        <v>-3.833108277102037</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.252737225125511</v>
+        <v>1.250803400937518</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7087252740537306</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.856054114533406</v>
+        <v>-3.86088867500339</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.253122267733509</v>
+        <v>1.251188443545515</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6809448761523775</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.974434787263544</v>
+        <v>-3.979269347733528</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.044125718642107</v>
+        <v>1.042191894454113</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6137270240014013</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.083048865706875</v>
+        <v>-4.087883426176859</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.12082974798398</v>
+        <v>1.118895923795987</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6137270240014013</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.047639827458732</v>
+        <v>-4.052474387928716</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14950638938556</v>
+        <v>1.147572565197567</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6137270240014013</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.009256164900581</v>
+        <v>-4.014090725370565</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.16227929575119</v>
+        <v>1.160345471563196</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6521106865595525</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.832139834865415</v>
+        <v>-3.836974395335399</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.229854856610558</v>
+        <v>1.227921032422564</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6521106865595525</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.877232079698961</v>
+        <v>-3.882066640168945</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.212501350439053</v>
+        <v>1.210567526251059</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5902146433901627</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.697856658460193</v>
+        <v>-3.702691218930177</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.278038494240974</v>
+        <v>1.276104670052981</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7469914015608814</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.742870871980799</v>
+        <v>-3.747705432450783</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.240840264164321</v>
+        <v>1.238906439976328</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7166425062462768</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.009875382253234</v>
+        <v>-4.014709942723218</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.139730022394293</v>
+        <v>1.137796198206299</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5222794682033283</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.111073163690407</v>
+        <v>-4.115907724160391</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.098454831715925</v>
+        <v>1.096521007527932</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4538706546580091</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.104562197076095</v>
+        <v>-4.109396757546079</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098659179915967</v>
+        <v>1.096725355727973</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4538706546580091</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.085524069368797</v>
+        <v>-4.090358629838781</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102799150207131</v>
+        <v>1.100865326019137</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3956870433268145</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.138039871643618</v>
+        <v>-4.142874432113602</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201087230931393</v>
+        <v>1.1991534067434</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3956870433268145</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.151906632977536</v>
+        <v>-4.15674119344752</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.19637385538396</v>
+        <v>1.194440031195966</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3578291265929916</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.107102461437606</v>
+        <v>-4.11193702190759</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.220304054396858</v>
+        <v>1.218370230208864</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3578291265929916</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.959359491202604</v>
+        <v>-3.964194051672588</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.177351463768058</v>
+        <v>1.175417639580064</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5256364838278748</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.043180712477302</v>
+        <v>-4.048015272947286</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14661659678966</v>
+        <v>1.144682772601666</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5256364838278748</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.037028006424517</v>
+        <v>-4.041862566894501</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.149740027602432</v>
+        <v>1.147806203414438</v>
       </c>
       <c r="F1968" t="n">
         <v>0.531789189880659</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.053837304575019</v>
+        <v>-4.058671865045003</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.142096785082341</v>
+        <v>1.140162960894348</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5149798917301573</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.991539305798897</v>
+        <v>-3.996373866268881</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.233351538389611</v>
+        <v>1.231417714201617</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5602741560045994</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.789749108133739</v>
+        <v>-3.794583668603723</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.116359619169801</v>
+        <v>1.114425794981807</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7582923481737538</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.840635820819934</v>
+        <v>-3.845470381289918</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.166295166417498</v>
+        <v>1.164361342229505</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7074056354875593</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.754025078170127</v>
+        <v>-3.758859638640111</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.215567199593465</v>
+        <v>1.213633375405471</v>
       </c>
       <c r="F1973" t="n">
         <v>0.7860313666927176</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.814234376175411</v>
+        <v>-3.819068936645395</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.190019461216023</v>
+        <v>1.188085637028029</v>
       </c>
       <c r="F1974" t="n">
         <v>0.725822068687433</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.737812329743484</v>
+        <v>-3.742646890213468</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.219079897828722</v>
+        <v>1.217146073640728</v>
       </c>
       <c r="F1975" t="n">
         <v>0.725822068687433</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.693439198104916</v>
+        <v>-3.6982737585749</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.236692017919586</v>
+        <v>1.234758193731592</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7701952003260016</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.715919548963801</v>
+        <v>-3.720754109433785</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.222093671714622</v>
+        <v>1.220159847526629</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7701952003260016</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.668263818402745</v>
+        <v>-3.673098378872729</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.247537720966849</v>
+        <v>1.245603896778856</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8178509308870573</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.567745659903991</v>
+        <v>-3.572580220373974</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.292637357741076</v>
+        <v>1.290703533553082</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9183690893858119</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.551840330471638</v>
+        <v>-3.556674890941622</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.285754161989889</v>
+        <v>1.283820337801896</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8392564286765729</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.50700192886324</v>
+        <v>-3.511836489333224</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.307787225243877</v>
+        <v>1.305853401055883</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8437998616214424</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.526500385105248</v>
+        <v>-3.531334945575232</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.304148782378152</v>
+        <v>1.302214958190158</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7957152203415381</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.482297548019348</v>
+        <v>-3.487132108489332</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.327709519740349</v>
+        <v>1.325775695552355</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8399180574274385</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.489857213856395</v>
+        <v>-3.494691774326379</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.323095653874778</v>
+        <v>1.321161829686784</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8947214614372578</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.331565796317122</v>
+        <v>-3.336400356787106</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.437659986073526</v>
+        <v>1.435726161885533</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8947214614372578</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.123923792682646</v>
+        <v>-3.12875835315263</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51915749212157</v>
+        <v>1.517223667933576</v>
       </c>
       <c r="F1986" t="n">
         <v>1.102363465071734</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.072891699960118</v>
+        <v>-3.077726260430102</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.534518557448851</v>
+        <v>1.532584733260858</v>
       </c>
       <c r="F1987" t="n">
         <v>1.153395557794262</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.007667518832912</v>
+        <v>-3.012502079302896</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.577795633992438</v>
+        <v>1.575861809804445</v>
       </c>
       <c r="F1988" t="n">
         <v>1.218619738921468</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.970240498761779</v>
+        <v>-2.975075059231763</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.588727414320172</v>
+        <v>1.586793590132179</v>
       </c>
       <c r="F1989" t="n">
         <v>1.223871276950649</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.990352154796487</v>
+        <v>-2.995186715266471</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.581939544237529</v>
+        <v>1.580005720049536</v>
       </c>
       <c r="F1990" t="n">
         <v>1.234898621948069</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961938891696603</v>
+        <v>-2.966773452166587</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.753862620498693</v>
+        <v>1.7519287963107</v>
       </c>
       <c r="F1991" t="n">
         <v>1.17592305920164</v>
@@ -47367,10 +47367,10 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.887156630671591</v>
+        <v>-2.891991191141575</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.903888434126516</v>
+        <v>1.901954609938522</v>
       </c>
       <c r="F1992" t="n">
         <v>1.250705320226652</v>
@@ -47390,10 +47390,10 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.861072546407783</v>
+        <v>-2.865907106877767</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.906030043845898</v>
+        <v>1.904096219657904</v>
       </c>
       <c r="F1993" t="n">
         <v>1.250705320226652</v>
@@ -47413,10 +47413,10 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.773194633298662</v>
+        <v>-2.778029193768646</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.939374404673326</v>
+        <v>1.937440580485332</v>
       </c>
       <c r="F1994" t="n">
         <v>1.366630962650004</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.764302171905379</v>
+        <v>-2.769136732375363</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.96048579495743</v>
+        <v>1.958551970769437</v>
       </c>
       <c r="F1995" t="n">
         <v>1.366630962650004</v>
@@ -47459,10 +47459,10 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.932778288875256</v>
+        <v>-2.93761284934524</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884950395574063</v>
+        <v>1.88301657138607</v>
       </c>
       <c r="F1996" t="n">
         <v>1.338683126933423</v>
@@ -47482,10 +47482,10 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.486522096245817</v>
+        <v>-2.491356656715801</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.044722569813701</v>
+        <v>2.042788745625707</v>
       </c>
       <c r="F1997" t="n">
         <v>1.24396445726379</v>
@@ -47505,10 +47505,10 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.463800992562664</v>
+        <v>-2.468635553032648</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.044475033783867</v>
+        <v>2.042541209595873</v>
       </c>
       <c r="F1998" t="n">
         <v>1.24396445726379</v>
@@ -47528,10 +47528,10 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.593002805856707</v>
+        <v>-2.59783736632669</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.151700434317418</v>
+        <v>2.149766610129425</v>
       </c>
       <c r="F1999" t="n">
         <v>1.114762643969748</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.618877204330732</v>
+        <v>-2.623711764800716</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.178428497421455</v>
+        <v>2.176494673233461</v>
       </c>
       <c r="F2000" t="n">
         <v>1.159674252681489</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.611822514115559</v>
+        <v>-2.616657074585543</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177925729497069</v>
+        <v>2.175991905309075</v>
       </c>
       <c r="F2001" t="n">
         <v>1.166728942896663</v>
@@ -47597,10 +47597,10 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.584871289789071</v>
+        <v>-2.589705850259055</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.198712372872406</v>
+        <v>2.196778548684413</v>
       </c>
       <c r="F2002" t="n">
         <v>1.181609288924382</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.720824297845387</v>
+        <v>-2.725658858315371</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.328434301794839</v>
+        <v>2.326500477606846</v>
       </c>
       <c r="F2003" t="n">
         <v>1.181609288924382</v>
@@ -47643,10 +47643,10 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.743232415650259</v>
+        <v>-2.748066976120243</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.311587749575883</v>
+        <v>2.30965392538789</v>
       </c>
       <c r="F2004" t="n">
         <v>1.181609288924382</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.771456651227859</v>
+        <v>-2.776291211697843</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.302352054894481</v>
+        <v>2.300418230706487</v>
       </c>
       <c r="F2005" t="n">
         <v>1.19958604137569</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.780897577116389</v>
+        <v>-2.785732137586373</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.354829402260916</v>
+        <v>2.352895578072923</v>
       </c>
       <c r="F2006" t="n">
         <v>1.322013158919082</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.838005744922015</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.334877229683967</v>
       </c>
       <c r="F2007" t="n">
         <v>1.269739551583441</v>
@@ -47735,10 +47735,10 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-2.914335722522921</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.30245705153738</v>
       </c>
       <c r="F2008" t="n">
         <v>1.269739551583441</v>
@@ -47758,10 +47758,10 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.116589442847274</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.216375793010501</v>
       </c>
       <c r="F2009" t="n">
         <v>1.067485831259087</v>
@@ -47781,10 +47781,10 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.278157868374529</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.150182433009751</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9407029074612078</v>
@@ -47804,10 +47804,10 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.410459160472082</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.110335323036648</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9407029074612078</v>
@@ -47827,10 +47827,10 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.596327471311312</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>2.027993195483896</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7821373141412601</v>
@@ -47850,10 +47850,10 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.624228258420785</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>2.015356921767109</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7475403899983253</v>
@@ -47873,10 +47873,10 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.746754361123679</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.96311092466315</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6250142872954314</v>
@@ -47896,10 +47896,10 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-3.977268857309268</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.937611085779419</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3944997911098427</v>
@@ -47919,10 +47919,10 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.233989675304091</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>1.975234477583336</v>
       </c>
       <c r="F2016" t="n">
         <v>0.2860852169660278</v>
@@ -47942,10 +47942,10 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.387976093080232</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>1.98262017961852</v>
       </c>
       <c r="F2017" t="n">
         <v>0.2860852169660278</v>
@@ -47965,10 +47965,10 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.337454189252566</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>1.988880143269707</v>
       </c>
       <c r="F2018" t="n">
         <v>0.2860852169660278</v>
@@ -47988,10 +47988,10 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.58992934326029</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.899760570722031</v>
       </c>
       <c r="F2019" t="n">
         <v>0.2860852169660278</v>
@@ -48011,10 +48011,10 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.882825099739702</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.78381280264921</v>
       </c>
       <c r="F2020" t="n">
         <v>0.2860852169660278</v>
@@ -48034,10 +48034,10 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-5.06948922787451</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.713268893622608</v>
       </c>
       <c r="F2021" t="n">
         <v>0.259346246141468</v>
@@ -48057,10 +48057,10 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.215509914788472</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.649938471593213</v>
       </c>
       <c r="F2022" t="n">
         <v>0.250263154347611</v>
@@ -48080,10 +48080,10 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.307223923898057</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.775456924648423</v>
       </c>
       <c r="F2023" t="n">
         <v>0.250263154347611</v>
@@ -48103,10 +48103,10 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.387107305649026</v>
+        <v>-5.39194186611901</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.73835020991185</v>
+        <v>1.736416385723856</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1651471254195646</v>
@@ -48126,10 +48126,10 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.46904212391791</v>
+        <v>-5.473876684387894</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.715805700172787</v>
+        <v>1.713871875984794</v>
       </c>
       <c r="F2025" t="n">
         <v>0.1552123798324844</v>
@@ -48149,10 +48149,10 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.571018246166317</v>
+        <v>-5.575852806636301</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.683940889729327</v>
+        <v>1.682007065541333</v>
       </c>
       <c r="F2026" t="n">
         <v>0.05323625758407685</v>
@@ -48172,10 +48172,10 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.461011962689096</v>
+        <v>-5.46584652315908</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.720096290364391</v>
+        <v>1.718162466176397</v>
       </c>
       <c r="F2027" t="n">
         <v>0.07644082950135206</v>
@@ -48195,10 +48195,10 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.31795238694817</v>
+        <v>-5.322786947418154</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.781570131382736</v>
+        <v>1.779636307194742</v>
       </c>
       <c r="F2028" t="n">
         <v>0.08445425609133134</v>
@@ -48218,10 +48218,10 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.016505661476332</v>
+        <v>-5.021340221946316</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.909409704454007</v>
+        <v>1.907475880266013</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3859009815631686</v>
@@ -48241,10 +48241,10 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.041095905711516</v>
+        <v>-5.0459304661815</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.900544784512644</v>
+        <v>1.89861096032465</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3859009815631686</v>
@@ -48264,10 +48264,10 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.990057529704996</v>
+        <v>-4.99489209017498</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.921803039295007</v>
+        <v>1.919869215107013</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3859009815631686</v>
@@ -48287,10 +48287,10 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.948918234838365</v>
+        <v>-4.953752795308349</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.957296856115804</v>
+        <v>1.955363031927811</v>
       </c>
       <c r="F2032" t="n">
         <v>0.4270402764297994</v>
@@ -48310,10 +48310,10 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.852283322819725</v>
+        <v>-4.857117883289709</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.812134817047195</v>
+        <v>1.810200992859202</v>
       </c>
       <c r="F2033" t="n">
         <v>0.5236751884484394</v>
@@ -48333,10 +48333,10 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.982864057350567</v>
+        <v>-4.987698617820551</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.763404567308822</v>
+        <v>1.761470743120828</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3930944539175969</v>
@@ -48356,10 +48356,10 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.818367723159605</v>
+        <v>-4.823202283629589</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.813629920061289</v>
+        <v>1.811696095873295</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3930944539175969</v>
@@ -48379,10 +48379,10 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.845737655844037</v>
+        <v>-4.850572216314021</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.801869657423946</v>
+        <v>1.799935833235953</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3930944539175969</v>
@@ -48402,10 +48402,10 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.856122850733927</v>
+        <v>-4.860957411203911</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.807584358593063</v>
+        <v>1.805650534405069</v>
       </c>
       <c r="F2037" t="n">
         <v>0.3827092590277076</v>
@@ -48425,10 +48425,10 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.874711009456152</v>
+        <v>-4.879545569926136</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.870986100880598</v>
+        <v>1.869052276692604</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3641211003054822</v>
@@ -48448,10 +48448,10 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.875009556152188</v>
+        <v>-4.879844116622172</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.867735693020482</v>
+        <v>1.865801868832488</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3641211003054822</v>
@@ -48471,10 +48471,10 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.77418642246176</v>
+        <v>-4.779020982931744</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.912595841436044</v>
+        <v>1.910662017248051</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3765853157898361</v>
@@ -48494,10 +48494,10 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.583405061709353</v>
+        <v>-4.588239622179337</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.98903763921555</v>
+        <v>1.987103815027557</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5673666765422434</v>
@@ -48517,10 +48517,10 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.564888207667533</v>
+        <v>-4.569722768137517</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.976281226569875</v>
+        <v>1.974347402381881</v>
       </c>
       <c r="F2042" t="n">
         <v>0.5802968059674516</v>
@@ -48540,10 +48540,10 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.539695023166215</v>
+        <v>-4.544529583636199</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.021325436982461</v>
+        <v>2.019391612794467</v>
       </c>
       <c r="F2043" t="n">
         <v>0.6054899904687699</v>
@@ -48563,10 +48563,10 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.527640896253252</v>
+        <v>-4.532475456723236</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.019833655649084</v>
+        <v>2.01789983146109</v>
       </c>
       <c r="F2044" t="n">
         <v>0.6175441173817328</v>
@@ -48586,10 +48586,10 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.53426414294361</v>
+        <v>-4.539098703413594</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.019064987157076</v>
+        <v>2.017131162969083</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6109208706913745</v>
@@ -48609,10 +48609,10 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.431383553415017</v>
+        <v>-4.436218113885001</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.073068248846396</v>
+        <v>2.071134424658402</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7138014602199674</v>
@@ -48632,10 +48632,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.454825592595104</v>
+        <v>-4.459660153065088</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.083894103347955</v>
+        <v>2.081960279159962</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7138014602199674</v>
@@ -48655,10 +48655,10 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.472898100886716</v>
+        <v>-4.4777326613567</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.076665100031311</v>
+        <v>2.074731275843317</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7138014602199674</v>
@@ -48678,10 +48678,10 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.704071894763348</v>
+        <v>-4.708906455233332</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.944447496074125</v>
+        <v>1.942513671886131</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7138014602199674</v>
@@ -48701,10 +48701,10 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.672785874222892</v>
+        <v>-4.677620434692876</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.963984523287247</v>
+        <v>1.962050699099253</v>
       </c>
       <c r="F2050" t="n">
         <v>0.7450874807604227</v>
@@ -48724,10 +48724,10 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.519760482109608</v>
+        <v>-4.524595042579592</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.124365679705464</v>
+        <v>2.122431855517471</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8981128728737069</v>
@@ -48747,10 +48747,10 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.548067795982878</v>
+        <v>-4.552902356452862</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.300508979064449</v>
+        <v>2.298575154876455</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8981128728737069</v>
@@ -48770,10 +48770,10 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.714661021096401</v>
+        <v>-4.719495581566385</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.203274640373122</v>
+        <v>2.201340816185128</v>
       </c>
       <c r="F2053" t="n">
         <v>0.7315196477601844</v>
@@ -48793,10 +48793,10 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.541596641714101</v>
+        <v>-4.546431202184085</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.27617679478776</v>
+        <v>2.274242970599766</v>
       </c>
       <c r="F2054" t="n">
         <v>0.7315196477601844</v>
@@ -48816,10 +48816,10 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.512350661258404</v>
+        <v>-4.517185221728388</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.285493242093534</v>
+        <v>2.28355941790554</v>
       </c>
       <c r="F2055" t="n">
         <v>0.7315196477601844</v>
@@ -48839,10 +48839,10 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.619276209136255</v>
+        <v>-4.624110769606239</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.240016262100029</v>
+        <v>2.238082437912035</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6245940998823331</v>
@@ -48862,10 +48862,10 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.764294767643504</v>
+        <v>-4.769129328113488</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.183437640840364</v>
+        <v>2.18150381665237</v>
       </c>
       <c r="F2057" t="n">
         <v>0.4795755413750845</v>
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.884400512706836</v>
+        <v>3.779511930913781</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.880233126318286</v>
+        <v>-4.887471093898205</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.236993536628203</v>
+        <v>2.234098349596236</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4902288030651559</v>
+        <v>0.4902615799379746</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.483580493308359</v>
+        <v>4.48360015943205</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>60.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>430.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.3%</t>
+          <t>-644.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.8%</t>
+          <t>-150.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.0%</t>
+          <t>-333.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-175.0%</t>
+          <t>-166.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>7.3%</t>
         </is>
       </c>
     </row>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.161720411333774</v>
+        <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.314417281679189</v>
+        <v>1.316351105867182</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.041547327969275</v>
+        <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.36363235946529</v>
+        <v>1.365566183653284</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.906293966639298</v>
+        <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.427821806558721</v>
+        <v>1.429755630746715</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.966168793996991</v>
+        <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.38990936701707</v>
+        <v>1.391843191205064</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.846348563086153</v>
+        <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.453126628615613</v>
+        <v>1.455060452803607</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.848818269547959</v>
+        <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359782945353333</v>
+        <v>1.361716769541326</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.917188455871969</v>
+        <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.25169673230903</v>
+        <v>1.253630556497024</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.930976508719016</v>
+        <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.236618219802103</v>
+        <v>1.238552043990096</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.986496584611605</v>
+        <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.351441026137269</v>
+        <v>1.353374850325263</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.811022324819136</v>
+        <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.426197962046045</v>
+        <v>1.428131786234038</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.803097950234222</v>
+        <v>-3.798263389764238</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.405109740641217</v>
+        <v>1.407043564829211</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.796819747664373</v>
+        <v>-3.791985187194389</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.336159335070607</v>
+        <v>1.3380931592586</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8176560300468725</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.73696712846065</v>
+        <v>-3.732132567990666</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.370272769184228</v>
+        <v>1.372206593372222</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8176560300468725</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.650723665434272</v>
+        <v>-3.645889104964288</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.39971642496864</v>
+        <v>1.401650249156633</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8176560300468725</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.696030484833252</v>
+        <v>-3.691195924363268</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.373369472653573</v>
+        <v>1.375303296841567</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7768458670376417</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.725063589535554</v>
+        <v>-3.72022902906557</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.362308103805754</v>
+        <v>1.364241927993748</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7768458670376417</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.632253108084694</v>
+        <v>-3.62741854761471</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.328704988277464</v>
+        <v>1.330638812465457</v>
       </c>
       <c r="F1946" t="n">
         <v>0.869656348488501</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.676642577414122</v>
+        <v>-3.671808016944138</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.312822676470293</v>
+        <v>1.314756500658287</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8252668791590734</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.793184182519465</v>
+        <v>-3.788349622049481</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.261281742939879</v>
+        <v>1.263215567127873</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7087252740537306</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.833108277102037</v>
+        <v>-3.828273716632053</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.250803400937518</v>
+        <v>1.252737225125511</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7087252740537306</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.86088867500339</v>
+        <v>-3.856054114533406</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.251188443545515</v>
+        <v>1.253122267733509</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6809448761523775</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.979269347733528</v>
+        <v>-3.974434787263544</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.042191894454113</v>
+        <v>1.044125718642107</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6137270240014013</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.087883426176859</v>
+        <v>-4.083048865706875</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.118895923795987</v>
+        <v>1.12082974798398</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6137270240014013</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.052474387928716</v>
+        <v>-4.047639827458732</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.147572565197567</v>
+        <v>1.14950638938556</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6137270240014013</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.014090725370565</v>
+        <v>-4.009256164900581</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.160345471563196</v>
+        <v>1.16227929575119</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6521106865595525</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.836974395335399</v>
+        <v>-3.832139834865415</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.227921032422564</v>
+        <v>1.229854856610558</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6521106865595525</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.882066640168945</v>
+        <v>-3.877232079698961</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.210567526251059</v>
+        <v>1.212501350439053</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5902146433901627</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.702691218930177</v>
+        <v>-3.697856658460193</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.276104670052981</v>
+        <v>1.278038494240974</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7469914015608814</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.747705432450783</v>
+        <v>-3.742870871980799</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.238906439976328</v>
+        <v>1.240840264164321</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7166425062462768</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.014709942723218</v>
+        <v>-4.009875382253234</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.137796198206299</v>
+        <v>1.139730022394293</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5222794682033283</v>
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.115907724160391</v>
+        <v>-4.058325547037066</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.096521007527932</v>
+        <v>1.119553878377262</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.5374027270286457</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.015562914300641</v>
+        <v>3.065682157723023</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.109396757546079</v>
+        <v>-4.051814580422754</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.096725355727973</v>
+        <v>1.119758226577304</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.5374027270286457</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.013162875854958</v>
+        <v>3.06328211927734</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.090358629838781</v>
+        <v>-4.032776452715456</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.100865326019137</v>
+        <v>1.123898196868467</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.4792191156974511</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.974777428264486</v>
+        <v>3.024896671686868</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.142874432113602</v>
+        <v>-4.085292254990277</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.1991534067434</v>
+        <v>1.222186277592729</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.4792191156974511</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.094071829898676</v>
+        <v>3.144191073321058</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.15674119344752</v>
+        <v>-4.099159016324195</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.194440031195966</v>
+        <v>1.217472902045296</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.4413611989636282</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.072190408844516</v>
+        <v>3.122309652266898</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.11193702190759</v>
+        <v>-4.054354844784265</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.218370230208864</v>
+        <v>1.241403101058194</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.4413611989636282</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.078198939241442</v>
+        <v>3.128318182663824</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.964194051672588</v>
+        <v>-3.906611874549263</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.175417639580064</v>
+        <v>1.198450510429394</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.6091685561985114</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.076833574859572</v>
+        <v>3.126952818281953</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.048015272947286</v>
+        <v>-3.990433095823961</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.144682772601666</v>
+        <v>1.167715643450996</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.6091685561985114</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.079627196391053</v>
+        <v>3.129746439813434</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.041862566894501</v>
+        <v>-3.984280389771176</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.147806203414438</v>
+        <v>1.170839074263768</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.531789189880659</v>
+        <v>0.6153212622512957</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.083981168414382</v>
+        <v>3.134100411836763</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.058671865045003</v>
+        <v>-4.001089687921677</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.140162960894348</v>
+        <v>1.163195831743678</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5149798917301573</v>
+        <v>0.5985119641007941</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.072976066264191</v>
+        <v>3.123095309686573</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.996373866268881</v>
+        <v>-3.938791689145555</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.231417714201617</v>
+        <v>1.254450585050947</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5602741560045994</v>
+        <v>0.6438062283752362</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.166488178625677</v>
+        <v>3.216607422048059</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.794583668603723</v>
+        <v>-3.737001491480398</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.114425794981807</v>
+        <v>1.137458665831138</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7582923481737538</v>
+        <v>0.8418244205443906</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.087591095641296</v>
+        <v>3.137710339063679</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.845470381289918</v>
+        <v>-3.787888204166592</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.164361342229505</v>
+        <v>1.187394213078835</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7074056354875593</v>
+        <v>0.7909377078581961</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.127349300351755</v>
+        <v>3.177468543774137</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.758859638640111</v>
+        <v>-3.701277461516785</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.213633375405471</v>
+        <v>1.236666246254801</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7860313666927176</v>
+        <v>0.8695634390633543</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.189152475190894</v>
+        <v>3.239271718613276</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.819068936645395</v>
+        <v>-3.761486759522069</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.188085637028029</v>
+        <v>1.211118507877359</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.725822068687433</v>
+        <v>0.8093541410580698</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.151562877212394</v>
+        <v>3.201682120634777</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.742646890213468</v>
+        <v>-3.685064713090143</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.217146073640728</v>
+        <v>1.240178944490059</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.725822068687433</v>
+        <v>0.8093541410580698</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.150054495252323</v>
+        <v>3.200173738674705</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.6982737585749</v>
+        <v>-3.640691581451574</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.234758193731592</v>
+        <v>1.257791064580922</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.8537272726966384</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.1765412416709</v>
+        <v>3.226660485093283</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.720754109433785</v>
+        <v>-3.663171932310459</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.220159847526629</v>
+        <v>1.243192718375959</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.8537272726966384</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.170935035809491</v>
+        <v>3.221054279231873</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.673098378872729</v>
+        <v>-3.615516201749403</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.245603896778856</v>
+        <v>1.268636767628186</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8178509308870573</v>
+        <v>0.901383003257694</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.205910231173929</v>
+        <v>3.256029474596311</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.572580220373974</v>
+        <v>-3.514998043250648</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.290703533553082</v>
+        <v>1.313736404402412</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9183690893858119</v>
+        <v>1.001901161756449</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.271113499647907</v>
+        <v>3.321232743070289</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.556674890941622</v>
+        <v>-3.499092713818296</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.283820337801896</v>
+        <v>1.306853208651226</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8392564286765729</v>
+        <v>0.9227885010472097</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.210400575698236</v>
+        <v>3.260519819120618</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.511836489333224</v>
+        <v>-3.454254312209898</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.305853401055883</v>
+        <v>1.328886271905214</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8437998616214424</v>
+        <v>0.9273319339920791</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.217224338075786</v>
+        <v>3.267343581498168</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.531334945575232</v>
+        <v>-3.473752768451906</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.302214958190158</v>
+        <v>1.325247829039488</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7957152203415381</v>
+        <v>0.8792472927121748</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.192534492938921</v>
+        <v>3.242653736361303</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.487132108489332</v>
+        <v>-3.429549931366005</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.325775695552355</v>
+        <v>1.348808566401686</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8399180574274385</v>
+        <v>0.9234501297980753</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.224935797718299</v>
+        <v>3.275055041140681</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.494691774326379</v>
+        <v>-3.437109597203052</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.321161829686784</v>
+        <v>1.344194700536114</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.9782535338078946</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.256227840593438</v>
+        <v>3.30634708401582</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.336400356787106</v>
+        <v>-3.27881817966378</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.435726161885533</v>
+        <v>1.458759032734863</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.9782535338078946</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.307475605776477</v>
+        <v>3.357594849198859</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.12875835315263</v>
+        <v>-3.071176176029304</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.517223667933576</v>
+        <v>1.540256538782907</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.102363465071734</v>
+        <v>1.185895537442371</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.430501512551416</v>
+        <v>3.480620755973798</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.077726260430102</v>
+        <v>-3.020144083306776</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.532584733260858</v>
+        <v>1.555617604110188</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.153395557794262</v>
+        <v>1.236927630164899</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.456068996423203</v>
+        <v>3.506188239845585</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.012502079302896</v>
+        <v>-2.95491990217957</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.575861809804445</v>
+        <v>1.598894680653775</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.218619738921468</v>
+        <v>1.302151811292104</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.512390909192232</v>
+        <v>3.562510152614613</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.975075059231763</v>
+        <v>-2.917492882108436</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.586793590132179</v>
+        <v>1.609826460981509</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.223871276950649</v>
+        <v>1.307403349321286</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.511502804309021</v>
+        <v>3.561622047731403</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.995186715266471</v>
+        <v>-2.937604538143145</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.580005720049536</v>
+        <v>1.603038590898866</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.234898621948069</v>
+        <v>1.318430694318705</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.519376003638713</v>
+        <v>3.569495247061095</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.966773452166587</v>
+        <v>-2.909191275043261</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.7519287963107</v>
+        <v>1.77496166716003</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.17592305920164</v>
+        <v>1.259455131572276</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644548437012066</v>
+        <v>3.694667680434448</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.891991191141575</v>
+        <v>-2.834409014018248</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.901954609938522</v>
+        <v>1.924987480787852</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.250705320226652</v>
+        <v>1.334237392597289</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809530702844891</v>
+        <v>3.859649946267273</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.865907106877767</v>
+        <v>-2.80832492975444</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.904096219657904</v>
+        <v>1.927129090507234</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.250705320226652</v>
+        <v>1.334237392597289</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.80123867885875</v>
+        <v>3.851357922281132</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.778029193768646</v>
+        <v>-2.72044701664532</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.937440580485332</v>
+        <v>1.960473451334662</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.366630962650004</v>
+        <v>1.45016303502064</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.86898725989654</v>
+        <v>3.919106503318922</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.769136732375363</v>
+        <v>-2.711554555252036</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.958551970769437</v>
+        <v>1.981584841618767</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.366630962650004</v>
+        <v>1.45016303502064</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886541665623331</v>
+        <v>3.936660909045713</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.93761284934524</v>
+        <v>-2.880030672221914</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.88301657138607</v>
+        <v>1.9060494422354</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.338683126933423</v>
+        <v>1.422215199304059</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.861628011597967</v>
+        <v>3.911747255020349</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.491356656715801</v>
+        <v>-2.433774479592474</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.042788745625707</v>
+        <v>2.065821616475038</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.24396445726379</v>
+        <v>1.327496529634427</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.786066506984049</v>
+        <v>3.836185750406431</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.468635553032648</v>
+        <v>-2.411053375909322</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.042541209595873</v>
+        <v>2.065574080445203</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.24396445726379</v>
+        <v>1.327496529634427</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.776730529480953</v>
+        <v>3.826849772903335</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.59783736632669</v>
+        <v>-2.540255189203364</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.149766610129425</v>
+        <v>2.172799480978755</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.114762643969748</v>
+        <v>1.198294716340384</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.858115567355697</v>
+        <v>3.908234810778079</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.623711764800716</v>
+        <v>-2.56612958767739</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.176494673233461</v>
+        <v>2.199527544082791</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.159674252681489</v>
+        <v>1.243206325052125</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.922140355076388</v>
+        <v>3.972259598498771</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.616657074585543</v>
+        <v>-2.559074897462216</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.175991905309075</v>
+        <v>2.199024776158406</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.166728942896663</v>
+        <v>1.250261015267299</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.923048525195038</v>
+        <v>3.97316776861742</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.589705850259055</v>
+        <v>-2.532123673135728</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.196778548684413</v>
+        <v>2.219811419533743</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.181609288924382</v>
+        <v>1.265141361295018</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.941982886456411</v>
+        <v>3.992102129878793</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.725658858315371</v>
+        <v>-2.668076681192045</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.326500477606846</v>
+        <v>2.349533348456176</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.181609288924382</v>
+        <v>1.265141361295018</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.126086018601371</v>
+        <v>4.176205262023752</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.748066976120243</v>
+        <v>-2.690484798996917</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.30965392538789</v>
+        <v>2.33268679623722</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.181609288924382</v>
+        <v>1.265141361295018</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.118202713504364</v>
+        <v>4.168321956926746</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.776291211697843</v>
+        <v>-2.718709034574517</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.300418230706487</v>
+        <v>2.323451101555817</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.19958604137569</v>
+        <v>1.283118113746327</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.131042764524786</v>
+        <v>4.181162007947169</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.785732137586373</v>
+        <v>-2.728149960463047</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.352895578072923</v>
+        <v>2.375928448922253</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.322013158919082</v>
+        <v>1.405545231289719</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.260752752772668</v>
+        <v>4.310871996195051</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.838005744922015</v>
+        <v>-2.780423567798688</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.334877229683967</v>
+        <v>2.357910100533297</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.353271623954077</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.282398926338967</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.914335722522921</v>
+        <v>-2.856753545399594</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.30245705153738</v>
+        <v>2.32548992238671</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.353271623954077</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.280510739232742</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.116589442847274</v>
+        <v>-3.059007265723948</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.216375793010501</v>
+        <v>2.239408663859831</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.151017903629724</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.153978736640992</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.278157868374529</v>
+        <v>-3.220575691251203</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.150182433009751</v>
+        <v>2.173215303859081</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>1.024234979831844</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>4.076342992572417</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.410459160472082</v>
+        <v>-3.352876983348756</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.110335323036648</v>
+        <v>2.133368193885978</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>1.024234979831844</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>4.089416399438336</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.596327471311312</v>
+        <v>-3.538745294187986</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.027993195483896</v>
+        <v>2.051026066333226</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.8656693865118967</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.986282240229307</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.624228258420785</v>
+        <v>-3.566646081297459</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.015356921767109</v>
+        <v>2.03838979261644</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.8310724623689619</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.964048126870548</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.746754361123679</v>
+        <v>-3.689172184000353</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.96311092466315</v>
+        <v>1.986143795512481</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.708546359666068</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.88729690922601</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.977268857309268</v>
+        <v>-3.919686680185941</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.937611085779419</v>
+        <v>1.960643956628749</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.4780318634804793</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.815694171105161</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.233989675304091</v>
+        <v>-4.176407498180765</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.975234477583336</v>
+        <v>1.998267348432667</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3696172893366645</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.890957145620719</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.387976093080232</v>
+        <v>-4.330393915956906</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.98262017961852</v>
+        <v>2.00565305046785</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3696172893366645</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.959937414766359</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.337454189252566</v>
+        <v>-4.27987201212924</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.988880143269707</v>
+        <v>2.011913014119037</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3696172893366645</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.94598861688648</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.58992934326029</v>
+        <v>-4.532347166136964</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.899760570722031</v>
+        <v>1.922793441571362</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3696172893366645</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.957859105941893</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.882825099739702</v>
+        <v>-4.825242922616376</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.78381280264921</v>
+        <v>1.806845673498541</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3696172893366645</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.959069640460838</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.06948922787451</v>
+        <v>-5.011907050751184</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.713268893622608</v>
+        <v>1.736301764471939</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.3428783185121046</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.947148000193422</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.215509914788472</v>
+        <v>-5.157927737665147</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.649938471593213</v>
+        <v>1.672971342442543</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.3337952267182476</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.936775997853298</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.307223923898057</v>
+        <v>-5.249641746774731</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.775456924648423</v>
+        <v>1.798489795497753</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.3337952267182476</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.098980054552342</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.39194186611901</v>
+        <v>-5.334359688995685</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.736416385723856</v>
+        <v>1.759449256573186</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1651471254195646</v>
+        <v>0.2486791977902013</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.992637831736946</v>
+        <v>4.042757075159328</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.473876684387894</v>
+        <v>-5.416294507264568</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.713871875984794</v>
+        <v>1.736904746834124</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1552123798324844</v>
+        <v>0.2387444522031211</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.99690640195319</v>
+        <v>4.047025645375571</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.575852806636301</v>
+        <v>-5.518270629512975</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.682007065541333</v>
+        <v>1.705039936390663</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.05323625758407685</v>
+        <v>0.1367683299547135</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.944646367060048</v>
+        <v>3.994765610482429</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.46584652315908</v>
+        <v>-5.408264346035754</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.718162466176397</v>
+        <v>1.741195337025728</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.07644082950135206</v>
+        <v>0.1599729018719887</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.950721997454588</v>
+        <v>4.00084124087697</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.322786947418154</v>
+        <v>-5.265204770294828</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.779636307194742</v>
+        <v>1.802669178044072</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.08445425609133134</v>
+        <v>0.167986328461968</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.95978006413055</v>
+        <v>4.009899307552931</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.021340221946316</v>
+        <v>-4.96375804482299</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.907475880266013</v>
+        <v>1.930508751115343</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.4694330539338052</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.147908982296189</v>
+        <v>4.19802822571857</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.0459304661815</v>
+        <v>-4.988348289058174</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.89861096032465</v>
+        <v>1.92164383117398</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.4694330539338052</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.148880160048899</v>
+        <v>4.198999403471281</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.99489209017498</v>
+        <v>-4.937309913051654</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.919869215107013</v>
+        <v>1.942902085956344</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.4694330539338052</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.149723064428654</v>
+        <v>4.199842307851036</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.953752795308349</v>
+        <v>-4.896170618185023</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.955363031927811</v>
+        <v>1.978395902777141</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4270402764297994</v>
+        <v>0.5105723488004361</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.193444740222778</v>
+        <v>4.24356398364516</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.857117883289709</v>
+        <v>-4.799535706166383</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.810200992859202</v>
+        <v>1.833233863708532</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5236751884484394</v>
+        <v>0.6072072608190761</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.067609683557897</v>
+        <v>4.117728926980278</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.987698617820551</v>
+        <v>-4.930116440697225</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.761470743120828</v>
+        <v>1.784503613970159</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3930944539175969</v>
+        <v>0.4766265262882335</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.992763286913354</v>
+        <v>4.042882530335737</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.823202283629589</v>
+        <v>-4.765620106506264</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.811696095873295</v>
+        <v>1.834728966722626</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3930944539175969</v>
+        <v>0.4766265262882335</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.977190105989437</v>
+        <v>4.027309349411819</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.850572216314021</v>
+        <v>-4.792990039190696</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.799935833235953</v>
+        <v>1.822968704085283</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3930944539175969</v>
+        <v>0.4766265262882335</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.976377816425867</v>
+        <v>4.026497059848249</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.860957411203911</v>
+        <v>-4.803375234080585</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.805650534405069</v>
+        <v>1.828683405254399</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3827092590277076</v>
+        <v>0.4662413313983442</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.980015478617005</v>
+        <v>4.030134722039388</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.879545569926136</v>
+        <v>-4.82196339280281</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.869052276692604</v>
+        <v>1.892085147541935</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3641211003054822</v>
+        <v>0.4476531726761189</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.039699589160096</v>
+        <v>4.089818832582478</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.879844116622172</v>
+        <v>-4.822261939498846</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.865801868832488</v>
+        <v>1.888834739681819</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3641211003054822</v>
+        <v>0.4476531726761189</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.036568599978394</v>
+        <v>4.086687843400776</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.779020982931744</v>
+        <v>-4.721438805808418</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.910662017248051</v>
+        <v>1.933694888097381</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3765853157898361</v>
+        <v>0.4601173881604727</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.048578024208398</v>
+        <v>4.098697267630779</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.588239622179337</v>
+        <v>-4.530657445056011</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.987103815027557</v>
+        <v>2.010136685876887</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5673666765422434</v>
+        <v>0.6508987489128801</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.163176094138385</v>
+        <v>4.213295337560767</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.569722768137517</v>
+        <v>-4.512140591014191</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.974347402381881</v>
+        <v>1.997380273231212</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5802968059674516</v>
+        <v>0.6638288783380883</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.150771017531107</v>
+        <v>4.200890260953489</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.544529583636199</v>
+        <v>-4.486947406512873</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019391612794467</v>
+        <v>2.042424483643797</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6054899904687699</v>
+        <v>0.6890220628394067</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.200853864843956</v>
+        <v>4.250973108266338</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.532475456723236</v>
+        <v>-4.47489327959991</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.01789983146109</v>
+        <v>2.04093270231042</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6175441173817328</v>
+        <v>0.7010761897523695</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.201772908893171</v>
+        <v>4.251892152315554</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.539098703413594</v>
+        <v>-4.481516526290268</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.017131162969083</v>
+        <v>2.040164033818413</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6109208706913745</v>
+        <v>0.6944529430620112</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.199679591063092</v>
+        <v>4.249798834485475</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.436218113885001</v>
+        <v>-4.378635936761675</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.071134424658402</v>
+        <v>2.094167295507733</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7973335325906041</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.27425897065813</v>
+        <v>4.324378214080513</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.459660153065088</v>
+        <v>-4.402077975941762</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.081960279159962</v>
+        <v>2.104993150009292</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7973335325906041</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.294461640831725</v>
+        <v>4.344580884254107</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.4777326613567</v>
+        <v>-4.420150484233374</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.074731275843317</v>
+        <v>2.097764146692648</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7973335325906041</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.294461640831725</v>
+        <v>4.344580884254107</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.708906455233332</v>
+        <v>-4.651324278110006</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.942513671886131</v>
+        <v>1.965546542735461</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7973335325906041</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.254713554425192</v>
+        <v>4.304832797847574</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.677620434692876</v>
+        <v>-4.620038257569551</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.962050699099253</v>
+        <v>1.985083569948583</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7450874807604227</v>
+        <v>0.8286195531310595</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.280507785746405</v>
+        <v>4.330627029168787</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.524595042579592</v>
+        <v>-4.467012865456266</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.122431855517471</v>
+        <v>2.145464726366801</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8981128728737069</v>
+        <v>0.9816449452443436</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.471494020587279</v>
+        <v>4.521613264009662</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.552902356452862</v>
+        <v>-4.495320179329537</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.298575154876455</v>
+        <v>2.321608025725785</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8981128728737069</v>
+        <v>0.9816449452443436</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.658960245495572</v>
+        <v>4.709079488917954</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.719495581566385</v>
+        <v>-4.661913404443059</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.201340816185128</v>
+        <v>2.224373687034459</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7315196477601844</v>
+        <v>0.8150517201308212</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.528407261781541</v>
+        <v>4.578526505203923</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.546431202184085</v>
+        <v>-4.488849025060759</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.274242970599766</v>
+        <v>2.297275841449097</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7315196477601844</v>
+        <v>0.8150517201308212</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.532083664443259</v>
+        <v>4.582202907865641</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.517185221728388</v>
+        <v>-4.459603044605062</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.28355941790554</v>
+        <v>2.306592288754871</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7315196477601844</v>
+        <v>0.8150517201308212</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.529701719566754</v>
+        <v>4.579820962989135</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.624110769606239</v>
+        <v>-4.566528592482913</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.238082437912035</v>
+        <v>2.261115308761365</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6245940998823331</v>
+        <v>0.7081261722529698</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.462839629997678</v>
+        <v>4.51295887342006</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.769129328113488</v>
+        <v>-4.711547150990162</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.18150381665237</v>
+        <v>2.2045366875017</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4795755413750845</v>
+        <v>0.5631076137457213</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.377257297036563</v>
+        <v>4.427376540458945</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.779511930913781</v>
+        <v>3.883261628616321</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.887471093898205</v>
+        <v>-4.82988891677488</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.234098349596236</v>
+        <v>2.257131220445566</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4902615799379746</v>
+        <v>0.5737936523086113</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.48360015943205</v>
+        <v>4.533719402854432</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>100.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>126.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>430.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.6%</t>
+          <t>-637.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.5%</t>
+          <t>-147.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-333.9%</t>
+          <t>-328.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.6%</t>
+          <t>-170.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2058"/>
+  <dimension ref="A1:G2059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.058325547037066</v>
+        <v>-4.111073163690407</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.119553878377262</v>
+        <v>1.098454831715925</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5374027270286457</v>
+        <v>0.4538706546580091</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.065682157723023</v>
+        <v>3.015562914300641</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.051814580422754</v>
+        <v>-4.104562197076095</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.119758226577304</v>
+        <v>1.098659179915967</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5374027270286457</v>
+        <v>0.4538706546580091</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.06328211927734</v>
+        <v>3.013162875854958</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.032776452715456</v>
+        <v>-4.085524069368797</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.123898196868467</v>
+        <v>1.102799150207131</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4792191156974511</v>
+        <v>0.3956870433268145</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.024896671686868</v>
+        <v>2.974777428264486</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.085292254990277</v>
+        <v>-4.138039871643618</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.222186277592729</v>
+        <v>1.201087230931393</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4792191156974511</v>
+        <v>0.3956870433268145</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.144191073321058</v>
+        <v>3.094071829898676</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.099159016324195</v>
+        <v>-4.151906632977536</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.217472902045296</v>
+        <v>1.19637385538396</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4413611989636282</v>
+        <v>0.3578291265929916</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.122309652266898</v>
+        <v>3.072190408844516</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.054354844784265</v>
+        <v>-4.107102461437606</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.241403101058194</v>
+        <v>1.220304054396858</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4413611989636282</v>
+        <v>0.3578291265929916</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.128318182663824</v>
+        <v>3.078198939241442</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.906611874549263</v>
+        <v>-3.959359491202604</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.198450510429394</v>
+        <v>1.177351463768058</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6091685561985114</v>
+        <v>0.5256364838278748</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.126952818281953</v>
+        <v>3.076833574859572</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.990433095823961</v>
+        <v>-4.043180712477302</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.167715643450996</v>
+        <v>1.14661659678966</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6091685561985114</v>
+        <v>0.5256364838278748</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.129746439813434</v>
+        <v>3.079627196391053</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.984280389771176</v>
+        <v>-4.037028006424517</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.170839074263768</v>
+        <v>1.149740027602432</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6153212622512957</v>
+        <v>0.531789189880659</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.134100411836763</v>
+        <v>3.083981168414382</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.001089687921677</v>
+        <v>-4.053837304575019</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.163195831743678</v>
+        <v>1.142096785082341</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5985119641007941</v>
+        <v>0.5149798917301573</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.123095309686573</v>
+        <v>3.072976066264191</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.938791689145555</v>
+        <v>-3.991539305798897</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.254450585050947</v>
+        <v>1.233351538389611</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6438062283752362</v>
+        <v>0.5602741560045994</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.216607422048059</v>
+        <v>3.166488178625677</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.737001491480398</v>
+        <v>-3.789749108133739</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.137458665831138</v>
+        <v>1.116359619169801</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8418244205443906</v>
+        <v>0.7582923481737538</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.137710339063679</v>
+        <v>3.087591095641296</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.787888204166592</v>
+        <v>-3.840635820819934</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.187394213078835</v>
+        <v>1.166295166417498</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7909377078581961</v>
+        <v>0.7074056354875593</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.177468543774137</v>
+        <v>3.127349300351755</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.701277461516785</v>
+        <v>-3.754025078170127</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.236666246254801</v>
+        <v>1.215567199593465</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8695634390633543</v>
+        <v>0.7860313666927176</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.239271718613276</v>
+        <v>3.189152475190894</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.761486759522069</v>
+        <v>-3.814234376175411</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.211118507877359</v>
+        <v>1.190019461216023</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8093541410580698</v>
+        <v>0.725822068687433</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.201682120634777</v>
+        <v>3.151562877212394</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.685064713090143</v>
+        <v>-3.737812329743484</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.240178944490059</v>
+        <v>1.219079897828722</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8093541410580698</v>
+        <v>0.725822068687433</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.200173738674705</v>
+        <v>3.150054495252323</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.640691581451574</v>
+        <v>-3.693439198104916</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.257791064580922</v>
+        <v>1.236692017919586</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8537272726966384</v>
+        <v>0.7701952003260016</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.226660485093283</v>
+        <v>3.1765412416709</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.663171932310459</v>
+        <v>-3.715919548963801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.243192718375959</v>
+        <v>1.222093671714622</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8537272726966384</v>
+        <v>0.7701952003260016</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.221054279231873</v>
+        <v>3.170935035809491</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.615516201749403</v>
+        <v>-3.668263818402745</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.268636767628186</v>
+        <v>1.247537720966849</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.901383003257694</v>
+        <v>0.8178509308870573</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.256029474596311</v>
+        <v>3.205910231173929</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.514998043250648</v>
+        <v>-3.567745659903991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.313736404402412</v>
+        <v>1.292637357741076</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.001901161756449</v>
+        <v>0.9183690893858119</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.321232743070289</v>
+        <v>3.271113499647907</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.499092713818296</v>
+        <v>-3.551840330471638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.306853208651226</v>
+        <v>1.285754161989889</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9227885010472097</v>
+        <v>0.8392564286765729</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.260519819120618</v>
+        <v>3.210400575698236</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.454254312209898</v>
+        <v>-3.50700192886324</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.328886271905214</v>
+        <v>1.307787225243877</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9273319339920791</v>
+        <v>0.8437998616214424</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.267343581498168</v>
+        <v>3.217224338075786</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.473752768451906</v>
+        <v>-3.526500385105248</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.325247829039488</v>
+        <v>1.304148782378152</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8792472927121748</v>
+        <v>0.7957152203415381</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.242653736361303</v>
+        <v>3.192534492938921</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.429549931366005</v>
+        <v>-3.482297548019348</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.348808566401686</v>
+        <v>1.327709519740349</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9234501297980753</v>
+        <v>0.8399180574274385</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.275055041140681</v>
+        <v>3.224935797718299</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.437109597203052</v>
+        <v>-3.489857213856395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.344194700536114</v>
+        <v>1.323095653874778</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9782535338078946</v>
+        <v>0.8947214614372578</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.30634708401582</v>
+        <v>3.256227840593438</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.27881817966378</v>
+        <v>-3.331565796317122</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.458759032734863</v>
+        <v>1.437659986073526</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9782535338078946</v>
+        <v>0.8947214614372578</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.357594849198859</v>
+        <v>3.307475605776477</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.071176176029304</v>
+        <v>-3.123923792682646</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.540256538782907</v>
+        <v>1.51915749212157</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.185895537442371</v>
+        <v>1.102363465071734</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.480620755973798</v>
+        <v>3.430501512551416</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.020144083306776</v>
+        <v>-3.072891699960118</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.555617604110188</v>
+        <v>1.534518557448851</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.236927630164899</v>
+        <v>1.153395557794262</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.506188239845585</v>
+        <v>3.456068996423203</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.95491990217957</v>
+        <v>-3.007667518832912</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.598894680653775</v>
+        <v>1.577795633992438</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.302151811292104</v>
+        <v>1.218619738921468</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.562510152614613</v>
+        <v>3.512390909192232</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.917492882108436</v>
+        <v>-2.970240498761779</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.609826460981509</v>
+        <v>1.588727414320172</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.307403349321286</v>
+        <v>1.223871276950649</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.561622047731403</v>
+        <v>3.511502804309021</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.937604538143145</v>
+        <v>-2.990352154796487</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.603038590898866</v>
+        <v>1.581939544237529</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.318430694318705</v>
+        <v>1.234898621948069</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.569495247061095</v>
+        <v>3.519376003638713</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.909191275043261</v>
+        <v>-2.961938891696603</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.77496166716003</v>
+        <v>1.753862620498693</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.259455131572276</v>
+        <v>1.17592305920164</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.694667680434448</v>
+        <v>3.644548437012066</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.834409014018248</v>
+        <v>-2.887156630671591</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.924987480787852</v>
+        <v>1.903888434126516</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.334237392597289</v>
+        <v>1.250705320226652</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.859649946267273</v>
+        <v>3.809530702844891</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.80832492975444</v>
+        <v>-2.861072546407783</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.927129090507234</v>
+        <v>1.906030043845898</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.334237392597289</v>
+        <v>1.250705320226652</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.851357922281132</v>
+        <v>3.80123867885875</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.72044701664532</v>
+        <v>-2.773194633298662</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.960473451334662</v>
+        <v>1.939374404673326</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.45016303502064</v>
+        <v>1.366630962650004</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.919106503318922</v>
+        <v>3.86898725989654</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.711554555252036</v>
+        <v>-2.764302171905379</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.981584841618767</v>
+        <v>1.96048579495743</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.45016303502064</v>
+        <v>1.366630962650004</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.936660909045713</v>
+        <v>3.886541665623331</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.880030672221914</v>
+        <v>-2.932778288875256</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.9060494422354</v>
+        <v>1.884950395574063</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.422215199304059</v>
+        <v>1.338683126933423</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.911747255020349</v>
+        <v>3.861628011597967</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.433774479592474</v>
+        <v>-2.486522096245817</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.065821616475038</v>
+        <v>2.044722569813701</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.327496529634427</v>
+        <v>1.24396445726379</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.836185750406431</v>
+        <v>3.786066506984049</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.411053375909322</v>
+        <v>-2.463800992562664</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.065574080445203</v>
+        <v>2.044475033783867</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.327496529634427</v>
+        <v>1.24396445726379</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.826849772903335</v>
+        <v>3.776730529480953</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.540255189203364</v>
+        <v>-2.593002805856707</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.172799480978755</v>
+        <v>2.151700434317418</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.198294716340384</v>
+        <v>1.114762643969748</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.908234810778079</v>
+        <v>3.858115567355697</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.56612958767739</v>
+        <v>-2.618877204330732</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.199527544082791</v>
+        <v>2.178428497421455</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.243206325052125</v>
+        <v>1.159674252681489</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.972259598498771</v>
+        <v>3.922140355076388</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.559074897462216</v>
+        <v>-2.611822514115559</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.199024776158406</v>
+        <v>2.177925729497069</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.250261015267299</v>
+        <v>1.166728942896663</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.97316776861742</v>
+        <v>3.923048525195038</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.532123673135728</v>
+        <v>-2.584871289789071</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.219811419533743</v>
+        <v>2.198712372872406</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.265141361295018</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.992102129878793</v>
+        <v>3.941982886456411</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.668076681192045</v>
+        <v>-2.720824297845387</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.349533348456176</v>
+        <v>2.328434301794839</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.265141361295018</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.176205262023752</v>
+        <v>4.126086018601371</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.690484798996917</v>
+        <v>-2.743232415650259</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.33268679623722</v>
+        <v>2.311587749575883</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.265141361295018</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.168321956926746</v>
+        <v>4.118202713504364</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.718709034574517</v>
+        <v>-2.771456651227859</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.323451101555817</v>
+        <v>2.302352054894481</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.283118113746327</v>
+        <v>1.19958604137569</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.181162007947169</v>
+        <v>4.131042764524786</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.728149960463047</v>
+        <v>-2.780897577116389</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.375928448922253</v>
+        <v>2.354829402260916</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.405545231289719</v>
+        <v>1.322013158919082</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.310871996195051</v>
+        <v>4.260752752772668</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.780423567798688</v>
+        <v>-2.833171184452031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.357910100533297</v>
+        <v>2.33681105387196</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.353271623954077</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.282398926338967</v>
+        <v>4.232279682916585</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.856753545399594</v>
+        <v>-2.909501162052937</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.32548992238671</v>
+        <v>2.304390875725373</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.353271623954077</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.280510739232742</v>
+        <v>4.23039149581036</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.059007265723948</v>
+        <v>-3.11175488237729</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.239408663859831</v>
+        <v>2.218309617198494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.151017903629724</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.153978736640992</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.220575691251203</v>
+        <v>-3.273323307904545</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.173215303859081</v>
+        <v>2.152116257197744</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.024234979831844</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.076342992572417</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.352876983348756</v>
+        <v>-3.405624600002098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.133368193885978</v>
+        <v>2.112269147224642</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.024234979831844</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.089416399438336</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.538745294187986</v>
+        <v>-3.591492910841328</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.051026066333226</v>
+        <v>2.02992701967189</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8656693865118967</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.986282240229307</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.566646081297459</v>
+        <v>-3.619393697950801</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.03838979261644</v>
+        <v>2.017290745955103</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8310724623689619</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.964048126870548</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.689172184000353</v>
+        <v>-3.741919800653695</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.986143795512481</v>
+        <v>1.965044748851144</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.708546359666068</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.88729690922601</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.919686680185941</v>
+        <v>-3.972434296839284</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.960643956628749</v>
+        <v>1.939544909967412</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4780318634804793</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.815694171105161</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.176407498180765</v>
+        <v>-4.229155114834107</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.998267348432667</v>
+        <v>1.97716830177133</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3696172893366645</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.890957145620719</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.330393915956906</v>
+        <v>-4.383141532610248</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.00565305046785</v>
+        <v>1.984554003806513</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3696172893366645</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.959937414766359</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.27987201212924</v>
+        <v>-4.332619628782582</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.011913014119037</v>
+        <v>1.990813967457701</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3696172893366645</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.94598861688648</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.532347166136964</v>
+        <v>-4.585094782790306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.922793441571362</v>
+        <v>1.901694394910025</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3696172893366645</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.957859105941893</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.825242922616376</v>
+        <v>-4.877990539269718</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.806845673498541</v>
+        <v>1.785746626837204</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3696172893366645</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.959069640460838</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.011907050751184</v>
+        <v>-5.064654667404526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.736301764471939</v>
+        <v>1.715202717810602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3428783185121046</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.947148000193422</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.157927737665147</v>
+        <v>-5.210675354318488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.672971342442543</v>
+        <v>1.651872295781207</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3337952267182476</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.936775997853298</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.249641746774731</v>
+        <v>-5.302389363428073</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.798489795497753</v>
+        <v>1.777390748836417</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3337952267182476</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.098980054552342</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.334359688995685</v>
+        <v>-5.387107305649026</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759449256573186</v>
+        <v>1.73835020991185</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2486791977902013</v>
+        <v>0.1651471254195646</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.042757075159328</v>
+        <v>3.992637831736946</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.416294507264568</v>
+        <v>-5.46904212391791</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.736904746834124</v>
+        <v>1.715805700172787</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2387444522031211</v>
+        <v>0.1552123798324844</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.047025645375571</v>
+        <v>3.99690640195319</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.518270629512975</v>
+        <v>-5.571018246166317</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.705039936390663</v>
+        <v>1.683940889729327</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1367683299547135</v>
+        <v>0.05323625758407685</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.994765610482429</v>
+        <v>3.944646367060048</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.408264346035754</v>
+        <v>-5.461011962689096</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741195337025728</v>
+        <v>1.720096290364391</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1599729018719887</v>
+        <v>0.07644082950135206</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.00084124087697</v>
+        <v>3.950721997454588</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.265204770294828</v>
+        <v>-5.31795238694817</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802669178044072</v>
+        <v>1.781570131382736</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.167986328461968</v>
+        <v>0.08445425609133134</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.009899307552931</v>
+        <v>3.95978006413055</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.96375804482299</v>
+        <v>-5.016505661476332</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.930508751115343</v>
+        <v>1.909409704454007</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4694330539338052</v>
+        <v>0.3859009815631686</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.19802822571857</v>
+        <v>4.147908982296189</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.988348289058174</v>
+        <v>-5.041095905711516</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.92164383117398</v>
+        <v>1.900544784512644</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4694330539338052</v>
+        <v>0.3859009815631686</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.198999403471281</v>
+        <v>4.148880160048899</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.937309913051654</v>
+        <v>-4.990057529704996</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.942902085956344</v>
+        <v>1.921803039295007</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4694330539338052</v>
+        <v>0.3859009815631686</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.199842307851036</v>
+        <v>4.149723064428654</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.896170618185023</v>
+        <v>-4.948918234838365</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978395902777141</v>
+        <v>1.957296856115804</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5105723488004361</v>
+        <v>0.4270402764297994</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.24356398364516</v>
+        <v>4.193444740222778</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.799535706166383</v>
+        <v>-4.852283322819725</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833233863708532</v>
+        <v>1.812134817047195</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6072072608190761</v>
+        <v>0.5236751884484394</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.117728926980278</v>
+        <v>4.067609683557897</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.930116440697225</v>
+        <v>-4.982864057350567</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784503613970159</v>
+        <v>1.763404567308822</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4766265262882335</v>
+        <v>0.3930944539175969</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.042882530335737</v>
+        <v>3.992763286913354</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.765620106506264</v>
+        <v>-4.818367723159605</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.834728966722626</v>
+        <v>1.813629920061289</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4766265262882335</v>
+        <v>0.3930944539175969</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.027309349411819</v>
+        <v>3.977190105989437</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.792990039190696</v>
+        <v>-4.845737655844037</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.822968704085283</v>
+        <v>1.801869657423946</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4766265262882335</v>
+        <v>0.3930944539175969</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.026497059848249</v>
+        <v>3.976377816425867</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.803375234080585</v>
+        <v>-4.856122850733927</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.828683405254399</v>
+        <v>1.807584358593063</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4662413313983442</v>
+        <v>0.3827092590277076</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.030134722039388</v>
+        <v>3.980015478617005</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.82196339280281</v>
+        <v>-4.874711009456152</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.892085147541935</v>
+        <v>1.870986100880598</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4476531726761189</v>
+        <v>0.3641211003054822</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.089818832582478</v>
+        <v>4.039699589160096</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.822261939498846</v>
+        <v>-4.875009556152188</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.888834739681819</v>
+        <v>1.867735693020482</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4476531726761189</v>
+        <v>0.3641211003054822</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.086687843400776</v>
+        <v>4.036568599978394</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.721438805808418</v>
+        <v>-4.77418642246176</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.933694888097381</v>
+        <v>1.912595841436044</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4601173881604727</v>
+        <v>0.3765853157898361</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.098697267630779</v>
+        <v>4.048578024208398</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.530657445056011</v>
+        <v>-4.583405061709353</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.010136685876887</v>
+        <v>1.98903763921555</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6508987489128801</v>
+        <v>0.5673666765422434</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.213295337560767</v>
+        <v>4.163176094138385</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.512140591014191</v>
+        <v>-4.564888207667533</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.997380273231212</v>
+        <v>1.976281226569875</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6638288783380883</v>
+        <v>0.5802968059674516</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.200890260953489</v>
+        <v>4.150771017531107</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.486947406512873</v>
+        <v>-4.539695023166215</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.042424483643797</v>
+        <v>2.021325436982461</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6890220628394067</v>
+        <v>0.6054899904687699</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.250973108266338</v>
+        <v>4.200853864843956</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.47489327959991</v>
+        <v>-4.527640896253252</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.04093270231042</v>
+        <v>2.019833655649084</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7010761897523695</v>
+        <v>0.6175441173817328</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.251892152315554</v>
+        <v>4.201772908893171</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.481516526290268</v>
+        <v>-4.53426414294361</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.040164033818413</v>
+        <v>2.019064987157076</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6944529430620112</v>
+        <v>0.6109208706913745</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.249798834485475</v>
+        <v>4.199679591063092</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.378635936761675</v>
+        <v>-4.431383553415017</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.094167295507733</v>
+        <v>2.073068248846396</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7973335325906041</v>
+        <v>0.7138014602199674</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.324378214080513</v>
+        <v>4.27425897065813</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.402077975941762</v>
+        <v>-4.454825592595104</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.104993150009292</v>
+        <v>2.083894103347955</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7973335325906041</v>
+        <v>0.7138014602199674</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.344580884254107</v>
+        <v>4.294461640831725</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.420150484233374</v>
+        <v>-4.472898100886716</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.097764146692648</v>
+        <v>2.076665100031311</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7973335325906041</v>
+        <v>0.7138014602199674</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.344580884254107</v>
+        <v>4.294461640831725</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.651324278110006</v>
+        <v>-4.704071894763348</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.965546542735461</v>
+        <v>1.944447496074125</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7973335325906041</v>
+        <v>0.7138014602199674</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.304832797847574</v>
+        <v>4.254713554425192</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.620038257569551</v>
+        <v>-4.672785874222892</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.985083569948583</v>
+        <v>1.963984523287247</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8286195531310595</v>
+        <v>0.7450874807604227</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.330627029168787</v>
+        <v>4.280507785746405</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.467012865456266</v>
+        <v>-4.519760482109608</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.145464726366801</v>
+        <v>2.124365679705464</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9816449452443436</v>
+        <v>0.8981128728737069</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.521613264009662</v>
+        <v>4.471494020587279</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.495320179329537</v>
+        <v>-4.548067795982878</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.321608025725785</v>
+        <v>2.300508979064449</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9816449452443436</v>
+        <v>0.8981128728737069</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.709079488917954</v>
+        <v>4.658960245495572</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.661913404443059</v>
+        <v>-4.714661021096401</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.224373687034459</v>
+        <v>2.203274640373122</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8150517201308212</v>
+        <v>0.7315196477601844</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.578526505203923</v>
+        <v>4.528407261781541</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.488849025060759</v>
+        <v>-4.541596641714101</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.297275841449097</v>
+        <v>2.27617679478776</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8150517201308212</v>
+        <v>0.7315196477601844</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.582202907865641</v>
+        <v>4.532083664443259</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.459603044605062</v>
+        <v>-4.512350661258404</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.306592288754871</v>
+        <v>2.285493242093534</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8150517201308212</v>
+        <v>0.7315196477601844</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.579820962989135</v>
+        <v>4.529701719566754</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.566528592482913</v>
+        <v>-4.619276209136255</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.261115308761365</v>
+        <v>2.240016262100029</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7081261722529698</v>
+        <v>0.6245940998823331</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.51295887342006</v>
+        <v>4.462839629997678</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.711547150990162</v>
+        <v>-4.764294767643504</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.2045366875017</v>
+        <v>2.183437640840364</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5631076137457213</v>
+        <v>0.4795755413750845</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.427376540458945</v>
+        <v>4.377257297036563</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,45 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.883261628616321</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.82988891677488</v>
+        <v>-4.754832812719731</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.257131220445566</v>
+        <v>2.287153662067626</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5737936523086113</v>
+        <v>0.5400821923113521</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.533719402854432</v>
+        <v>4.513492526856076</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="2" t="n">
+        <v>45521</v>
+      </c>
+      <c r="B2059" t="n">
+        <v>3.880701500692747</v>
+      </c>
+      <c r="C2059" t="n">
+        <v>4.385400062628727</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>-4.754832812719731</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>2.287153662067626</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>0.5400821923113521</v>
+      </c>
+      <c r="G2059" t="n">
+        <v>4.378463859615095</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.8%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>125.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>430.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-637.1%</t>
+          <t>-645.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-151.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.8%</t>
+          <t>-333.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-170.0%</t>
+          <t>-167.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-10.0%</t>
         </is>
       </c>
     </row>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.161720411333774</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.314417281679189</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.041547327969275</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.36363235946529</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.906293966639298</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.427821806558721</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.966168793996991</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.38990936701707</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.846348563086153</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.453126628615613</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.848818269547959</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.359782945353333</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.917188455871969</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.25169673230903</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.930976508719016</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.236618219802103</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.986496584611605</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.351441026137269</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.811022324819136</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.426197962046045</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.798263389764238</v>
+        <v>-3.803097950234222</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.407043564829211</v>
+        <v>1.405109740641217</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.791985187194389</v>
+        <v>-3.796819747664373</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.3380931592586</v>
+        <v>1.336159335070607</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8176560300468725</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.732132567990666</v>
+        <v>-3.73696712846065</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.372206593372222</v>
+        <v>1.370272769184228</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8176560300468725</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.645889104964288</v>
+        <v>-3.650723665434272</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.401650249156633</v>
+        <v>1.39971642496864</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8176560300468725</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.691195924363268</v>
+        <v>-3.696030484833252</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.375303296841567</v>
+        <v>1.373369472653573</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7768458670376417</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.72022902906557</v>
+        <v>-3.725063589535554</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.364241927993748</v>
+        <v>1.362308103805754</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7768458670376417</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.62741854761471</v>
+        <v>-3.632253108084694</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.330638812465457</v>
+        <v>1.328704988277464</v>
       </c>
       <c r="F1946" t="n">
         <v>0.869656348488501</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.671808016944138</v>
+        <v>-3.676642577414122</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.314756500658287</v>
+        <v>1.312822676470293</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8252668791590734</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.788349622049481</v>
+        <v>-3.793184182519465</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.263215567127873</v>
+        <v>1.261281742939879</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7087252740537306</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.828273716632053</v>
+        <v>-3.833108277102037</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.252737225125511</v>
+        <v>1.250803400937518</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7087252740537306</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.856054114533406</v>
+        <v>-3.86088867500339</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.253122267733509</v>
+        <v>1.251188443545515</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6809448761523775</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.974434787263544</v>
+        <v>-3.979269347733528</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.044125718642107</v>
+        <v>1.042191894454113</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6137270240014013</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.083048865706875</v>
+        <v>-4.087883426176859</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.12082974798398</v>
+        <v>1.118895923795987</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6137270240014013</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.047639827458732</v>
+        <v>-4.052474387928716</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14950638938556</v>
+        <v>1.147572565197567</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6137270240014013</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.009256164900581</v>
+        <v>-4.014090725370565</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.16227929575119</v>
+        <v>1.160345471563196</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6521106865595525</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.832139834865415</v>
+        <v>-3.836974395335399</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.229854856610558</v>
+        <v>1.227921032422564</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6521106865595525</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.877232079698961</v>
+        <v>-3.882066640168945</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.212501350439053</v>
+        <v>1.210567526251059</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5902146433901627</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.697856658460193</v>
+        <v>-3.702691218930177</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.278038494240974</v>
+        <v>1.276104670052981</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7469914015608814</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.742870871980799</v>
+        <v>-3.747705432450783</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.240840264164321</v>
+        <v>1.238906439976328</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7166425062462768</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.009875382253234</v>
+        <v>-4.014709942723218</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.139730022394293</v>
+        <v>1.137796198206299</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5222794682033283</v>
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.111073163690407</v>
+        <v>-4.071950817362448</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.098454831715925</v>
+        <v>1.114103770247109</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.5328683888640631</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.015562914300641</v>
+        <v>3.062961554824274</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.104562197076095</v>
+        <v>-4.065439850748136</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098659179915967</v>
+        <v>1.114308118447151</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.5328683888640631</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.013162875854958</v>
+        <v>3.06056151637859</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.085524069368797</v>
+        <v>-4.046401723040838</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102799150207131</v>
+        <v>1.118448088738315</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.4746847775328685</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.974777428264486</v>
+        <v>3.022176068788119</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.138039871643618</v>
+        <v>-4.098917525315659</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201087230931393</v>
+        <v>1.216736169462577</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.4746847775328685</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.094071829898676</v>
+        <v>3.141470470422309</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.151906632977536</v>
+        <v>-4.112784286649577</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.19637385538396</v>
+        <v>1.212022793915143</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.4368268607990456</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.072190408844516</v>
+        <v>3.119589049368149</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.107102461437606</v>
+        <v>-4.067980115109647</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.220304054396858</v>
+        <v>1.235952992928041</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.4368268607990456</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.078198939241442</v>
+        <v>3.125597579765075</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.959359491202604</v>
+        <v>-3.920237144874644</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.177351463768058</v>
+        <v>1.193000402299242</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.6046342180339288</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.076833574859572</v>
+        <v>3.124232215383204</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.043180712477302</v>
+        <v>-4.004058366149343</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14661659678966</v>
+        <v>1.162265535320843</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.6046342180339288</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.079627196391053</v>
+        <v>3.127025836914685</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.037028006424517</v>
+        <v>-3.997905660096558</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.149740027602432</v>
+        <v>1.165388966133615</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.531789189880659</v>
+        <v>0.6107869240867131</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.083981168414382</v>
+        <v>3.131379808938014</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.053837304575019</v>
+        <v>-4.01471495824706</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.142096785082341</v>
+        <v>1.157745723613525</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5149798917301573</v>
+        <v>0.5939776259362115</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.072976066264191</v>
+        <v>3.120374706787823</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.991539305798897</v>
+        <v>-3.952416959470938</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.233351538389611</v>
+        <v>1.249000476920795</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5602741560045994</v>
+        <v>0.6392718902106536</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.166488178625677</v>
+        <v>3.213886819149309</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.789749108133739</v>
+        <v>-3.75062676180578</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.116359619169801</v>
+        <v>1.132008557700985</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7582923481737538</v>
+        <v>0.837290082379808</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.087591095641296</v>
+        <v>3.134989736164929</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.840635820819934</v>
+        <v>-3.801513474491975</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.166295166417498</v>
+        <v>1.181944104948682</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7074056354875593</v>
+        <v>0.7864033696936135</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.127349300351755</v>
+        <v>3.174747940875387</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.754025078170127</v>
+        <v>-3.714902731842168</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.215567199593465</v>
+        <v>1.231216138124648</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7860313666927176</v>
+        <v>0.8650291008987717</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.189152475190894</v>
+        <v>3.236551115714526</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.814234376175411</v>
+        <v>-3.775112029847452</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.190019461216023</v>
+        <v>1.205668399747206</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.725822068687433</v>
+        <v>0.8048198028934872</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.151562877212394</v>
+        <v>3.198961517736027</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.737812329743484</v>
+        <v>-3.698689983415525</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.219079897828722</v>
+        <v>1.234728836359906</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.725822068687433</v>
+        <v>0.8048198028934872</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.150054495252323</v>
+        <v>3.197453135775956</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.693439198104916</v>
+        <v>-3.654316851776957</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.236692017919586</v>
+        <v>1.252340956450769</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.8491929345320558</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.1765412416709</v>
+        <v>3.223939882194533</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.715919548963801</v>
+        <v>-3.676797202635842</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.222093671714622</v>
+        <v>1.237742610245806</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.8491929345320558</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.170935035809491</v>
+        <v>3.218333676333124</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.668263818402745</v>
+        <v>-3.629141472074786</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.247537720966849</v>
+        <v>1.263186659498033</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8178509308870573</v>
+        <v>0.8968486650931115</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.205910231173929</v>
+        <v>3.253308871697562</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.567745659903991</v>
+        <v>-3.528623313576031</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.292637357741076</v>
+        <v>1.308286296272259</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9183690893858119</v>
+        <v>0.997366823591866</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.271113499647907</v>
+        <v>3.318512140171539</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.551840330471638</v>
+        <v>-3.512717984143679</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.285754161989889</v>
+        <v>1.301403100521073</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8392564286765729</v>
+        <v>0.9182541628826271</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.210400575698236</v>
+        <v>3.257799216221868</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.50700192886324</v>
+        <v>-3.467879582535281</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.307787225243877</v>
+        <v>1.32343616377506</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8437998616214424</v>
+        <v>0.9227975958274965</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.217224338075786</v>
+        <v>3.264622978599419</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.526500385105248</v>
+        <v>-3.487378038777289</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.304148782378152</v>
+        <v>1.319797720909335</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7957152203415381</v>
+        <v>0.8747129545475922</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.192534492938921</v>
+        <v>3.239933133462554</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.482297548019348</v>
+        <v>-3.443175201691389</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.327709519740349</v>
+        <v>1.343358458271533</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8399180574274385</v>
+        <v>0.9189157916334927</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.224935797718299</v>
+        <v>3.272334438241931</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.489857213856395</v>
+        <v>-3.450734867528436</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.323095653874778</v>
+        <v>1.338744592405961</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.973719195643312</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.256227840593438</v>
+        <v>3.30362648111707</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.331565796317122</v>
+        <v>-3.292443449989163</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.437659986073526</v>
+        <v>1.45330892460471</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.973719195643312</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.307475605776477</v>
+        <v>3.35487424630011</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.123923792682646</v>
+        <v>-3.084801446354687</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51915749212157</v>
+        <v>1.534806430652754</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.102363465071734</v>
+        <v>1.181361199277788</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.430501512551416</v>
+        <v>3.477900153075049</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.072891699960118</v>
+        <v>-3.033769353632159</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.534518557448851</v>
+        <v>1.550167495980035</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.153395557794262</v>
+        <v>1.232393292000316</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.456068996423203</v>
+        <v>3.503467636946835</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.007667518832912</v>
+        <v>-2.968545172504953</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.577795633992438</v>
+        <v>1.593444572523622</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.218619738921468</v>
+        <v>1.297617473127522</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.512390909192232</v>
+        <v>3.559789549715864</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.970240498761779</v>
+        <v>-2.931118152433819</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.588727414320172</v>
+        <v>1.604376352851356</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.223871276950649</v>
+        <v>1.302869011156703</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.511502804309021</v>
+        <v>3.558901444832653</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.990352154796487</v>
+        <v>-2.951229808468528</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.581939544237529</v>
+        <v>1.597588482768713</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.234898621948069</v>
+        <v>1.313896356154123</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.519376003638713</v>
+        <v>3.566774644162345</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961938891696603</v>
+        <v>-2.922816545368644</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.753862620498693</v>
+        <v>1.769511559029877</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.17592305920164</v>
+        <v>1.254920793407694</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644548437012066</v>
+        <v>3.691947077535699</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.887156630671591</v>
+        <v>-2.848034284343631</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.903888434126516</v>
+        <v>1.919537372657699</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.250705320226652</v>
+        <v>1.329703054432706</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809530702844891</v>
+        <v>3.856929343368523</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.861072546407783</v>
+        <v>-2.821950200079824</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.906030043845898</v>
+        <v>1.921678982377081</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.250705320226652</v>
+        <v>1.329703054432706</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.80123867885875</v>
+        <v>3.848637319382382</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.773194633298662</v>
+        <v>-2.734072286970703</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.939374404673326</v>
+        <v>1.955023343204509</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.366630962650004</v>
+        <v>1.445628696856057</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.86898725989654</v>
+        <v>3.916385900420172</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.764302171905379</v>
+        <v>-2.72517982557742</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.96048579495743</v>
+        <v>1.976134733488614</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.366630962650004</v>
+        <v>1.445628696856057</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886541665623331</v>
+        <v>3.933940306146964</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.932778288875256</v>
+        <v>-2.893655942547297</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884950395574063</v>
+        <v>1.900599334105247</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.338683126933423</v>
+        <v>1.417680861139477</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.861628011597967</v>
+        <v>3.909026652121599</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.486522096245817</v>
+        <v>-2.447399749917857</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.044722569813701</v>
+        <v>2.060371508344884</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.24396445726379</v>
+        <v>1.322962191469844</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.786066506984049</v>
+        <v>3.833465147507682</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.463800992562664</v>
+        <v>-2.424678646234705</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.044475033783867</v>
+        <v>2.06012397231505</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.24396445726379</v>
+        <v>1.322962191469844</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.776730529480953</v>
+        <v>3.824129170004586</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.593002805856707</v>
+        <v>-2.553880459528747</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.151700434317418</v>
+        <v>2.167349372848602</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.114762643969748</v>
+        <v>1.193760378175802</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.858115567355697</v>
+        <v>3.90551420787933</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.618877204330732</v>
+        <v>-2.579754858002773</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.178428497421455</v>
+        <v>2.194077435952638</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.159674252681489</v>
+        <v>1.238671986887543</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.922140355076388</v>
+        <v>3.969538995600021</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.611822514115559</v>
+        <v>-2.5727001677876</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177925729497069</v>
+        <v>2.193574668028253</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.166728942896663</v>
+        <v>1.245726677102717</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.923048525195038</v>
+        <v>3.97044716571867</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.584871289789071</v>
+        <v>-2.545748943461112</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.198712372872406</v>
+        <v>2.21436131140359</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.181609288924382</v>
+        <v>1.260607023130436</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.941982886456411</v>
+        <v>3.989381526980043</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.720824297845387</v>
+        <v>-2.681701951517428</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.328434301794839</v>
+        <v>2.344083240326023</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.181609288924382</v>
+        <v>1.260607023130436</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.126086018601371</v>
+        <v>4.173484659125003</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.743232415650259</v>
+        <v>-2.7041100693223</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.311587749575883</v>
+        <v>2.327236688107067</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.181609288924382</v>
+        <v>1.260607023130436</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.118202713504364</v>
+        <v>4.165601354027996</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.771456651227859</v>
+        <v>-2.7323343048999</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.302352054894481</v>
+        <v>2.318000993425665</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.19958604137569</v>
+        <v>1.278583775581744</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.131042764524786</v>
+        <v>4.178441405048419</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.780897577116389</v>
+        <v>-2.74177523078843</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.354829402260916</v>
+        <v>2.3704783407921</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.322013158919082</v>
+        <v>1.401010893125136</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.260752752772668</v>
+        <v>4.308151393296301</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.794048838124072</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.352459992403144</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.348737285789495</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.279678323440217</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-2.870378815724977</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.320039814256557</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.348737285789495</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.277790136333993</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.072632536049331</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.233958555729678</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.146483565465141</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.151258133742243</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.234200961576586</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.167765195728928</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>1.019700641667262</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>4.073622389673667</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.366502253674139</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.127918085755826</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>1.019700641667262</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>4.086695796539586</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.552370564513369</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>2.045575958203074</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.8611350483473141</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.983561637330557</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.580271351622842</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>2.032939684486286</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.8265381242043793</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.961327523971798</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.702797454325736</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.980693687382328</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.7040120215014855</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.88457630632726</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-3.933311950511325</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.955193848498596</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.4734975253158967</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.812973568206411</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.190032768506148</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>1.992817240302514</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3650829511720819</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.888236542721969</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.344019186282289</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>2.000202942337697</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3650829511720819</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.957216811867609</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.293497282454623</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>2.006462905988884</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3650829511720819</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.94326801398773</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.545972436462347</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.917343333441209</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3650829511720819</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.955138503043144</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.838868192941759</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.801395565368387</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3650829511720819</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.956349037562088</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-5.025532321076567</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.730851656341786</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.338343980347522</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.944427397294673</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.171553007990529</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.66752123431239</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.329260888553665</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.934055394954548</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.263267017100114</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.7930396873676</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.329260888553665</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.096259451653593</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.387107305649026</v>
+        <v>-5.347984959321067</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.73835020991185</v>
+        <v>1.753999148443033</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1651471254195646</v>
+        <v>0.2441448596256187</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.992637831736946</v>
+        <v>4.040036472260579</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.46904212391791</v>
+        <v>-5.429919777589951</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.715805700172787</v>
+        <v>1.731454638703971</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1552123798324844</v>
+        <v>0.2342101140385385</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.99690640195319</v>
+        <v>4.044305042476822</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.571018246166317</v>
+        <v>-5.531895899838358</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.683940889729327</v>
+        <v>1.69958982826051</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.05323625758407685</v>
+        <v>0.1322339917901309</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.944646367060048</v>
+        <v>3.99204500758368</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.461011962689096</v>
+        <v>-5.421889616361137</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.720096290364391</v>
+        <v>1.735745228895575</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.07644082950135206</v>
+        <v>0.1554385637074061</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.950721997454588</v>
+        <v>3.998120637978221</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.31795238694817</v>
+        <v>-5.27883004062021</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.781570131382736</v>
+        <v>1.797219069913919</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.08445425609133134</v>
+        <v>0.1634519902973854</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.95978006413055</v>
+        <v>4.007178704654182</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.016505661476332</v>
+        <v>-4.977383315148373</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.909409704454007</v>
+        <v>1.92505864298519</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.4648987157692226</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.147908982296189</v>
+        <v>4.19530762281982</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.041095905711516</v>
+        <v>-5.001973559383557</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.900544784512644</v>
+        <v>1.916193723043827</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.4648987157692226</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.148880160048899</v>
+        <v>4.196278800572531</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.990057529704996</v>
+        <v>-4.950935183377037</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.921803039295007</v>
+        <v>1.93745197782619</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.4648987157692226</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.149723064428654</v>
+        <v>4.197121704952286</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.948918234838365</v>
+        <v>-4.909795888510406</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.957296856115804</v>
+        <v>1.972945794646988</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4270402764297994</v>
+        <v>0.5060380106358535</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.193444740222778</v>
+        <v>4.24084338074641</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.852283322819725</v>
+        <v>-4.813160976491766</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.812134817047195</v>
+        <v>1.827783755578379</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5236751884484394</v>
+        <v>0.6026729226544935</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.067609683557897</v>
+        <v>4.115008324081528</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.982864057350567</v>
+        <v>-4.943741711022608</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.763404567308822</v>
+        <v>1.779053505840006</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3930944539175969</v>
+        <v>0.4720921881236509</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.992763286913354</v>
+        <v>4.040161927436987</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.818367723159605</v>
+        <v>-4.779245376831646</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.813629920061289</v>
+        <v>1.829278858592473</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3930944539175969</v>
+        <v>0.4720921881236509</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.977190105989437</v>
+        <v>4.02458874651307</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.845737655844037</v>
+        <v>-4.806615309516078</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.801869657423946</v>
+        <v>1.81751859595513</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3930944539175969</v>
+        <v>0.4720921881236509</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.976377816425867</v>
+        <v>4.023776456949499</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.856122850733927</v>
+        <v>-4.817000504405968</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.807584358593063</v>
+        <v>1.823233297124246</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3827092590277076</v>
+        <v>0.4617069932337616</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.980015478617005</v>
+        <v>4.027414119140638</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.874711009456152</v>
+        <v>-4.835588663128193</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.870986100880598</v>
+        <v>1.886635039411781</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3641211003054822</v>
+        <v>0.4431188345115363</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.039699589160096</v>
+        <v>4.087098229683728</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.875009556152188</v>
+        <v>-4.835887209824229</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.867735693020482</v>
+        <v>1.883384631551666</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3641211003054822</v>
+        <v>0.4431188345115363</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.036568599978394</v>
+        <v>4.083967240502027</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.77418642246176</v>
+        <v>-4.735064076133801</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.912595841436044</v>
+        <v>1.928244779967228</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3765853157898361</v>
+        <v>0.4555830499958901</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.048578024208398</v>
+        <v>4.09597666473203</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.583405061709353</v>
+        <v>-4.544282715381394</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.98903763921555</v>
+        <v>2.004686577746734</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5673666765422434</v>
+        <v>0.6463644107482975</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.163176094138385</v>
+        <v>4.210574734662018</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.564888207667533</v>
+        <v>-4.525765861339574</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.976281226569875</v>
+        <v>1.991930165101059</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5802968059674516</v>
+        <v>0.6592945401735057</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.150771017531107</v>
+        <v>4.19816965805474</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.539695023166215</v>
+        <v>-4.500572676838256</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.021325436982461</v>
+        <v>2.036974375513644</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6054899904687699</v>
+        <v>0.6844877246748241</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.200853864843956</v>
+        <v>4.248252505367589</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.527640896253252</v>
+        <v>-4.488518549925293</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.019833655649084</v>
+        <v>2.035482594180268</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6175441173817328</v>
+        <v>0.6965418515877869</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.201772908893171</v>
+        <v>4.249171549416804</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.53426414294361</v>
+        <v>-4.495141796615651</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.019064987157076</v>
+        <v>2.03471392568826</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6109208706913745</v>
+        <v>0.6899186048974286</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.199679591063092</v>
+        <v>4.247078231586725</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.431383553415017</v>
+        <v>-4.392261207087058</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.073068248846396</v>
+        <v>2.08871718737758</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7927991944260215</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.27425897065813</v>
+        <v>4.321657611181763</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.454825592595104</v>
+        <v>-4.415703246267145</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.083894103347955</v>
+        <v>2.099543041879139</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7927991944260215</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.294461640831725</v>
+        <v>4.341860281355357</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.472898100886716</v>
+        <v>-4.433775754558757</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.076665100031311</v>
+        <v>2.092314038562495</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7927991944260215</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.294461640831725</v>
+        <v>4.341860281355357</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.704071894763348</v>
+        <v>-4.664949548435389</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.944447496074125</v>
+        <v>1.960096434605308</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7138014602199674</v>
+        <v>0.7927991944260215</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.254713554425192</v>
+        <v>4.302112194948824</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.672785874222892</v>
+        <v>-4.633663527894933</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.963984523287247</v>
+        <v>1.97963346181843</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7450874807604227</v>
+        <v>0.8240852149664769</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.280507785746405</v>
+        <v>4.327906426270038</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.519760482109608</v>
+        <v>-4.480638135781649</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.124365679705464</v>
+        <v>2.140014618236648</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8981128728737069</v>
+        <v>0.9771106070797611</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.471494020587279</v>
+        <v>4.518892661110912</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.548067795982878</v>
+        <v>-4.508945449654919</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.300508979064449</v>
+        <v>2.316157917595633</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8981128728737069</v>
+        <v>0.9771106070797611</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.658960245495572</v>
+        <v>4.706358886019204</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.714661021096401</v>
+        <v>-4.675538674768442</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.203274640373122</v>
+        <v>2.218923578904306</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7315196477601844</v>
+        <v>0.8105173819662386</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.528407261781541</v>
+        <v>4.575805902305174</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.541596641714101</v>
+        <v>-4.502474295386142</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.27617679478776</v>
+        <v>2.291825733318944</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7315196477601844</v>
+        <v>0.8105173819662386</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.532083664443259</v>
+        <v>4.579482304966891</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.512350661258404</v>
+        <v>-4.473228314930445</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.285493242093534</v>
+        <v>2.301142180624717</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7315196477601844</v>
+        <v>0.8105173819662386</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.529701719566754</v>
+        <v>4.577100360090387</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.619276209136255</v>
+        <v>-4.580153862808296</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.240016262100029</v>
+        <v>2.255665200631212</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6245940998823331</v>
+        <v>0.7035918340883872</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.462839629997678</v>
+        <v>4.51023827052131</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.764294767643504</v>
+        <v>-4.725172421315545</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.183437640840364</v>
+        <v>2.199086579371547</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4795755413750845</v>
+        <v>0.5585732755811387</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.377257297036563</v>
+        <v>4.424655937560195</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.754832812719731</v>
+        <v>-4.843514187100262</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.287153662067626</v>
+        <v>2.251681112315413</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5400821923113521</v>
+        <v>0.5692593141440287</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.513492526856076</v>
+        <v>4.530998799955682</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.880701500692747</v>
+        <v>3.8795870343688</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.385400062628727</v>
+        <v>4.367586854436059</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.754832812719731</v>
+        <v>-4.843514187100262</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.287153662067626</v>
+        <v>2.251681112315413</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5400821923113521</v>
+        <v>0.5692593141440287</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.378463859615095</v>
+        <v>4.360650651422427</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.3%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>123.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>430.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-645.9%</t>
+          <t>-639.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.1%</t>
+          <t>-148.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-333.7%</t>
+          <t>-332.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.1%</t>
+          <t>-164.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.161720411333774</v>
+        <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.314417281679189</v>
+        <v>1.316351105867182</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.041547327969275</v>
+        <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.36363235946529</v>
+        <v>1.365566183653284</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.906293966639298</v>
+        <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.427821806558721</v>
+        <v>1.429755630746715</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.966168793996991</v>
+        <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.38990936701707</v>
+        <v>1.391843191205064</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.846348563086153</v>
+        <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.453126628615613</v>
+        <v>1.455060452803607</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.848818269547959</v>
+        <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359782945353333</v>
+        <v>1.361716769541326</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.917188455871969</v>
+        <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.25169673230903</v>
+        <v>1.253630556497024</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.930976508719016</v>
+        <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.236618219802103</v>
+        <v>1.238552043990096</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.986496584611605</v>
+        <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.351441026137269</v>
+        <v>1.353374850325263</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.811022324819136</v>
+        <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.426197962046045</v>
+        <v>1.428131786234038</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.803097950234222</v>
+        <v>-3.798263389764238</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.405109740641217</v>
+        <v>1.407043564829211</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.796819747664373</v>
+        <v>-3.791985187194389</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.336159335070607</v>
+        <v>1.3380931592586</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8176560300468725</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.73696712846065</v>
+        <v>-3.732132567990666</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.370272769184228</v>
+        <v>1.372206593372222</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8176560300468725</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.650723665434272</v>
+        <v>-3.645889104964288</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.39971642496864</v>
+        <v>1.401650249156633</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8176560300468725</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.696030484833252</v>
+        <v>-3.691195924363268</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.373369472653573</v>
+        <v>1.375303296841567</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7768458670376417</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.725063589535554</v>
+        <v>-3.72022902906557</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.362308103805754</v>
+        <v>1.364241927993748</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7768458670376417</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.632253108084694</v>
+        <v>-3.62741854761471</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.328704988277464</v>
+        <v>1.330638812465457</v>
       </c>
       <c r="F1946" t="n">
         <v>0.869656348488501</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.676642577414122</v>
+        <v>-3.671808016944138</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.312822676470293</v>
+        <v>1.314756500658287</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8252668791590734</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.793184182519465</v>
+        <v>-3.788349622049481</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.261281742939879</v>
+        <v>1.263215567127873</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7087252740537306</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.833108277102037</v>
+        <v>-3.828273716632053</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.250803400937518</v>
+        <v>1.252737225125511</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7087252740537306</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.86088867500339</v>
+        <v>-3.856054114533406</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.251188443545515</v>
+        <v>1.253122267733509</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6809448761523775</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.979269347733528</v>
+        <v>-3.974434787263544</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.042191894454113</v>
+        <v>1.044125718642107</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6137270240014013</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.087883426176859</v>
+        <v>-4.083048865706875</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.118895923795987</v>
+        <v>1.12082974798398</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6137270240014013</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.052474387928716</v>
+        <v>-4.047639827458732</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.147572565197567</v>
+        <v>1.14950638938556</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6137270240014013</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.014090725370565</v>
+        <v>-4.009256164900581</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.160345471563196</v>
+        <v>1.16227929575119</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6521106865595525</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.836974395335399</v>
+        <v>-3.832139834865415</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.227921032422564</v>
+        <v>1.229854856610558</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6521106865595525</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.882066640168945</v>
+        <v>-3.877232079698961</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.210567526251059</v>
+        <v>1.212501350439053</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5902146433901627</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.702691218930177</v>
+        <v>-3.697856658460193</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.276104670052981</v>
+        <v>1.278038494240974</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7469914015608814</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.747705432450783</v>
+        <v>-3.742870871980799</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.238906439976328</v>
+        <v>1.240840264164321</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7166425062462768</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.014709942723218</v>
+        <v>-4.009875382253234</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.137796198206299</v>
+        <v>1.139730022394293</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5222794682033283</v>
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.071950817362448</v>
+        <v>-4.111073163690407</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.114103770247109</v>
+        <v>1.098454831715925</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5328683888640631</v>
+        <v>0.4538706546580091</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.062961554824274</v>
+        <v>3.015562914300641</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.065439850748136</v>
+        <v>-4.104562197076095</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.114308118447151</v>
+        <v>1.098659179915967</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5328683888640631</v>
+        <v>0.4538706546580091</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.06056151637859</v>
+        <v>3.013162875854958</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.046401723040838</v>
+        <v>-4.085524069368797</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.118448088738315</v>
+        <v>1.102799150207131</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4746847775328685</v>
+        <v>0.3956870433268145</v>
       </c>
       <c r="G1962" t="n">
-        <v>3.022176068788119</v>
+        <v>2.974777428264486</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.098917525315659</v>
+        <v>-4.138039871643618</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.216736169462577</v>
+        <v>1.201087230931393</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4746847775328685</v>
+        <v>0.3956870433268145</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.141470470422309</v>
+        <v>3.094071829898676</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.112784286649577</v>
+        <v>-4.151906632977536</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.212022793915143</v>
+        <v>1.19637385538396</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4368268607990456</v>
+        <v>0.3578291265929916</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.119589049368149</v>
+        <v>3.072190408844516</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.067980115109647</v>
+        <v>-4.107102461437606</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.235952992928041</v>
+        <v>1.220304054396858</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4368268607990456</v>
+        <v>0.3578291265929916</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.125597579765075</v>
+        <v>3.078198939241442</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.920237144874644</v>
+        <v>-3.959359491202604</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.193000402299242</v>
+        <v>1.177351463768058</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6046342180339288</v>
+        <v>0.5256364838278748</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.124232215383204</v>
+        <v>3.076833574859572</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.004058366149343</v>
+        <v>-4.043180712477302</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.162265535320843</v>
+        <v>1.14661659678966</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6046342180339288</v>
+        <v>0.5256364838278748</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.127025836914685</v>
+        <v>3.079627196391053</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.997905660096558</v>
+        <v>-4.037028006424517</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.165388966133615</v>
+        <v>1.149740027602432</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6107869240867131</v>
+        <v>0.531789189880659</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.131379808938014</v>
+        <v>3.083981168414382</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.01471495824706</v>
+        <v>-4.053837304575019</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.157745723613525</v>
+        <v>1.142096785082341</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5939776259362115</v>
+        <v>0.5149798917301573</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.120374706787823</v>
+        <v>3.072976066264191</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.952416959470938</v>
+        <v>-3.991539305798897</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.249000476920795</v>
+        <v>1.233351538389611</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6392718902106536</v>
+        <v>0.5602741560045994</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.213886819149309</v>
+        <v>3.166488178625677</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.75062676180578</v>
+        <v>-3.789749108133739</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.132008557700985</v>
+        <v>1.116359619169801</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.837290082379808</v>
+        <v>0.7582923481737538</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.134989736164929</v>
+        <v>3.087591095641296</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.801513474491975</v>
+        <v>-3.840635820819934</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.181944104948682</v>
+        <v>1.166295166417498</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7864033696936135</v>
+        <v>0.7074056354875593</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.174747940875387</v>
+        <v>3.127349300351755</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.714902731842168</v>
+        <v>-3.754025078170127</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.231216138124648</v>
+        <v>1.215567199593465</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8650291008987717</v>
+        <v>0.7860313666927176</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.236551115714526</v>
+        <v>3.189152475190894</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.775112029847452</v>
+        <v>-3.709877113012892</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.205668399747206</v>
+        <v>1.231762366481031</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8048198028934872</v>
+        <v>0.8301793318499526</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.198961517736027</v>
+        <v>3.214177235109906</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.698689983415525</v>
+        <v>-3.633455066580965</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.234728836359906</v>
+        <v>1.26082280309373</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8048198028934872</v>
+        <v>0.8301793318499526</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.197453135775956</v>
+        <v>3.212668853149835</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.654316851776957</v>
+        <v>-3.589081934942396</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.252340956450769</v>
+        <v>1.278434923184594</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8491929345320558</v>
+        <v>0.8745524634885212</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.223939882194533</v>
+        <v>3.239155599568412</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.676797202635842</v>
+        <v>-3.611562285801281</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.237742610245806</v>
+        <v>1.26383657697963</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8491929345320558</v>
+        <v>0.8745524634885212</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.218333676333124</v>
+        <v>3.233549393707003</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.629141472074786</v>
+        <v>-3.563906555240226</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.263186659498033</v>
+        <v>1.289280626231857</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8968486650931115</v>
+        <v>0.9222081940495769</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.253308871697562</v>
+        <v>3.268524589071441</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.528623313576031</v>
+        <v>-3.463388396741471</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.308286296272259</v>
+        <v>1.334380263006084</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.997366823591866</v>
+        <v>1.022726352548331</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.318512140171539</v>
+        <v>3.333727857545418</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.512717984143679</v>
+        <v>-3.447483067309118</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.301403100521073</v>
+        <v>1.327497067254897</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9182541628826271</v>
+        <v>0.9436136918390925</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.257799216221868</v>
+        <v>3.273014933595747</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.467879582535281</v>
+        <v>-3.40264466570072</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.32343616377506</v>
+        <v>1.349530130508885</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9227975958274965</v>
+        <v>0.948157124783962</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.264622978599419</v>
+        <v>3.279838695973297</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.487378038777289</v>
+        <v>-3.422143121942729</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.319797720909335</v>
+        <v>1.345891687643159</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8747129545475922</v>
+        <v>0.9000724835040577</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.239933133462554</v>
+        <v>3.255148850836433</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.443175201691389</v>
+        <v>-3.377940284856828</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.343358458271533</v>
+        <v>1.369452425005357</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9189157916334927</v>
+        <v>0.9442753205899581</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.272334438241931</v>
+        <v>3.28755015561581</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.450734867528436</v>
+        <v>-3.385499950693875</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.338744592405961</v>
+        <v>1.364838559139786</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.973719195643312</v>
+        <v>0.9990787245997774</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.30362648111707</v>
+        <v>3.31884219849095</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.292443449989163</v>
+        <v>-3.227208533154603</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.45330892460471</v>
+        <v>1.479402891338534</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.973719195643312</v>
+        <v>0.9990787245997774</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.35487424630011</v>
+        <v>3.370089963673989</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.084801446354687</v>
+        <v>-3.019566529520127</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.534806430652754</v>
+        <v>1.560900397386578</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.181361199277788</v>
+        <v>1.206720728234254</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.477900153075049</v>
+        <v>3.493115870448928</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.033769353632159</v>
+        <v>-2.968534436797599</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.550167495980035</v>
+        <v>1.576261462713859</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.232393292000316</v>
+        <v>1.257752820956782</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.503467636946835</v>
+        <v>3.518683354320715</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.968545172504953</v>
+        <v>-2.903310255670393</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.593444572523622</v>
+        <v>1.619538539257446</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.297617473127522</v>
+        <v>1.322977002083987</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.559789549715864</v>
+        <v>3.575005267089743</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.931118152433819</v>
+        <v>-2.865883235599259</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.604376352851356</v>
+        <v>1.63047031958518</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.302869011156703</v>
+        <v>1.328228540113169</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.558901444832653</v>
+        <v>3.574117162206532</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.951229808468528</v>
+        <v>-2.885994891633967</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.597588482768713</v>
+        <v>1.623682449502537</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.313896356154123</v>
+        <v>1.339255885110588</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.566774644162345</v>
+        <v>3.581990361536224</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.922816545368644</v>
+        <v>-2.857581628534084</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.769511559029877</v>
+        <v>1.795605525763701</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.254920793407694</v>
+        <v>1.280280322364159</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.691947077535699</v>
+        <v>3.707162794909578</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.848034284343631</v>
+        <v>-2.782799367509071</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.919537372657699</v>
+        <v>1.945631339391523</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.329703054432706</v>
+        <v>1.355062583389172</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.856929343368523</v>
+        <v>3.872145060742403</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.821950200079824</v>
+        <v>-2.756715283245263</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.921678982377081</v>
+        <v>1.947772949110906</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.329703054432706</v>
+        <v>1.355062583389172</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.848637319382382</v>
+        <v>3.863853036756262</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.734072286970703</v>
+        <v>-2.668837370136143</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.955023343204509</v>
+        <v>1.981117309938333</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.445628696856057</v>
+        <v>1.470988225812523</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.916385900420172</v>
+        <v>3.931601617794052</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.72517982557742</v>
+        <v>-2.659944908742859</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.976134733488614</v>
+        <v>2.002228700222438</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.445628696856057</v>
+        <v>1.470988225812523</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.933940306146964</v>
+        <v>3.949156023520843</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.893655942547297</v>
+        <v>-2.828421025712737</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.900599334105247</v>
+        <v>1.926693300839071</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.417680861139477</v>
+        <v>1.443040390095942</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.909026652121599</v>
+        <v>3.924242369495478</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.447399749917857</v>
+        <v>-2.382164833083297</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.060371508344884</v>
+        <v>2.086465475078709</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.322962191469844</v>
+        <v>1.34832172042631</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.833465147507682</v>
+        <v>3.848680864881561</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.424678646234705</v>
+        <v>-2.359443729400144</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.06012397231505</v>
+        <v>2.086217939048874</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.322962191469844</v>
+        <v>1.34832172042631</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.824129170004586</v>
+        <v>3.839344887378465</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.553880459528747</v>
+        <v>-2.488645542694187</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.167349372848602</v>
+        <v>2.193443339582426</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.193760378175802</v>
+        <v>1.219119907132267</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.90551420787933</v>
+        <v>3.920729925253209</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.579754858002773</v>
+        <v>-2.514519941168213</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.194077435952638</v>
+        <v>2.220171402686463</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.238671986887543</v>
+        <v>1.264031515844009</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.969538995600021</v>
+        <v>3.9847547129739</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.5727001677876</v>
+        <v>-2.507465250953039</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.193574668028253</v>
+        <v>2.219668634762077</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.245726677102717</v>
+        <v>1.271086206059182</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.97044716571867</v>
+        <v>3.98566288309255</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.545748943461112</v>
+        <v>-2.480514026626551</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.21436131140359</v>
+        <v>2.240455278137414</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.260607023130436</v>
+        <v>1.285966552086901</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.989381526980043</v>
+        <v>4.004597244353922</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.681701951517428</v>
+        <v>-2.616467034682867</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.344083240326023</v>
+        <v>2.370177207059847</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.260607023130436</v>
+        <v>1.285966552086901</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.173484659125003</v>
+        <v>4.188700376498883</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.7041100693223</v>
+        <v>-2.638875152487739</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.327236688107067</v>
+        <v>2.353330654840891</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.260607023130436</v>
+        <v>1.285966552086901</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.165601354027996</v>
+        <v>4.180817071401876</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.7323343048999</v>
+        <v>-2.66709938806534</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.318000993425665</v>
+        <v>2.344094960159489</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.278583775581744</v>
+        <v>1.30394330453821</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.178441405048419</v>
+        <v>4.193657122422298</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.74177523078843</v>
+        <v>-2.67654031395387</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.3704783407921</v>
+        <v>2.396572307525924</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.401010893125136</v>
+        <v>1.426370422081602</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.308151393296301</v>
+        <v>4.32336711067018</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.794048838124072</v>
+        <v>-2.728813921289511</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.352459992403144</v>
+        <v>2.378553959136968</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.348737285789495</v>
+        <v>1.37409681474596</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.279678323440217</v>
+        <v>4.294894040814096</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.870378815724977</v>
+        <v>-2.805143898890417</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.320039814256557</v>
+        <v>2.346133780990381</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.348737285789495</v>
+        <v>1.37409681474596</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.277790136333993</v>
+        <v>4.293005853707871</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.072632536049331</v>
+        <v>-3.00739761921477</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.233958555729678</v>
+        <v>2.260052522463502</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.146483565465141</v>
+        <v>1.171843094421607</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.151258133742243</v>
+        <v>4.166473851116121</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.234200961576586</v>
+        <v>-3.168966044742025</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.167765195728928</v>
+        <v>2.193859162462752</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.019700641667262</v>
+        <v>1.045060170623727</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.073622389673667</v>
+        <v>4.088838107047547</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.366502253674139</v>
+        <v>-3.301267336839579</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.127918085755826</v>
+        <v>2.15401205248965</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.019700641667262</v>
+        <v>1.045060170623727</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.086695796539586</v>
+        <v>4.101911513913465</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.552370564513369</v>
+        <v>-3.487135647678809</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.045575958203074</v>
+        <v>2.071669924936898</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8611350483473141</v>
+        <v>0.8864945773037798</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.983561637330557</v>
+        <v>3.998777354704437</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.580271351622842</v>
+        <v>-3.515036434788282</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.032939684486286</v>
+        <v>2.05903365122011</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8265381242043793</v>
+        <v>0.851897653160845</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.961327523971798</v>
+        <v>3.976543241345677</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.702797454325736</v>
+        <v>-3.637562537491176</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.980693687382328</v>
+        <v>2.006787654116152</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7040120215014855</v>
+        <v>0.7293715504579511</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.88457630632726</v>
+        <v>3.89979202370114</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.933311950511325</v>
+        <v>-3.868077033676764</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.955193848498596</v>
+        <v>1.98128781523242</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4734975253158967</v>
+        <v>0.4988570542723624</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.812973568206411</v>
+        <v>3.828189285580291</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.190032768506148</v>
+        <v>-4.124797851671588</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.992817240302514</v>
+        <v>2.018911207036338</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3650829511720819</v>
+        <v>0.3904424801285475</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.888236542721969</v>
+        <v>3.903452260095849</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.344019186282289</v>
+        <v>-4.278784269447728</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.000202942337697</v>
+        <v>2.026296909071521</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3650829511720819</v>
+        <v>0.3904424801285475</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.957216811867609</v>
+        <v>3.972432529241488</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.293497282454623</v>
+        <v>-4.228262365620062</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.006462905988884</v>
+        <v>2.032556872722708</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3650829511720819</v>
+        <v>0.3904424801285475</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.94326801398773</v>
+        <v>3.95848373136161</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.545972436462347</v>
+        <v>-4.480737519627787</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.917343333441209</v>
+        <v>1.943437300175033</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3650829511720819</v>
+        <v>0.3904424801285475</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.955138503043144</v>
+        <v>3.970354220417024</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.838868192941759</v>
+        <v>-4.773633276107199</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.801395565368387</v>
+        <v>1.827489532102212</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3650829511720819</v>
+        <v>0.3904424801285475</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.956349037562088</v>
+        <v>3.971564754935967</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.025532321076567</v>
+        <v>-4.960297404242007</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.730851656341786</v>
+        <v>1.75694562307561</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.338343980347522</v>
+        <v>0.3637035093039876</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.944427397294673</v>
+        <v>3.959643114668553</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.171553007990529</v>
+        <v>-5.106318091155969</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.66752123431239</v>
+        <v>1.693615201046214</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.329260888553665</v>
+        <v>0.3546204175101307</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.934055394954548</v>
+        <v>3.949271112328428</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.263267017100114</v>
+        <v>-5.198032100265554</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.7930396873676</v>
+        <v>1.819133654101424</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.329260888553665</v>
+        <v>0.3546204175101307</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.096259451653593</v>
+        <v>4.111475169027472</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.347984959321067</v>
+        <v>-5.282750042486507</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.753999148443033</v>
+        <v>1.780093115176857</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2441448596256187</v>
+        <v>0.2695043885820843</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.040036472260579</v>
+        <v>4.055252189634459</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.429919777589951</v>
+        <v>-5.36468486075539</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.731454638703971</v>
+        <v>1.757548605437795</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2342101140385385</v>
+        <v>0.2595696429950041</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044305042476822</v>
+        <v>4.059520759850701</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.531895899838358</v>
+        <v>-5.466660983003798</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.69958982826051</v>
+        <v>1.725683794994335</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1322339917901309</v>
+        <v>0.1575935207465965</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.99204500758368</v>
+        <v>4.007260724957559</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.421889616361137</v>
+        <v>-5.356654699526576</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.735745228895575</v>
+        <v>1.761839195629399</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1554385637074061</v>
+        <v>0.1807980926638718</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998120637978221</v>
+        <v>4.0133363553521</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.27883004062021</v>
+        <v>-5.21359512378565</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.797219069913919</v>
+        <v>1.823313036647743</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1634519902973854</v>
+        <v>0.188811519253851</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007178704654182</v>
+        <v>4.022394422028062</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.977383315148373</v>
+        <v>-4.912148398313812</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.92505864298519</v>
+        <v>1.951152609719014</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4648987157692226</v>
+        <v>0.4902582447256882</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.19530762281982</v>
+        <v>4.2105233401937</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.001973559383557</v>
+        <v>-4.936738642548996</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.916193723043827</v>
+        <v>1.942287689777651</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4648987157692226</v>
+        <v>0.4902582447256882</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196278800572531</v>
+        <v>4.21149451794641</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.950935183377037</v>
+        <v>-4.885700266542476</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.93745197782619</v>
+        <v>1.963545944560015</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4648987157692226</v>
+        <v>0.4902582447256882</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197121704952286</v>
+        <v>4.212337422326166</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.909795888510406</v>
+        <v>-4.844560971675845</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.972945794646988</v>
+        <v>1.999039761380812</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5060380106358535</v>
+        <v>0.5313975395923191</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.24084338074641</v>
+        <v>4.256059098120289</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.813160976491766</v>
+        <v>-4.747926059657205</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.827783755578379</v>
+        <v>1.853877722312203</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6026729226544935</v>
+        <v>0.628032451610959</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.115008324081528</v>
+        <v>4.130224041455408</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.943741711022608</v>
+        <v>-4.878506794188048</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.779053505840006</v>
+        <v>1.80514747257383</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4720921881236509</v>
+        <v>0.4974517170801165</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040161927436987</v>
+        <v>4.055377644810866</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.779245376831646</v>
+        <v>-4.714010459997086</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.829278858592473</v>
+        <v>1.855372825326297</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4720921881236509</v>
+        <v>0.4974517170801165</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.02458874651307</v>
+        <v>4.039804463886949</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.806615309516078</v>
+        <v>-4.741380392681518</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.81751859595513</v>
+        <v>1.843612562688954</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4720921881236509</v>
+        <v>0.4974517170801165</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.023776456949499</v>
+        <v>4.038992174323378</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.817000504405968</v>
+        <v>-4.751765587571407</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.823233297124246</v>
+        <v>1.849327263858071</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4617069932337616</v>
+        <v>0.4870665221902272</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.027414119140638</v>
+        <v>4.042629836514517</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.835588663128193</v>
+        <v>-4.770353746293632</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.886635039411781</v>
+        <v>1.912729006145606</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4431188345115363</v>
+        <v>0.4684783634680018</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.087098229683728</v>
+        <v>4.102313947057607</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.835887209824229</v>
+        <v>-4.770652292989668</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.883384631551666</v>
+        <v>1.90947859828549</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4431188345115363</v>
+        <v>0.4684783634680018</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.083967240502027</v>
+        <v>4.099182957875906</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.735064076133801</v>
+        <v>-4.66982915929924</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.928244779967228</v>
+        <v>1.954338746701052</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4555830499958901</v>
+        <v>0.4809425789523556</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.09597666473203</v>
+        <v>4.11119238210591</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.544282715381394</v>
+        <v>-4.479047798546834</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.004686577746734</v>
+        <v>2.030780544480558</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6463644107482975</v>
+        <v>0.671723939704763</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.210574734662018</v>
+        <v>4.225790452035898</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.525765861339574</v>
+        <v>-4.460530944505013</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.991930165101059</v>
+        <v>2.018024131834883</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6592945401735057</v>
+        <v>0.6846540691299712</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.19816965805474</v>
+        <v>4.213385375428619</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.500572676838256</v>
+        <v>-4.435337760003695</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.036974375513644</v>
+        <v>2.063068342247469</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6844877246748241</v>
+        <v>0.7098472536312895</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.248252505367589</v>
+        <v>4.263468222741468</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.488518549925293</v>
+        <v>-4.423283633090732</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.035482594180268</v>
+        <v>2.061576560914092</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6965418515877869</v>
+        <v>0.7219013805442523</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.249171549416804</v>
+        <v>4.264387266790683</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.495141796615651</v>
+        <v>-4.429906879781091</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.03471392568826</v>
+        <v>2.060807892422084</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6899186048974286</v>
+        <v>0.715278133853894</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.247078231586725</v>
+        <v>4.262293948960604</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.392261207087058</v>
+        <v>-4.327026290252498</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.08871718737758</v>
+        <v>2.114811154111404</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7927991944260215</v>
+        <v>0.818158723382487</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.321657611181763</v>
+        <v>4.336873328555643</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.415703246267145</v>
+        <v>-4.350468329432585</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.099543041879139</v>
+        <v>2.125637008612963</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7927991944260215</v>
+        <v>0.818158723382487</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.341860281355357</v>
+        <v>4.357075998729237</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.433775754558757</v>
+        <v>-4.368540837724196</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.092314038562495</v>
+        <v>2.118408005296319</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7927991944260215</v>
+        <v>0.818158723382487</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.341860281355357</v>
+        <v>4.357075998729237</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.664949548435389</v>
+        <v>-4.599714631600828</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.960096434605308</v>
+        <v>1.986190401339132</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7927991944260215</v>
+        <v>0.818158723382487</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.302112194948824</v>
+        <v>4.317327912322703</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.633663527894933</v>
+        <v>-4.568428611060373</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.97963346181843</v>
+        <v>2.005727428552254</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8240852149664769</v>
+        <v>0.8494447439229423</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.327906426270038</v>
+        <v>4.343122143643916</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.480638135781649</v>
+        <v>-4.415403218947088</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.140014618236648</v>
+        <v>2.166108584970472</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9771106070797611</v>
+        <v>1.002470136036226</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.518892661110912</v>
+        <v>4.534108378484791</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.508945449654919</v>
+        <v>-4.443710532820359</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.316157917595633</v>
+        <v>2.342251884329457</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9771106070797611</v>
+        <v>1.002470136036226</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.706358886019204</v>
+        <v>4.721574603393083</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.675538674768442</v>
+        <v>-4.610303757933881</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.218923578904306</v>
+        <v>2.24501754563813</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8105173819662386</v>
+        <v>0.835876910922704</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.575805902305174</v>
+        <v>4.591021619679053</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.502474295386142</v>
+        <v>-4.437239378551581</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.291825733318944</v>
+        <v>2.317919700052768</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8105173819662386</v>
+        <v>0.835876910922704</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.579482304966891</v>
+        <v>4.59469802234077</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.473228314930445</v>
+        <v>-4.407993398095885</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.301142180624717</v>
+        <v>2.327236147358541</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8105173819662386</v>
+        <v>0.835876910922704</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.577100360090387</v>
+        <v>4.592316077464266</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.580153862808296</v>
+        <v>-4.514918945973736</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.255665200631212</v>
+        <v>2.281759167365037</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7035918340883872</v>
+        <v>0.7289513630448526</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.51023827052131</v>
+        <v>4.525453987895189</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983739</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.725172421315545</v>
+        <v>-4.659937504480984</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.199086579371547</v>
+        <v>2.225180546105371</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5585732755811387</v>
+        <v>0.5839328045376041</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.424655937560195</v>
+        <v>4.439871654934075</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969748</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.843514187100262</v>
+        <v>-4.778279270265702</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.251681112315413</v>
+        <v>2.277775079049237</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5692593141440287</v>
+        <v>0.5946188431004942</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.530998799955682</v>
+        <v>4.546214517329561</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.8795870343688</v>
+        <v>3.834926398069887</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.367586854436059</v>
+        <v>4.353985024945755</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.843514187100262</v>
+        <v>-4.778279270265702</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.251681112315413</v>
+        <v>2.277775079049237</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5692593141440287</v>
+        <v>0.5946188431004942</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.360650651422427</v>
+        <v>4.347048821932123</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.9%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>139.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>430.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.4%</t>
+          <t>-628.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.4%</t>
+          <t>-144.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-332.3%</t>
+          <t>-324.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-153.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539944</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.709877113012892</v>
+        <v>-3.814234376175411</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.231762366481031</v>
+        <v>1.190019461216023</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8301793318499526</v>
+        <v>0.725822068687433</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.214177235109906</v>
+        <v>3.151562877212394</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.633455066580965</v>
+        <v>-3.737812329743484</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.26082280309373</v>
+        <v>1.219079897828722</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8301793318499526</v>
+        <v>0.725822068687433</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.212668853149835</v>
+        <v>3.150054495252323</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.589081934942396</v>
+        <v>-3.693439198104916</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.278434923184594</v>
+        <v>1.236692017919586</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8745524634885212</v>
+        <v>0.7701952003260016</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.239155599568412</v>
+        <v>3.1765412416709</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.611562285801281</v>
+        <v>-3.715919548963801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.26383657697963</v>
+        <v>1.222093671714622</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8745524634885212</v>
+        <v>0.7701952003260016</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.233549393707003</v>
+        <v>3.170935035809491</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.563906555240226</v>
+        <v>-3.668263818402745</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.289280626231857</v>
+        <v>1.247537720966849</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9222081940495769</v>
+        <v>0.8178509308870573</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.268524589071441</v>
+        <v>3.205910231173929</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.463388396741471</v>
+        <v>-3.567745659903991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.334380263006084</v>
+        <v>1.292637357741076</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.022726352548331</v>
+        <v>0.9183690893858119</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.333727857545418</v>
+        <v>3.271113499647907</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.447483067309118</v>
+        <v>-3.551840330471638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.327497067254897</v>
+        <v>1.285754161989889</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9436136918390925</v>
+        <v>0.8392564286765729</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.273014933595747</v>
+        <v>3.210400575698236</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.40264466570072</v>
+        <v>-3.50700192886324</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.349530130508885</v>
+        <v>1.307787225243877</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.948157124783962</v>
+        <v>0.8437998616214424</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.279838695973297</v>
+        <v>3.217224338075786</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.422143121942729</v>
+        <v>-3.526500385105248</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.345891687643159</v>
+        <v>1.304148782378152</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9000724835040577</v>
+        <v>0.7957152203415381</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.255148850836433</v>
+        <v>3.192534492938921</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.377940284856828</v>
+        <v>-3.482297548019348</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.369452425005357</v>
+        <v>1.327709519740349</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9442753205899581</v>
+        <v>0.8399180574274385</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.28755015561581</v>
+        <v>3.224935797718299</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.385499950693875</v>
+        <v>-3.489857213856395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.364838559139786</v>
+        <v>1.323095653874778</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9990787245997774</v>
+        <v>0.8947214614372578</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.31884219849095</v>
+        <v>3.256227840593438</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.227208533154603</v>
+        <v>-3.331565796317122</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.479402891338534</v>
+        <v>1.437659986073526</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9990787245997774</v>
+        <v>0.8947214614372578</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.370089963673989</v>
+        <v>3.307475605776477</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.019566529520127</v>
+        <v>-3.123923792682646</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.560900397386578</v>
+        <v>1.51915749212157</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.206720728234254</v>
+        <v>1.102363465071734</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.493115870448928</v>
+        <v>3.430501512551416</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.968534436797599</v>
+        <v>-3.072891699960118</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.576261462713859</v>
+        <v>1.534518557448851</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.257752820956782</v>
+        <v>1.153395557794262</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.518683354320715</v>
+        <v>3.456068996423203</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.903310255670393</v>
+        <v>-3.007667518832912</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.619538539257446</v>
+        <v>1.577795633992438</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.322977002083987</v>
+        <v>1.218619738921468</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.575005267089743</v>
+        <v>3.512390909192232</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.865883235599259</v>
+        <v>-2.970240498761779</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.63047031958518</v>
+        <v>1.588727414320172</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.328228540113169</v>
+        <v>1.223871276950649</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.574117162206532</v>
+        <v>3.511502804309021</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.885994891633967</v>
+        <v>-2.990352154796487</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.623682449502537</v>
+        <v>1.581939544237529</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.339255885110588</v>
+        <v>1.234898621948069</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.581990361536224</v>
+        <v>3.519376003638713</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.857581628534084</v>
+        <v>-2.961938891696603</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.795605525763701</v>
+        <v>1.753862620498693</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.280280322364159</v>
+        <v>1.17592305920164</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.707162794909578</v>
+        <v>3.644548437012066</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.782799367509071</v>
+        <v>-2.887156630671591</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.945631339391523</v>
+        <v>1.903888434126516</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.355062583389172</v>
+        <v>1.250705320226652</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.872145060742403</v>
+        <v>3.809530702844891</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.756715283245263</v>
+        <v>-2.861072546407783</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.947772949110906</v>
+        <v>1.906030043845898</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.355062583389172</v>
+        <v>1.250705320226652</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.863853036756262</v>
+        <v>3.80123867885875</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.668837370136143</v>
+        <v>-2.773194633298662</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.981117309938333</v>
+        <v>1.939374404673326</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.470988225812523</v>
+        <v>1.366630962650004</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.931601617794052</v>
+        <v>3.86898725989654</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.659944908742859</v>
+        <v>-2.764302171905379</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.002228700222438</v>
+        <v>1.96048579495743</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.470988225812523</v>
+        <v>1.366630962650004</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.949156023520843</v>
+        <v>3.886541665623331</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.828421025712737</v>
+        <v>-2.932778288875256</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.926693300839071</v>
+        <v>1.884950395574063</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.443040390095942</v>
+        <v>1.338683126933423</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.924242369495478</v>
+        <v>3.861628011597967</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.382164833083297</v>
+        <v>-2.486522096245817</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.086465475078709</v>
+        <v>2.044722569813701</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.34832172042631</v>
+        <v>1.24396445726379</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.848680864881561</v>
+        <v>3.786066506984049</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.359443729400144</v>
+        <v>-2.463800992562664</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.086217939048874</v>
+        <v>2.044475033783867</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.34832172042631</v>
+        <v>1.24396445726379</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.839344887378465</v>
+        <v>3.776730529480953</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.488645542694187</v>
+        <v>-2.593002805856707</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.193443339582426</v>
+        <v>2.151700434317418</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.219119907132267</v>
+        <v>1.114762643969748</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.920729925253209</v>
+        <v>3.858115567355697</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.514519941168213</v>
+        <v>-2.618877204330732</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.220171402686463</v>
+        <v>2.178428497421455</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.264031515844009</v>
+        <v>1.159674252681489</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.9847547129739</v>
+        <v>3.922140355076388</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.507465250953039</v>
+        <v>-2.611822514115559</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.219668634762077</v>
+        <v>2.177925729497069</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.271086206059182</v>
+        <v>1.166728942896663</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.98566288309255</v>
+        <v>3.923048525195038</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.480514026626551</v>
+        <v>-2.584871289789071</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.240455278137414</v>
+        <v>2.198712372872406</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.285966552086901</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.004597244353922</v>
+        <v>3.941982886456411</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.616467034682867</v>
+        <v>-2.720824297845387</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.370177207059847</v>
+        <v>2.328434301794839</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.285966552086901</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.188700376498883</v>
+        <v>4.126086018601371</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.638875152487739</v>
+        <v>-2.743232415650259</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.353330654840891</v>
+        <v>2.311587749575883</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.285966552086901</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.180817071401876</v>
+        <v>4.118202713504364</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.66709938806534</v>
+        <v>-2.771456651227859</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.344094960159489</v>
+        <v>2.302352054894481</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.30394330453821</v>
+        <v>1.19958604137569</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.193657122422298</v>
+        <v>4.131042764524786</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.67654031395387</v>
+        <v>-2.780897577116389</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.396572307525924</v>
+        <v>2.354829402260916</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.426370422081602</v>
+        <v>1.322013158919082</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.32336711067018</v>
+        <v>4.260752752772668</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.728813921289511</v>
+        <v>-2.833171184452031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.378553959136968</v>
+        <v>2.33681105387196</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.37409681474596</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.294894040814096</v>
+        <v>4.232279682916585</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.805143898890417</v>
+        <v>-2.909501162052937</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.346133780990381</v>
+        <v>2.304390875725373</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.37409681474596</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.293005853707871</v>
+        <v>4.23039149581036</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.00739761921477</v>
+        <v>-3.11175488237729</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.260052522463502</v>
+        <v>2.218309617198494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.171843094421607</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.166473851116121</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.168966044742025</v>
+        <v>-3.273323307904545</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.193859162462752</v>
+        <v>2.152116257197744</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.045060170623727</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.088838107047547</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.301267336839579</v>
+        <v>-3.405624600002098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.15401205248965</v>
+        <v>2.112269147224642</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.045060170623727</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.101911513913465</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.487135647678809</v>
+        <v>-3.591492910841328</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.071669924936898</v>
+        <v>2.02992701967189</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8864945773037798</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.998777354704437</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.515036434788282</v>
+        <v>-3.619393697950801</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.05903365122011</v>
+        <v>2.017290745955103</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.851897653160845</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.976543241345677</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.637562537491176</v>
+        <v>-3.741919800653695</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.006787654116152</v>
+        <v>1.965044748851144</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7293715504579511</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.89979202370114</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.868077033676764</v>
+        <v>-3.972434296839284</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.98128781523242</v>
+        <v>1.939544909967412</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4988570542723624</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.828189285580291</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.124797851671588</v>
+        <v>-4.229155114834107</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.018911207036338</v>
+        <v>1.97716830177133</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3904424801285475</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.903452260095849</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.278784269447728</v>
+        <v>-4.383141532610248</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.026296909071521</v>
+        <v>1.984554003806513</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3904424801285475</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.972432529241488</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.228262365620062</v>
+        <v>-4.332619628782582</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.032556872722708</v>
+        <v>1.990813967457701</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3904424801285475</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.95848373136161</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.480737519627787</v>
+        <v>-4.585094782790306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.943437300175033</v>
+        <v>1.901694394910025</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3904424801285475</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.970354220417024</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.773633276107199</v>
+        <v>-4.877990539269718</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.827489532102212</v>
+        <v>1.785746626837204</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3904424801285475</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.971564754935967</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.960297404242007</v>
+        <v>-5.064654667404526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.75694562307561</v>
+        <v>1.715202717810602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3637035093039876</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.959643114668553</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.106318091155969</v>
+        <v>-5.210675354318488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.693615201046214</v>
+        <v>1.651872295781207</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3546204175101307</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.949271112328428</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.198032100265554</v>
+        <v>-5.302389363428073</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.819133654101424</v>
+        <v>1.777390748836417</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3546204175101307</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.111475169027472</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.282750042486507</v>
+        <v>-5.387107305649026</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.780093115176857</v>
+        <v>1.73835020991185</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2695043885820843</v>
+        <v>0.1651471254195646</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.055252189634459</v>
+        <v>3.992637831736946</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.36468486075539</v>
+        <v>-5.46904212391791</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.757548605437795</v>
+        <v>1.715805700172787</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2595696429950041</v>
+        <v>0.1552123798324844</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.059520759850701</v>
+        <v>3.99690640195319</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.466660983003798</v>
+        <v>-5.571018246166317</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.725683794994335</v>
+        <v>1.683940889729327</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1575935207465965</v>
+        <v>0.05323625758407685</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.007260724957559</v>
+        <v>3.944646367060048</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.356654699526576</v>
+        <v>-5.461011962689096</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.761839195629399</v>
+        <v>1.720096290364391</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1807980926638718</v>
+        <v>0.07644082950135206</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.0133363553521</v>
+        <v>3.950721997454588</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.21359512378565</v>
+        <v>-5.31795238694817</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.823313036647743</v>
+        <v>1.781570131382736</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.188811519253851</v>
+        <v>0.08445425609133134</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.022394422028062</v>
+        <v>3.95978006413055</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.912148398313812</v>
+        <v>-5.016505661476332</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.951152609719014</v>
+        <v>1.909409704454007</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4902582447256882</v>
+        <v>0.3859009815631686</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.2105233401937</v>
+        <v>4.147908982296189</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.936738642548996</v>
+        <v>-5.041095905711516</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.942287689777651</v>
+        <v>1.900544784512644</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4902582447256882</v>
+        <v>0.3859009815631686</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.21149451794641</v>
+        <v>4.148880160048899</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.885700266542476</v>
+        <v>-4.990057529704996</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.963545944560015</v>
+        <v>1.921803039295007</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4902582447256882</v>
+        <v>0.3859009815631686</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.212337422326166</v>
+        <v>4.149723064428654</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.844560971675845</v>
+        <v>-4.948918234838365</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.999039761380812</v>
+        <v>1.957296856115804</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5313975395923191</v>
+        <v>0.4270402764297994</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.256059098120289</v>
+        <v>4.193444740222778</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.747926059657205</v>
+        <v>-4.852283322819725</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.853877722312203</v>
+        <v>1.812134817047195</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.628032451610959</v>
+        <v>0.5236751884484394</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.130224041455408</v>
+        <v>4.067609683557897</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.878506794188048</v>
+        <v>-4.769176599063955</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.80514747257383</v>
+        <v>1.848879550623467</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4974517170801165</v>
+        <v>0.6067819122042095</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.055377644810866</v>
+        <v>4.120975761885322</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.714010459997086</v>
+        <v>-4.604680264872993</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.855372825326297</v>
+        <v>1.899104903375934</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4974517170801165</v>
+        <v>0.6067819122042095</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.039804463886949</v>
+        <v>4.105402580961405</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.741380392681518</v>
+        <v>-4.632050197557425</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.843612562688954</v>
+        <v>1.887344640738591</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4974517170801165</v>
+        <v>0.6067819122042095</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.038992174323378</v>
+        <v>4.104590291397835</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.751765587571407</v>
+        <v>-4.642435392447315</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.849327263858071</v>
+        <v>1.893059341907708</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4870665221902272</v>
+        <v>0.5963967173143202</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.042629836514517</v>
+        <v>4.108227953588973</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.770353746293632</v>
+        <v>-4.661023551169539</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.912729006145606</v>
+        <v>1.956461084195243</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4684783634680018</v>
+        <v>0.5778085585920949</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.102313947057607</v>
+        <v>4.167912064132063</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.770652292989668</v>
+        <v>-4.661322097865575</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.90947859828549</v>
+        <v>1.953210676335127</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4684783634680018</v>
+        <v>0.5778085585920949</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.099182957875906</v>
+        <v>4.164781074950362</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.66982915929924</v>
+        <v>-4.560498964175148</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.954338746701052</v>
+        <v>1.998070824750689</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4809425789523556</v>
+        <v>0.5902727740764487</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.11119238210591</v>
+        <v>4.176790499180365</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.479047798546834</v>
+        <v>-4.369717603422741</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.030780544480558</v>
+        <v>2.074512622530196</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.671723939704763</v>
+        <v>0.7810541348288561</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.225790452035898</v>
+        <v>4.291388569110353</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.460530944505013</v>
+        <v>-4.35120074938092</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.018024131834883</v>
+        <v>2.06175620988452</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6846540691299712</v>
+        <v>0.7939842642540643</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.213385375428619</v>
+        <v>4.278983492503075</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.435337760003695</v>
+        <v>-4.326007564879602</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.063068342247469</v>
+        <v>2.106800420297106</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7098472536312895</v>
+        <v>0.8191774487553827</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.263468222741468</v>
+        <v>4.329066339815924</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.423283633090732</v>
+        <v>-4.31395343796664</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.061576560914092</v>
+        <v>2.105308638963729</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7219013805442523</v>
+        <v>0.8312315756683455</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.264387266790683</v>
+        <v>4.329985383865139</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.429906879781091</v>
+        <v>-4.320576684656998</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.060807892422084</v>
+        <v>2.104539970471722</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.715278133853894</v>
+        <v>0.8246083289779871</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.262293948960604</v>
+        <v>4.32789206603506</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.327026290252498</v>
+        <v>-4.217696095128405</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.114811154111404</v>
+        <v>2.158543232161041</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.818158723382487</v>
+        <v>0.92748891850658</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.336873328555643</v>
+        <v>4.402471445630098</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.350468329432585</v>
+        <v>-4.241138134308492</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.125637008612963</v>
+        <v>2.1693690866626</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.818158723382487</v>
+        <v>0.92748891850658</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.357075998729237</v>
+        <v>4.422674115803693</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.368540837724196</v>
+        <v>-4.259210642600103</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.118408005296319</v>
+        <v>2.162140083345956</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.818158723382487</v>
+        <v>0.92748891850658</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.357075998729237</v>
+        <v>4.422674115803693</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.599714631600828</v>
+        <v>-4.490384436476735</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.986190401339132</v>
+        <v>2.02992247938877</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.818158723382487</v>
+        <v>0.92748891850658</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.317327912322703</v>
+        <v>4.38292602939716</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.568428611060373</v>
+        <v>-4.45909841593628</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.005727428552254</v>
+        <v>2.049459506601892</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8494447439229423</v>
+        <v>0.9587749390470354</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.343122143643916</v>
+        <v>4.408720260718372</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.415403218947088</v>
+        <v>-4.306073023822996</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.166108584970472</v>
+        <v>2.20984066302011</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.002470136036226</v>
+        <v>1.11180033116032</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.534108378484791</v>
+        <v>4.599706495559247</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.443710532820359</v>
+        <v>-4.334380337696266</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.342251884329457</v>
+        <v>2.385983962379094</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.002470136036226</v>
+        <v>1.11180033116032</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.721574603393083</v>
+        <v>4.78717272046754</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.610303757933881</v>
+        <v>-4.500973562809788</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.24501754563813</v>
+        <v>2.288749623687767</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.835876910922704</v>
+        <v>0.945207106046797</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.591021619679053</v>
+        <v>4.656619736753508</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.437239378551581</v>
+        <v>-4.327909183427488</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.317919700052768</v>
+        <v>2.361651778102405</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.835876910922704</v>
+        <v>0.945207106046797</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.59469802234077</v>
+        <v>4.660296139415226</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.407993398095885</v>
+        <v>-4.298663202971792</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.327236147358541</v>
+        <v>2.370968225408179</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.835876910922704</v>
+        <v>0.945207106046797</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.592316077464266</v>
+        <v>4.657914194538721</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.514918945973736</v>
+        <v>-4.405588750849643</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.281759167365037</v>
+        <v>2.325491245414673</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7289513630448526</v>
+        <v>0.8382815581689457</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.525453987895189</v>
+        <v>4.591052104969646</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.659937504480984</v>
+        <v>-4.550607309356892</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.225180546105371</v>
+        <v>2.268912624155008</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5839328045376041</v>
+        <v>0.6932629996616971</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.439871654934075</v>
+        <v>4.505469772008531</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.778279270265702</v>
+        <v>-4.668949075141609</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.277775079049237</v>
+        <v>2.321507157098874</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5946188431004942</v>
+        <v>0.7039490382245872</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.546214517329561</v>
+        <v>4.611812634404018</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.834926398069887</v>
+        <v>3.947072508949229</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.353985024945755</v>
+        <v>4.515119992005221</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.778279270265702</v>
+        <v>-4.668949075141609</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.277775079049237</v>
+        <v>2.321507157098874</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5946188431004942</v>
+        <v>0.7039490382245872</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.347048821932123</v>
+        <v>4.508183788991588</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,37 +834,37 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.9%</t>
+          <t>110.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.7%</t>
+          <t>430.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-628.5%</t>
+          <t>-652.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.1%</t>
+          <t>-150.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.5%</t>
+          <t>-325.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.6%</t>
+          <t>-182.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.16895219399483</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.1360239630966471</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-0.9263221416308458</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.576120053836525</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.223023693503189</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1547590065784181</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-0.9803936411392052</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.546570710453082</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.427281868833052</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.2309490795917215</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.108032585753194</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.475500540803331</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.460934707341526</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.2399276605106748</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.208445953670231</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.419735074537544</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.387464875674077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1951680263502737</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.134976122002783</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.479188675031435</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.56258929306062</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.2506625725573746</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.310100539389327</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.388669245347025</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.79704138707511</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3516625750647662</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.310100539389327</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.381450080445429</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.901416118101556</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.4000846582493209</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.414475270415773</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.312153051055585</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-9.063929583800141</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4639742546901986</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.512108700834459</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.25468878264293</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.18996637716843</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.5116952434083997</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.486857078024717</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.27253348495789</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.132894605272499</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4848761989636263</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.486857078024717</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.276523820644291</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.274566446996619</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.5430201625520161</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.486857078024717</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.275048593745549</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.224975602571785</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.5081304146172103</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.437266233599883</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.319856510565322</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-9.076057268099929</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4616142144751505</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.40601664286471</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.325555131359742</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.850212115380518</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3616970803511781</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.364089967277546</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.360290209748249</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.725633459042927</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.3107264732600821</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.364089967277546</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.361429354304308</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.778528747087213</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.3292508143156891</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.3591346211891</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.367036336119483</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.706395571799332</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2946638399619004</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.3591346211891</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.37277004035812</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.635029179189685</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2758545453119066</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.287768228579452</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.405852613530044</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.54157014520446</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2483544130307243</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.287768228579452</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.395969132217136</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.530916963651029</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.2459277009087253</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.287768228579452</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.394134571717762</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.433009924974538</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.20706520041159</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.219782478718896</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.434625706660635</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.40905638399858</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1968152778757131</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.195828937742938</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.449666337391704</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.144996445675783</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.1044516187083468</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9317689994201421</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.594841984223629</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.437916822170945</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.1755931970332876</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9317689994201421</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.592054950563328</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.397732523804755</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.1920105402676051</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.8915847010539514</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.616509153470884</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.234332652865392</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.256737309864107</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.7281848301145889</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.713915897255259</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-7.051375431807474</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.337844627125127</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.5452276090566703</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.831614658727862</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.901709040799958</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.3948189732151741</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4523241178141344</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.884464543160424</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.769433567169072</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.4430966494145556</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.3200486441832477</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.959197314085984</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.61369523460933</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.508207043126089</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1643103116235062</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>3.055455374309465</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.528730567880011</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.5550992510414754</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.07934564489418661</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.119340515570715</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.634320557653115</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.3848873255330147</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.184935634667291</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.928010592107634</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.566085973027688</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.4607255012602725</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.166520311794755</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>2.987604127708242</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.418145931620089</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.4000225951351446</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.1461993958861974</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.879917754565209</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.3651764093661</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.4124964177832617</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.09322987363220853</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.902985481664124</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.199388213405809</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.4718510840722847</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.09322987363220853</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.896024869569031</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-6.166025006927041</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.4996587210449355</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.09322987363220853</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.910487223950174</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-6.057765869804519</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.5374944963531392</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.09322987363220853</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.905019344409369</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.934474734987388</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.5843090442905683</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.03006126118492197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.976492119310224</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.881777867856097</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.6130887693804099</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.08275812831621315</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>3.015811217826324</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.638012425872652</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.7063756545208384</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.08275812831621315</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>3.011591926173375</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.54823675349618</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.7444102373914432</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1443575732305232</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>3.050675907041977</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.298386359547106</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.8370924699547753</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1443575732305232</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>3.043417982025679</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-5.122494267079674</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.9110484304623969</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1443575732305232</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>3.047017105546328</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.95104780405721</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>0.9929545217259359</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.3158040362529863</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.163212489414359</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.855365915877906</v>
+        <v>-4.871025516948089</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.030247754613955</v>
+        <v>1.023983914185881</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.3958263233621073</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.210246339296129</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.791730173643971</v>
+        <v>-4.807389774714155</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.060396852561846</v>
+        <v>1.054133012133772</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.4594620655960418</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.253122585690807</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.698032855427576</v>
+        <v>-4.71369245649776</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.079070038632199</v>
+        <v>1.072806198204126</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.4594620655960418</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.234316844474602</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.708535478492865</v>
+        <v>-4.724195079563049</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.076612066030961</v>
+        <v>1.070348225602888</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4489594425307529</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.229758347260307</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.636292910321671</v>
+        <v>-4.651952511391854</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.109438407134259</v>
+        <v>1.103174566706186</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4489594425307529</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.233687661095127</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.618579223443805</v>
+        <v>-4.634238824513988</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117202465802746</v>
+        <v>1.110938625374672</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4521407714276697</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.236275042350617</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.509774337964078</v>
+        <v>-4.525433939034261</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.15772249121463</v>
+        <v>1.151458650786557</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.4521407714276697</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.23327311357061</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.289753539927068</v>
+        <v>-4.305413140997251</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247309847440048</v>
+        <v>1.241046007011975</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.59336061649565</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.319584057622013</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.172545451933973</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.310087265439109</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.59336061649565</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.335478240423836</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.052372368569475</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.35930234322521</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.7135336998601489</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.408727934882837</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.917119007239497</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.423491790318641</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.848787061190126</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.499968054242263</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.97699383459719</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.38557935077699</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7889122338324339</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.450080649229074</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.857173603686352</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.448796612375534</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7889122338324339</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.465369818463282</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.859643310148158</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.355452929113253</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.7864425273706277</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.37153219390864</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.928013496472168</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.24736671606895</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7957182264068426</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.296359474815671</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.941801549319215</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.232288203562023</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7957182264068426</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.286796183447562</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.997321625211804</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.347111009897189</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7957182264068426</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.423827020139764</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.821847365419335</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.421867945805965</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7957182264068426</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.428394252131552</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.798263389764238</v>
+        <v>-3.813922990834421</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.407043564829211</v>
+        <v>1.400779724401138</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.7957182264068426</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.404136280892759</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.791985187194389</v>
+        <v>-3.807644788264572</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.3380931592586</v>
+        <v>1.331829318830527</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8176560300468725</v>
+        <v>0.8019964289766917</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.345837276478227</v>
+        <v>3.336441515836118</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.732132567990666</v>
+        <v>-3.747792169060849</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.372206593372222</v>
+        <v>1.365942752944149</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8176560300468725</v>
+        <v>0.8019964289766917</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.356009662910359</v>
+        <v>3.346613902268251</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.645889104964288</v>
+        <v>-3.661548706034472</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.401650249156633</v>
+        <v>1.39538640872856</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8176560300468725</v>
+        <v>0.8019964289766917</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.35095593348422</v>
+        <v>3.341560172842111</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.691195924363268</v>
+        <v>-3.706855525433451</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.375303296841567</v>
+        <v>1.369039456413494</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7768458670376417</v>
+        <v>0.7611862659674609</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.318245611123206</v>
+        <v>3.308849850481098</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.72022902906557</v>
+        <v>-3.735888630135753</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.364241927993748</v>
+        <v>1.357978087565674</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7768458670376417</v>
+        <v>0.7611862659674609</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.318797484156308</v>
+        <v>3.309401723514199</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.62741854761471</v>
+        <v>-3.643078148684894</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.330638812465457</v>
+        <v>1.324374972037384</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.869656348488501</v>
+        <v>0.8539967474183202</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.303756464918189</v>
+        <v>3.294360704276081</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.671808016944138</v>
+        <v>-3.687467618014321</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.314756500658287</v>
+        <v>1.308492660230214</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8252668791590734</v>
+        <v>0.8096072780888925</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.278996259245134</v>
+        <v>3.269600498603025</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.788349622049481</v>
+        <v>-3.804009223119664</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.263215567127873</v>
+        <v>1.256951726699799</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7087252740537306</v>
+        <v>0.6930656729835498</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.204147004693651</v>
+        <v>3.194751244051543</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.828273716632053</v>
+        <v>-3.843933317702236</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.252737225125511</v>
+        <v>1.246473384697438</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7087252740537306</v>
+        <v>0.6930656729835498</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.209638300524318</v>
+        <v>3.20024253988221</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.856054114533406</v>
+        <v>-3.871713715603589</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.253122267733509</v>
+        <v>1.246858427305436</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6809448761523775</v>
+        <v>0.6652852750821967</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.204467263552045</v>
+        <v>3.195071502909937</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.974434787263544</v>
+        <v>-3.990094388333727</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.044125718642107</v>
+        <v>1.037861878214034</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6137270240014013</v>
+        <v>0.5980674229312205</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.002492272262113</v>
+        <v>2.993096511620005</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.083048865706875</v>
+        <v>-4.098708466777058</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.12082974798398</v>
+        <v>1.114565907555907</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6137270240014013</v>
+        <v>0.5980674229312205</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.122641932981319</v>
+        <v>3.11324617233921</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.047639827458732</v>
+        <v>-4.063299428528915</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14950638938556</v>
+        <v>1.143242548957487</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6137270240014013</v>
+        <v>0.5980674229312205</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.137154959083642</v>
+        <v>3.127759198441533</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.009256164900581</v>
+        <v>-4.024915765970764</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.16227929575119</v>
+        <v>1.156015455323116</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6521106865595525</v>
+        <v>0.6364510854893717</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.157604597960901</v>
+        <v>3.148208837318792</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.832139834865415</v>
+        <v>-3.847799435935598</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.229854856610558</v>
+        <v>1.223591016182485</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6521106865595525</v>
+        <v>0.6364510854893717</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.154333626806203</v>
+        <v>3.144937866164094</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.877232079698961</v>
+        <v>-3.892891680769144</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.212501350439053</v>
+        <v>1.206237510010979</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5902146433901627</v>
+        <v>0.5745550423199819</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.117879392666482</v>
+        <v>3.108483632024374</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.697856658460193</v>
+        <v>-3.713516259530376</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.278038494240974</v>
+        <v>1.271774653812901</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7469914015608814</v>
+        <v>0.7313318004907006</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.205732422875328</v>
+        <v>3.196336662233219</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.742870871980799</v>
+        <v>-3.758530473050982</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.240840264164321</v>
+        <v>1.234576423736248</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7166425062462768</v>
+        <v>0.700982905176096</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.168330541018155</v>
+        <v>3.158934780376046</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.009875382253234</v>
+        <v>-4.025534983323418</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.139730022394293</v>
+        <v>1.13346618196622</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5222794682033283</v>
+        <v>0.5066198671331474</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.057404280531332</v>
+        <v>3.048008519889223</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.111073163690407</v>
+        <v>-4.12673276476059</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.098454831715925</v>
+        <v>1.092190991287852</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.4382110535878282</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.015562914300641</v>
+        <v>3.006167153658533</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.104562197076095</v>
+        <v>-4.120221798146278</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098659179915967</v>
+        <v>1.092395339487894</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.4382110535878282</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.013162875854958</v>
+        <v>3.003767115212849</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.085524069368797</v>
+        <v>-4.101183670438981</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102799150207131</v>
+        <v>1.096535309779058</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.3800274422566337</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.974777428264486</v>
+        <v>2.965381667622378</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.138039871643618</v>
+        <v>-4.153699472713801</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201087230931393</v>
+        <v>1.19482339050332</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.3800274422566337</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.094071829898676</v>
+        <v>3.084676069256568</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.151906632977536</v>
+        <v>-4.167566234047719</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.19637385538396</v>
+        <v>1.190110014955886</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.3421695255228108</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.072190408844516</v>
+        <v>3.062794648202408</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.107102461437606</v>
+        <v>-4.122762062507789</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.220304054396858</v>
+        <v>1.214040213968784</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.3421695255228108</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.078198939241442</v>
+        <v>3.068803178599334</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.959359491202604</v>
+        <v>-3.975019092272787</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.177351463768058</v>
+        <v>1.171087623339985</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.5099768827576939</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.076833574859572</v>
+        <v>3.067437814217463</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.043180712477302</v>
+        <v>-4.058840313547485</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14661659678966</v>
+        <v>1.140352756361586</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.5099768827576939</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.079627196391053</v>
+        <v>3.070231435748944</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.037028006424517</v>
+        <v>-4.0526876074947</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.149740027602432</v>
+        <v>1.143476187174358</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.531789189880659</v>
+        <v>0.5161295888104782</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.083981168414382</v>
+        <v>3.074585407772273</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.716964352826587</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.053837304575019</v>
+        <v>-4.069496905645202</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.142096785082341</v>
+        <v>1.088809166254759</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5149798917301573</v>
+        <v>0.4993202906599765</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.072976066264191</v>
+        <v>3.016556527222573</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.783299906623408</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.991539305798897</v>
+        <v>-4.00719890686908</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.233351538389611</v>
+        <v>1.180063919562028</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5602741560045994</v>
+        <v>0.5446145549344186</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.166488178625677</v>
+        <v>3.110068639584059</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.585591908337535</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.789749108133739</v>
+        <v>-3.805408709203922</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.116359619169801</v>
+        <v>1.063072000342219</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7582923481737538</v>
+        <v>0.742632747103573</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.087591095641296</v>
+        <v>3.031171556599679</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.65588214065971</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.840635820819934</v>
+        <v>-3.856295421890117</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.166295166417498</v>
+        <v>1.113007547589916</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7074056354875593</v>
+        <v>0.6917460344173785</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.127349300351755</v>
+        <v>3.070929761310138</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.670509876775754</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.754025078170127</v>
+        <v>-3.76968467924031</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.215567199593465</v>
+        <v>1.162279580765883</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7860313666927176</v>
+        <v>0.7703717656225367</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.189152475190894</v>
+        <v>3.132732936149276</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.669045857600425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.814234376175411</v>
+        <v>-3.829893977245594</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.190019461216023</v>
+        <v>1.13673184238844</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.725822068687433</v>
+        <v>0.7101624676172522</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.151562877212394</v>
+        <v>3.095143338170777</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.667537475640354</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.737812329743484</v>
+        <v>-3.753471930813667</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.219079897828722</v>
+        <v>1.16579227900114</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.725822068687433</v>
+        <v>0.7101624676172522</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.150054495252323</v>
+        <v>3.093634956210706</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.66740034307579</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.693439198104916</v>
+        <v>-3.709098799175099</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.236692017919586</v>
+        <v>1.183404399092003</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.7545355992558208</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.1765412416709</v>
+        <v>3.120121702629283</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.661794137214381</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.715919548963801</v>
+        <v>-3.731579150033983</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.222093671714622</v>
+        <v>1.16880605288704</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.7545355992558208</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.170935035809491</v>
+        <v>3.114515496767873</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.668175894242185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.668263818402745</v>
+        <v>-3.683923419472928</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.247537720966849</v>
+        <v>1.194250102139266</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8178509308870573</v>
+        <v>0.8021913298168765</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.205910231173929</v>
+        <v>3.149490692132311</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.67306826761691</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.567745659903991</v>
+        <v>-3.583405260974173</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.292637357741076</v>
+        <v>1.239349738913493</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9183690893858119</v>
+        <v>0.902709488315631</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.271113499647907</v>
+        <v>3.214693960606289</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.659822940092782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.551840330471638</v>
+        <v>-3.567499931541821</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.285754161989889</v>
+        <v>1.232466543162306</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8392564286765729</v>
+        <v>0.8235968276063921</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.210400575698236</v>
+        <v>3.153981036656617</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.663920642703411</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.50700192886324</v>
+        <v>-3.522661529933423</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.307787225243877</v>
+        <v>1.254499606416294</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8437998616214424</v>
+        <v>0.8281402605512616</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.217224338075786</v>
+        <v>3.160804799034168</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.668081582334489</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.526500385105248</v>
+        <v>-3.542159986175431</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.304148782378152</v>
+        <v>1.250861163550569</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7957152203415381</v>
+        <v>0.7800556192713572</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.192534492938921</v>
+        <v>3.136114953897303</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.673961184862326</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.482297548019348</v>
+        <v>-3.49795714908953</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.327709519740349</v>
+        <v>1.274421900912766</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8399180574274385</v>
+        <v>0.8242584563572577</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.224935797718299</v>
+        <v>3.16851625867668</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.672371185331573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.489857213856395</v>
+        <v>-3.505516814926577</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.323095653874778</v>
+        <v>1.269808035047195</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.879061860367077</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.256227840593438</v>
+        <v>3.19980830155182</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.723618950514613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.331565796317122</v>
+        <v>-3.347225397387305</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.437659986073526</v>
+        <v>1.384372367245943</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.879061860367077</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.307475605776477</v>
+        <v>3.25105606673486</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.722059655108866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.123923792682646</v>
+        <v>-3.139583393752829</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51915749212157</v>
+        <v>1.465869873293987</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.102363465071734</v>
+        <v>1.086703864001553</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.430501512551416</v>
+        <v>3.374081973509798</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.717007883347136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.072891699960118</v>
+        <v>-3.088551301030301</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.534518557448851</v>
+        <v>1.481230938621268</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.153395557794262</v>
+        <v>1.137735956724081</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.456068996423203</v>
+        <v>3.399649457381585</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.734195287439841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.007667518832912</v>
+        <v>-3.023327119903095</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.577795633992438</v>
+        <v>1.524508015164856</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.218619738921468</v>
+        <v>1.202960137851287</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.512390909192232</v>
+        <v>3.455971370150613</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.730156259739121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.970240498761779</v>
+        <v>-2.985900099831961</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.588727414320172</v>
+        <v>1.535439795492589</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.223871276950649</v>
+        <v>1.208211675880468</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.511502804309021</v>
+        <v>3.455083265267403</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.731413052070362</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.990352154796487</v>
+        <v>-3.00601175586667</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.581939544237529</v>
+        <v>1.528651925409946</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.234898621948069</v>
+        <v>1.219239020877888</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.519376003638713</v>
+        <v>3.462956464597094</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.891970823091572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961938891696603</v>
+        <v>-2.977598492766786</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.753862620498693</v>
+        <v>1.700575001671111</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.17592305920164</v>
+        <v>1.160263458131459</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644548437012066</v>
+        <v>3.588128897970448</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>3.01208373230939</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.887156630671591</v>
+        <v>-2.902816231741773</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.903888434126516</v>
+        <v>1.850600815298933</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.250705320226652</v>
+        <v>1.235045719156471</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809530702844891</v>
+        <v>3.753111163803273</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>3.003791708323249</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.861072546407783</v>
+        <v>-2.876732147477965</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.906030043845898</v>
+        <v>1.852742425018315</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.250705320226652</v>
+        <v>1.235045719156471</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.80123867885875</v>
+        <v>3.744819139817132</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>3.001984903907028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.773194633298662</v>
+        <v>-2.788854234368845</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.939374404673326</v>
+        <v>1.886086785845743</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.366630962650004</v>
+        <v>1.350971361579822</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.86898725989654</v>
+        <v>3.812567720854922</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>3.019539309633819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.764302171905379</v>
+        <v>-2.779961772975561</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.96048579495743</v>
+        <v>1.907198176129848</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.366630962650004</v>
+        <v>1.350971361579822</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886541665623331</v>
+        <v>3.830122126581713</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>3.011394357038403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.932778288875256</v>
+        <v>-2.948437889945439</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884950395574063</v>
+        <v>1.83166277674648</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.338683126933423</v>
+        <v>1.323023525863242</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.861628011597967</v>
+        <v>3.805208472556349</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.992664054226265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.486522096245817</v>
+        <v>-2.502181697315999</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.044722569813701</v>
+        <v>1.991434950986118</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.24396445726379</v>
+        <v>1.228304856193609</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.786066506984049</v>
+        <v>3.729646967942431</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.98332807672317</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.463800992562664</v>
+        <v>-2.479460593632847</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.044475033783867</v>
+        <v>1.991187414956284</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.24396445726379</v>
+        <v>1.228304856193609</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.776730529480953</v>
+        <v>3.720310990439335</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.142234202574339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.593002805856707</v>
+        <v>-2.608662406926889</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.151700434317418</v>
+        <v>2.098412815489835</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.114762643969748</v>
+        <v>1.099103042899567</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.858115567355697</v>
+        <v>3.801696028314079</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.179312025067985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.618877204330732</v>
+        <v>-2.634536805400915</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.178428497421455</v>
+        <v>2.125140878593872</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.159674252681489</v>
+        <v>1.144014651611308</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.922140355076388</v>
+        <v>3.86572081603477</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.175987381057531</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.611822514115559</v>
+        <v>-2.627482115185741</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177925729497069</v>
+        <v>2.124638110669486</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.166728942896663</v>
+        <v>1.151069341826482</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.923048525195038</v>
+        <v>3.86662898615342</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.185993534702272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.584871289789071</v>
+        <v>-2.600530890859253</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.198712372872406</v>
+        <v>2.145424754044823</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.181609288924382</v>
+        <v>1.165949687854201</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.941982886456411</v>
+        <v>3.885563347414793</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.370096666847232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.720824297845387</v>
+        <v>-2.73648389891557</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.328434301794839</v>
+        <v>2.275146682967256</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.181609288924382</v>
+        <v>1.165949687854201</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.126086018601371</v>
+        <v>4.069666479559753</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.362213361750225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.743232415650259</v>
+        <v>-2.758892016720442</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.311587749575883</v>
+        <v>2.258300130748301</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.181609288924382</v>
+        <v>1.165949687854201</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.118202713504364</v>
+        <v>4.061783174462746</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.364267361299862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.771456651227859</v>
+        <v>-2.787116252298042</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.302352054894481</v>
+        <v>2.249064436066898</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.19958604137569</v>
+        <v>1.183926440305509</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.131042764524786</v>
+        <v>4.074623225483168</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.42052107902171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.780897577116389</v>
+        <v>-2.796557178186572</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.354829402260916</v>
+        <v>2.301541783433334</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.322013158919082</v>
+        <v>1.306353557848901</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.260752752772668</v>
+        <v>4.204333213731051</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.42341217356701</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.848830785522213</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.283523435044378</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.25407995051326</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.175860143874966</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.421523986460786</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-2.925160763123119</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.251103256897791</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.25407995051326</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.173971956768741</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.416344216063648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.127414483447473</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.165021998370912</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.051826230188906</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.047439954176991</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.4147782262738</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.288982908974728</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.098828638370162</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.9250433063910267</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>3.969804210108417</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.427851633139719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.421284201072281</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.058981528397059</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.9250433063910267</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>3.982877616974335</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.419856829922659</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.607152511911511</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>1.976639400844307</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.766477713071079</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.879743457765306</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.418380871049661</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.635053299020984</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>1.96400312712752</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.7318807889281442</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.857509344406548</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.41514531502686</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.757579401723878</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.911757130023561</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.6093546862252504</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.78075812676201</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.481851274617363</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-3.988093897909466</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.886257291139829</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.3788401900396616</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.709155388641161</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.62216299361921</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.24481471590429</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>1.923880682943747</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2704256158958468</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.784418363156719</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.69114326276485</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.398801133680431</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>1.93126638497893</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2704256158958468</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.853398632302358</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.677194464884971</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.348279229852765</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>1.937526348630118</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2704256158958468</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.839449834422479</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.689064953940385</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.600754383860489</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.848406776082442</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2704256158958468</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.851320323477893</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.690275488459329</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.893650140339902</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.732459008009621</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2704256158958468</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.852530857996837</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.69439723068665</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-5.08031426847471</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.661915098983019</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.2436866450712869</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.840609217729423</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.68947508342284</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.226334955388672</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.598584676953624</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2346035532774299</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.830237215389298</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.851679140121884</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.318048964498256</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.724103130008834</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2346035532774299</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>3.992441272088342</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.846525778085698</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.387107305649026</v>
+        <v>-5.40276690671921</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.73835020991185</v>
+        <v>1.685062591084267</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1651471254195646</v>
+        <v>0.1494875243493836</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.992637831736946</v>
+        <v>3.936218292695329</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.856755195654189</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.46904212391791</v>
+        <v>-5.484701724988093</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.715805700172787</v>
+        <v>1.662518081345205</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1552123798324844</v>
+        <v>0.1395527787623034</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.99690640195319</v>
+        <v>3.940486862911571</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.865680834110091</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.571018246166317</v>
+        <v>-5.5866778472365</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.683940889729327</v>
+        <v>1.630653270901744</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.05323625758407685</v>
+        <v>0.0375766565138958</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.944646367060048</v>
+        <v>3.888226828018429</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.857833721354267</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.461011962689096</v>
+        <v>-5.476671563759279</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.720096290364391</v>
+        <v>1.666808671536808</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.07644082950135206</v>
+        <v>0.06078122843117101</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.950721997454588</v>
+        <v>3.89430245841297</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.862083732076241</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.31795238694817</v>
+        <v>-5.333611988018353</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.781570131382736</v>
+        <v>1.728282512555153</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.08445425609133134</v>
+        <v>0.06879465502115029</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.95978006413055</v>
+        <v>3.903360525088932</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.869344614958777</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.016505661476332</v>
+        <v>-5.032165262546515</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.909409704454007</v>
+        <v>1.856122085626424</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.3702413804929875</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.147908982296189</v>
+        <v>4.09148944325457</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.870315792711488</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.041095905711516</v>
+        <v>-5.056755506781699</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.900544784512644</v>
+        <v>1.847257165685061</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.3702413804929875</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.148880160048899</v>
+        <v>4.09246062100728</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.871158697091243</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.990057529704996</v>
+        <v>-5.005717130775179</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.921803039295007</v>
+        <v>1.868515420467424</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3859009815631686</v>
+        <v>0.3702413804929875</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.149723064428654</v>
+        <v>4.093303525387036</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.890196795965389</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.948918234838365</v>
+        <v>-4.964577835908548</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.957296856115804</v>
+        <v>1.904009237288222</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4270402764297994</v>
+        <v>0.4113806753596184</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.193444740222778</v>
+        <v>4.13702520118116</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.706380792089323</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.852283322819725</v>
+        <v>-4.867942923889908</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.812134817047195</v>
+        <v>1.758847198219613</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5236751884484394</v>
+        <v>0.5080155873782584</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.067609683557897</v>
+        <v>4.011190144516279</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.709882836163287</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.769176599063955</v>
+        <v>-4.99852365842075</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.848879550623467</v>
+        <v>1.71011694848124</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6067819122042095</v>
+        <v>0.3774348528474158</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.120975761885322</v>
+        <v>3.936343747871737</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.69430965523937</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.604680264872993</v>
+        <v>-4.834027324229789</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.899104903375934</v>
+        <v>1.760342301233707</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6067819122042095</v>
+        <v>0.3774348528474158</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.105402580961405</v>
+        <v>3.920770566947819</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.6934973656758</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.632050197557425</v>
+        <v>-4.861397256914221</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.887344640738591</v>
+        <v>1.748582038596364</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6067819122042095</v>
+        <v>0.3774348528474158</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.104590291397835</v>
+        <v>3.919958277384249</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.703366144800872</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.642435392447315</v>
+        <v>-4.87178245180411</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.893059341907708</v>
+        <v>1.754296739765481</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5963967173143202</v>
+        <v>0.3670496579575265</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.108227953588973</v>
+        <v>3.923595939575388</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.774203150577297</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.661023551169539</v>
+        <v>-4.890370610526335</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.956461084195243</v>
+        <v>1.817698482053016</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5778085585920949</v>
+        <v>0.3484614992353012</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.167912064132063</v>
+        <v>3.983280050118478</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.771072161395596</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.661322097865575</v>
+        <v>-4.890669157222371</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.953210676335127</v>
+        <v>1.8144480741929</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5778085585920949</v>
+        <v>0.3484614992353012</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.164781074950362</v>
+        <v>3.980149060936776</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.775603056334987</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.560498964175148</v>
+        <v>-4.789846023531943</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.998070824750689</v>
+        <v>1.859308222608463</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5902727740764487</v>
+        <v>0.360925714719655</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.176790499180365</v>
+        <v>3.99215848516678</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.77573230981353</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.369717603422741</v>
+        <v>-4.599064662779536</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.074512622530196</v>
+        <v>1.935750020387969</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7810541348288561</v>
+        <v>0.5517070754720623</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.291388569110353</v>
+        <v>4.106756555096768</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.755569155551127</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.35120074938092</v>
+        <v>-4.580547808737716</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.06175620988452</v>
+        <v>1.922993607742293</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7939842642540643</v>
+        <v>0.5646372048972705</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.278983492503075</v>
+        <v>4.094351478489489</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.790536092163185</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.326007564879602</v>
+        <v>-4.555354624236398</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.106800420297106</v>
+        <v>1.968037818154879</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8191774487553827</v>
+        <v>0.5898303893985889</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.329066339815924</v>
+        <v>4.144434325802339</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.784222660064623</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.31395343796664</v>
+        <v>-4.543300497323435</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.105308638963729</v>
+        <v>1.966546036821502</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8312315756683455</v>
+        <v>0.6018845163115517</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.329985383865139</v>
+        <v>4.145353369851555</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.786103290248759</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.320576684656998</v>
+        <v>-4.549923744013793</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.104539970471722</v>
+        <v>1.965777368329494</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8246083289779871</v>
+        <v>0.5952612696211934</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.32789206603506</v>
+        <v>4.143260052021476</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.798954316126641</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.217696095128405</v>
+        <v>-4.4470431544852</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.158543232161041</v>
+        <v>2.019780630018814</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.92748891850658</v>
+        <v>0.6981418591497863</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.402471445630098</v>
+        <v>4.217839431616514</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.819156986300236</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.241138134308492</v>
+        <v>-4.470485193665287</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.1693690866626</v>
+        <v>2.030606484520374</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.92748891850658</v>
+        <v>0.6981418591497863</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.422674115803693</v>
+        <v>4.238042101790108</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.819156986300236</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.259210642600103</v>
+        <v>-4.488557701956899</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.162140083345956</v>
+        <v>2.023377481203729</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.92748891850658</v>
+        <v>0.6981418591497863</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.422674115803693</v>
+        <v>4.238042101790108</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.779408899893702</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.490384436476735</v>
+        <v>-4.719731495833531</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.02992247938877</v>
+        <v>1.891159877246543</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.92748891850658</v>
+        <v>0.6981418591497863</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.38292602939716</v>
+        <v>4.198294015383574</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.786431518890642</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.45909841593628</v>
+        <v>-4.688445475293076</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.049459506601892</v>
+        <v>1.910696904459665</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9587749390470354</v>
+        <v>0.7294278796902417</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.408720260718372</v>
+        <v>4.224088246704787</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.885602518463547</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.306073023822996</v>
+        <v>-4.535420083179791</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.20984066302011</v>
+        <v>2.071078060877883</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.11180033116032</v>
+        <v>0.8824532718035258</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.599706495559247</v>
+        <v>4.415074481545663</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>4.073068743371839</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.334380337696266</v>
+        <v>-4.563727397053062</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.385983962379094</v>
+        <v>2.247221360236867</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.11180033116032</v>
+        <v>0.8824532718035258</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.78717272046754</v>
+        <v>4.602540706453954</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>4.042471694725921</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.500973562809788</v>
+        <v>-4.730320622166584</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.288749623687767</v>
+        <v>2.14998702154554</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.945207106046797</v>
+        <v>0.7158600466900034</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.656619736753508</v>
+        <v>4.471987722739923</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>4.046148097387639</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.327909183427488</v>
+        <v>-4.557256242784284</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.361651778102405</v>
+        <v>2.222889175960178</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.945207106046797</v>
+        <v>0.7158600466900034</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.660296139415226</v>
+        <v>4.475664125401641</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.090789930910643</v>
+        <v>4.043766152511134</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.298663202971792</v>
+        <v>-4.528010262328587</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.370968225408179</v>
+        <v>2.232205623265952</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.945207106046797</v>
+        <v>0.7158600466900034</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.657914194538721</v>
+        <v>4.473282180525136</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.088083170068278</v>
+        <v>4.041059391668769</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.405588750849643</v>
+        <v>-4.634935810206438</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.325491245414673</v>
+        <v>2.186728643272446</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8382815581689457</v>
+        <v>0.608934498812152</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.591052104969646</v>
+        <v>4.40642009095606</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983739</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.089511972211512</v>
+        <v>4.042488193812003</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.550607309356892</v>
+        <v>-4.779954368713687</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.268912624155008</v>
+        <v>2.130150022012781</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6932629996616971</v>
+        <v>0.4639159403049035</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.505469772008531</v>
+        <v>4.320837757994946</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969748</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.189443211469265</v>
+        <v>4.142419433069756</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.668949075141609</v>
+        <v>-4.898296134498405</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.321507157098874</v>
+        <v>2.182744554956647</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7039490382245872</v>
+        <v>0.4746019788677935</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.611812634404018</v>
+        <v>4.427180620390433</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.947072508949229</v>
+        <v>3.830294423823139</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.515119992005221</v>
+        <v>4.220705456674215</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.668949075141609</v>
+        <v>-4.907097221562331</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.321507157098874</v>
+        <v>2.257510143735535</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7039490382245872</v>
+        <v>0.4165437287334747</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.508183788991588</v>
+        <v>4.470631693914299</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240817.xlsx
+++ b/tame_output/ON/bt/strategyON_20240817.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>107.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.5%</t>
+          <t>430.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-652.3%</t>
+          <t>-649.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.5%</t>
+          <t>-152.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-325.3%</t>
+          <t>-331.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.3%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.16895219399483</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1360239630966471</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9263221416308458</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.576120053836525</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.223023693503189</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1547590065784181</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9803936411392052</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.546570710453082</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.427281868833052</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2309490795917215</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.108032585753194</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.475500540803331</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.460934707341526</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2399276605106748</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.208445953670231</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.419735074537544</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.387464875674077</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1951680263502737</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.134976122002783</v>
+        <v>-1.169840522104282</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.479188675031435</v>
+        <v>2.458270034970535</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.56258929306062</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2506625725573746</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.310100539389327</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.388669245347025</v>
+        <v>2.367750605286126</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.79704138707511</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3516625750647662</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.310100539389327</v>
+        <v>-1.344964939490826</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.381450080445429</v>
+        <v>2.36053144038453</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.901416118101556</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4000846582493209</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.414475270415773</v>
+        <v>-1.449339670517272</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.312153051055585</v>
+        <v>2.291234410994686</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.063929583800141</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4639742546901986</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.512108700834459</v>
+        <v>-1.546973100935959</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.25468878264293</v>
+        <v>2.23377014258203</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.18996637716843</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5116952434083997</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.486857078024717</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.27253348495789</v>
+        <v>2.25161484489699</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.132894605272499</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4848761989636263</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.486857078024717</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.276523820644291</v>
+        <v>2.255605180583391</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.274566446996619</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5430201625520161</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.486857078024717</v>
+        <v>-1.521721478126216</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.275048593745549</v>
+        <v>2.254129953684649</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.224975602571785</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5081304146172103</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.437266233599883</v>
+        <v>-1.472130633701382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.319856510565322</v>
+        <v>2.298937870504422</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.076057268099929</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4616142144751505</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.40601664286471</v>
+        <v>-1.440881042966209</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.325555131359742</v>
+        <v>2.304636491298843</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.850212115380518</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3616970803511781</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.364089967277546</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.360290209748249</v>
+        <v>2.33937156968735</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.725633459042927</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3107264732600821</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.364089967277546</v>
+        <v>-1.398954367379046</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.361429354304308</v>
+        <v>2.340510714243409</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.778528747087213</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3292508143156891</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.3591346211891</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.367036336119483</v>
+        <v>2.346117696058584</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.706395571799332</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2946638399619004</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.3591346211891</v>
+        <v>-1.393999021290599</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.37277004035812</v>
+        <v>2.351851400297221</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.635029179189685</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2758545453119066</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.287768228579452</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.405852613530044</v>
+        <v>2.384933973469144</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.54157014520446</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2483544130307243</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.287768228579452</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.395969132217136</v>
+        <v>2.375050492156237</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.530916963651029</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2459277009087253</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.287768228579452</v>
+        <v>-1.322632628680952</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.394134571717762</v>
+        <v>2.373215931656863</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.433009924974538</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.20706520041159</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.219782478718896</v>
+        <v>-1.254646878820395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.434625706660635</v>
+        <v>2.413707066599736</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.40905638399858</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1968152778757131</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.195828937742938</v>
+        <v>-1.230693337844438</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.449666337391704</v>
+        <v>2.428747697330804</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.144996445675783</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1044516187083468</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9317689994201421</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.594841984223629</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.437916822170945</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1755931970332876</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9317689994201421</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.592054950563328</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.397732523804755</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1920105402676051</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.8915847010539514</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.616509153470884</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.234332652865392</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.256737309864107</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7281848301145889</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.713915897255259</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.051375431807474</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.337844627125127</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5452276090566703</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.831614658727862</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.901709040799958</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3948189732151741</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4523241178141344</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.884464543160424</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.769433567169072</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4430966494145556</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3200486441832477</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.959197314085984</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.61369523460933</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.508207043126089</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1643103116235062</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.055455374309465</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.528730567880011</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5550992510414754</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.07934564489418661</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.119340515570715</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.634320557653115</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3848873255330147</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.184935634667291</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.928010592107634</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.566085973027688</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4607255012602725</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.166520311794755</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.987604127708242</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.418145931620089</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4000225951351446</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1461993958861974</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.879917754565209</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.3651764093661</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4124964177832617</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.09322987363220853</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.902985481664124</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.199388213405809</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4718510840722847</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.09322987363220853</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.896024869569031</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.166025006927041</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4996587210449355</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.09322987363220853</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.910487223950174</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.057765869804519</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5374944963531392</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.09322987363220853</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.905019344409369</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.934474734987388</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5843090442905683</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.03006126118492197</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.976492119310224</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.881777867856097</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6130887693804099</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.08275812831621315</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.015811217826324</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.638012425872652</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7063756545208384</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.08275812831621315</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.011591926173375</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.54823675349618</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7444102373914432</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1443575732305232</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.050675907041977</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.298386359547106</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8370924699547753</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1443575732305232</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.043417982025679</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.122494267079674</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9110484304623969</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1443575732305232</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.047017105546328</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.95104780405721</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9929545217259359</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3158040362529863</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.163212489414359</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.871025516948089</v>
+        <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.023983914185881</v>
+        <v>1.030247754613955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3958263233621073</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.210246339296129</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.807389774714155</v>
+        <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.054133012133772</v>
+        <v>1.060396852561846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4594620655960418</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.253122585690807</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.71369245649776</v>
+        <v>-4.698032855427576</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.072806198204126</v>
+        <v>1.079070038632199</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4594620655960418</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.234316844474602</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.724195079563049</v>
+        <v>-4.708535478492865</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.070348225602888</v>
+        <v>1.076612066030961</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4489594425307529</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.229758347260307</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.651952511391854</v>
+        <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.103174566706186</v>
+        <v>1.109438407134259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4489594425307529</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.233687661095127</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.634238824513988</v>
+        <v>-4.618579223443805</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.110938625374672</v>
+        <v>1.117202465802746</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4521407714276697</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.236275042350617</v>
+        <v>3.245670802992725</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.525433939034261</v>
+        <v>-4.509774337964078</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.151458650786557</v>
+        <v>1.15772249121463</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4521407714276697</v>
+        <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.23327311357061</v>
+        <v>3.242668874212719</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.305413140997251</v>
+        <v>-4.289753539927068</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.241046007011975</v>
+        <v>1.247309847440048</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.59336061649565</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.319584057622013</v>
+        <v>3.328979818264121</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.172545451933973</v>
+        <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.310087265439109</v>
+        <v>1.316351105867182</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.59336061649565</v>
+        <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.335478240423836</v>
+        <v>3.344874001065945</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.052372368569475</v>
+        <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.35930234322521</v>
+        <v>1.365566183653284</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7135336998601489</v>
+        <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.408727934882837</v>
+        <v>3.418123695524946</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.917119007239497</v>
+        <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.423491790318641</v>
+        <v>1.429755630746715</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.848787061190126</v>
+        <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.499968054242263</v>
+        <v>3.509363814884372</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.97699383459719</v>
+        <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.38557935077699</v>
+        <v>1.391843191205064</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7889122338324339</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.450080649229074</v>
+        <v>3.459476409871182</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.857173603686352</v>
+        <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.448796612375534</v>
+        <v>1.455060452803607</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7889122338324339</v>
+        <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.465369818463282</v>
+        <v>3.474765579105391</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.859643310148158</v>
+        <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.355452929113253</v>
+        <v>1.361716769541326</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7864425273706277</v>
+        <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.37153219390864</v>
+        <v>3.380927954550749</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.928013496472168</v>
+        <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.24736671606895</v>
+        <v>1.253630556497024</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7957182264068426</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.296359474815671</v>
+        <v>3.305755235457779</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.941801549319215</v>
+        <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.232288203562023</v>
+        <v>1.238552043990096</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7957182264068426</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.286796183447562</v>
+        <v>3.29619194408967</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.997321625211804</v>
+        <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.347111009897189</v>
+        <v>1.353374850325263</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7957182264068426</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.423827020139764</v>
+        <v>3.433222780781873</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.821847365419335</v>
+        <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.421867945805965</v>
+        <v>1.428131786234038</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7957182264068426</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.428394252131552</v>
+        <v>3.43779001277366</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.813922990834421</v>
+        <v>-3.798263389764238</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.400779724401138</v>
+        <v>1.407043564829211</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7957182264068426</v>
+        <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.404136280892759</v>
+        <v>3.413532041534868</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.807644788264572</v>
+        <v>-3.791985187194389</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.331829318830527</v>
+        <v>1.3380931592586</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8019964289766917</v>
+        <v>0.8176560300468725</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.336441515836118</v>
+        <v>3.345837276478227</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.747792169060849</v>
+        <v>-3.732132567990666</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.365942752944149</v>
+        <v>1.372206593372222</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8019964289766917</v>
+        <v>0.8176560300468725</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.346613902268251</v>
+        <v>3.356009662910359</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.661548706034472</v>
+        <v>-3.645889104964288</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.39538640872856</v>
+        <v>1.401650249156633</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8019964289766917</v>
+        <v>0.8176560300468725</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.341560172842111</v>
+        <v>3.35095593348422</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.706855525433451</v>
+        <v>-3.691195924363268</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.369039456413494</v>
+        <v>1.375303296841567</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7611862659674609</v>
+        <v>0.7768458670376417</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.308849850481098</v>
+        <v>3.318245611123206</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.735888630135753</v>
+        <v>-3.72022902906557</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.357978087565674</v>
+        <v>1.364241927993748</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7611862659674609</v>
+        <v>0.7768458670376417</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.309401723514199</v>
+        <v>3.318797484156308</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.643078148684894</v>
+        <v>-3.62741854761471</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.324374972037384</v>
+        <v>1.330638812465457</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8539967474183202</v>
+        <v>0.869656348488501</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.294360704276081</v>
+        <v>3.303756464918189</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.687467618014321</v>
+        <v>-3.671808016944138</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.308492660230214</v>
+        <v>1.314756500658287</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8096072780888925</v>
+        <v>0.8252668791590734</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.269600498603025</v>
+        <v>3.278996259245134</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.804009223119664</v>
+        <v>-3.788349622049481</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.256951726699799</v>
+        <v>1.263215567127873</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6930656729835498</v>
+        <v>0.7087252740537306</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.194751244051543</v>
+        <v>3.204147004693651</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.843933317702236</v>
+        <v>-3.828273716632053</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.246473384697438</v>
+        <v>1.252737225125511</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6930656729835498</v>
+        <v>0.7087252740537306</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.20024253988221</v>
+        <v>3.209638300524318</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.871713715603589</v>
+        <v>-3.856054114533406</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.246858427305436</v>
+        <v>1.253122267733509</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6652852750821967</v>
+        <v>0.6809448761523775</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.195071502909937</v>
+        <v>3.204467263552045</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.990094388333727</v>
+        <v>-3.974434787263544</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.037861878214034</v>
+        <v>1.044125718642107</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5980674229312205</v>
+        <v>0.6137270240014013</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.993096511620005</v>
+        <v>3.002492272262113</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.098708466777058</v>
+        <v>-4.083048865706875</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.114565907555907</v>
+        <v>1.12082974798398</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5980674229312205</v>
+        <v>0.6137270240014013</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.11324617233921</v>
+        <v>3.122641932981319</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.063299428528915</v>
+        <v>-4.047639827458732</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.143242548957487</v>
+        <v>1.14950638938556</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5980674229312205</v>
+        <v>0.6137270240014013</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.127759198441533</v>
+        <v>3.137154959083642</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.024915765970764</v>
+        <v>-4.009256164900581</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.156015455323116</v>
+        <v>1.16227929575119</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6364510854893717</v>
+        <v>0.6521106865595525</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.148208837318792</v>
+        <v>3.157604597960901</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.847799435935598</v>
+        <v>-3.832139834865415</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.223591016182485</v>
+        <v>1.229854856610558</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6364510854893717</v>
+        <v>0.6521106865595525</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.144937866164094</v>
+        <v>3.154333626806203</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.892891680769144</v>
+        <v>-3.877232079698961</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.206237510010979</v>
+        <v>1.212501350439053</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5745550423199819</v>
+        <v>0.5902146433901627</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.108483632024374</v>
+        <v>3.117879392666482</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.713516259530376</v>
+        <v>-3.697856658460193</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.271774653812901</v>
+        <v>1.278038494240974</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7313318004907006</v>
+        <v>0.7469914015608814</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.196336662233219</v>
+        <v>3.205732422875328</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.758530473050982</v>
+        <v>-3.742870871980799</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.234576423736248</v>
+        <v>1.240840264164321</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.700982905176096</v>
+        <v>0.7166425062462768</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.158934780376046</v>
+        <v>3.168330541018155</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.025534983323418</v>
+        <v>-4.009875382253234</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.13346618196622</v>
+        <v>1.139730022394293</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5066198671331474</v>
+        <v>0.5222794682033283</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.048008519889223</v>
+        <v>3.057404280531332</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.12673276476059</v>
+        <v>-4.111073163690407</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.092190991287852</v>
+        <v>1.098454831715925</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4382110535878282</v>
+        <v>0.4538706546580091</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.006167153658533</v>
+        <v>3.015562914300641</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.120221798146278</v>
+        <v>-4.104562197076095</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.092395339487894</v>
+        <v>1.098659179915967</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4382110535878282</v>
+        <v>0.4538706546580091</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.003767115212849</v>
+        <v>3.013162875854958</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.101183670438981</v>
+        <v>-4.085524069368797</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.096535309779058</v>
+        <v>1.102799150207131</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3800274422566337</v>
+        <v>0.3956870433268145</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.965381667622378</v>
+        <v>2.974777428264486</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.153699472713801</v>
+        <v>-4.138039871643618</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.19482339050332</v>
+        <v>1.201087230931393</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3800274422566337</v>
+        <v>0.3956870433268145</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.084676069256568</v>
+        <v>3.094071829898676</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.167566234047719</v>
+        <v>-4.151906632977536</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.190110014955886</v>
+        <v>1.19637385538396</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3421695255228108</v>
+        <v>0.3578291265929916</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.062794648202408</v>
+        <v>3.072190408844516</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.122762062507789</v>
+        <v>-4.107102461437606</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.214040213968784</v>
+        <v>1.220304054396858</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3421695255228108</v>
+        <v>0.3578291265929916</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.068803178599334</v>
+        <v>3.078198939241442</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.975019092272787</v>
+        <v>-3.959359491202604</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.171087623339985</v>
+        <v>1.177351463768058</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5099768827576939</v>
+        <v>0.5256364838278748</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.067437814217463</v>
+        <v>3.076833574859572</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.058840313547485</v>
+        <v>-4.043180712477302</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.140352756361586</v>
+        <v>1.14661659678966</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5099768827576939</v>
+        <v>0.5256364838278748</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.070231435748944</v>
+        <v>3.079627196391053</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.0526876074947</v>
+        <v>-4.037028006424517</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.143476187174358</v>
+        <v>1.149740027602432</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5161295888104782</v>
+        <v>0.531789189880659</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.074585407772273</v>
+        <v>3.083981168414382</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.716964352826587</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.069496905645202</v>
+        <v>-4.053837304575019</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.088809166254759</v>
+        <v>1.142096785082341</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4993202906599765</v>
+        <v>0.5149798917301573</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.016556527222573</v>
+        <v>3.072976066264191</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.783299906623408</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.00719890686908</v>
+        <v>-3.991539305798897</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.180063919562028</v>
+        <v>1.233351538389611</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5446145549344186</v>
+        <v>0.5602741560045994</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.110068639584059</v>
+        <v>3.166488178625677</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.585591908337535</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.805408709203922</v>
+        <v>-3.789749108133739</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.063072000342219</v>
+        <v>1.116359619169801</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.742632747103573</v>
+        <v>0.7582923481737538</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.031171556599679</v>
+        <v>3.087591095641296</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.65588214065971</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.856295421890117</v>
+        <v>-3.840635820819934</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.113007547589916</v>
+        <v>1.166295166417498</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6917460344173785</v>
+        <v>0.7074056354875593</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.070929761310138</v>
+        <v>3.127349300351755</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.670509876775754</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.76968467924031</v>
+        <v>-3.754025078170127</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.162279580765883</v>
+        <v>1.215567199593465</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7703717656225367</v>
+        <v>0.7860313666927176</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.132732936149276</v>
+        <v>3.189152475190894</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.669045857600425</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.829893977245594</v>
+        <v>-3.814234376175411</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.13673184238844</v>
+        <v>1.190019461216023</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7101624676172522</v>
+        <v>0.725822068687433</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.095143338170777</v>
+        <v>3.151562877212394</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.667537475640354</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.753471930813667</v>
+        <v>-3.737812329743484</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.16579227900114</v>
+        <v>1.219079897828722</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7101624676172522</v>
+        <v>0.725822068687433</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.093634956210706</v>
+        <v>3.150054495252323</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.66740034307579</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.709098799175099</v>
+        <v>-3.693439198104916</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.183404399092003</v>
+        <v>1.236692017919586</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7545355992558208</v>
+        <v>0.7701952003260016</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.120121702629283</v>
+        <v>3.1765412416709</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.661794137214381</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.731579150033983</v>
+        <v>-3.715919548963801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.16880605288704</v>
+        <v>1.222093671714622</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7545355992558208</v>
+        <v>0.7701952003260016</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.114515496767873</v>
+        <v>3.170935035809491</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.668175894242185</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.683923419472928</v>
+        <v>-3.668263818402745</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.194250102139266</v>
+        <v>1.247537720966849</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8021913298168765</v>
+        <v>0.8178509308870573</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.149490692132311</v>
+        <v>3.205910231173929</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.67306826761691</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.583405260974173</v>
+        <v>-3.567745659903991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.239349738913493</v>
+        <v>1.292637357741076</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.902709488315631</v>
+        <v>0.9183690893858119</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.214693960606289</v>
+        <v>3.271113499647907</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.659822940092782</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.567499931541821</v>
+        <v>-3.551840330471638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.232466543162306</v>
+        <v>1.285754161989889</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8235968276063921</v>
+        <v>0.8392564286765729</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.153981036656617</v>
+        <v>3.210400575698236</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.663920642703411</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.522661529933423</v>
+        <v>-3.50700192886324</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.254499606416294</v>
+        <v>1.307787225243877</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8281402605512616</v>
+        <v>0.8437998616214424</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.160804799034168</v>
+        <v>3.217224338075786</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.668081582334489</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.542159986175431</v>
+        <v>-3.526500385105248</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.250861163550569</v>
+        <v>1.304148782378152</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7800556192713572</v>
+        <v>0.7957152203415381</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.136114953897303</v>
+        <v>3.192534492938921</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.673961184862326</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.49795714908953</v>
+        <v>-3.482297548019348</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.274421900912766</v>
+        <v>1.327709519740349</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8242584563572577</v>
+        <v>0.8399180574274385</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.16851625867668</v>
+        <v>3.224935797718299</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.672371185331573</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.505516814926577</v>
+        <v>-3.489857213856395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.269808035047195</v>
+        <v>1.323095653874778</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.879061860367077</v>
+        <v>0.8947214614372578</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.19980830155182</v>
+        <v>3.256227840593438</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.723618950514613</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.347225397387305</v>
+        <v>-3.331565796317122</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.384372367245943</v>
+        <v>1.437659986073526</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.879061860367077</v>
+        <v>0.8947214614372578</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.25105606673486</v>
+        <v>3.307475605776477</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.722059655108866</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.139583393752829</v>
+        <v>-3.123923792682646</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.465869873293987</v>
+        <v>1.51915749212157</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.086703864001553</v>
+        <v>1.102363465071734</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.374081973509798</v>
+        <v>3.430501512551416</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.717007883347136</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.088551301030301</v>
+        <v>-3.072891699960118</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.481230938621268</v>
+        <v>1.534518557448851</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.137735956724081</v>
+        <v>1.153395557794262</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.399649457381585</v>
+        <v>3.456068996423203</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.734195287439841</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.023327119903095</v>
+        <v>-3.007667518832912</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.524508015164856</v>
+        <v>1.577795633992438</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.202960137851287</v>
+        <v>1.218619738921468</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.455971370150613</v>
+        <v>3.512390909192232</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.730156259739121</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.985900099831961</v>
+        <v>-2.970240498761779</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.535439795492589</v>
+        <v>1.588727414320172</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.208211675880468</v>
+        <v>1.223871276950649</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.455083265267403</v>
+        <v>3.511502804309021</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.731413052070362</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.00601175586667</v>
+        <v>-2.990352154796487</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.528651925409946</v>
+        <v>1.581939544237529</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.219239020877888</v>
+        <v>1.234898621948069</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.462956464597094</v>
+        <v>3.519376003638713</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.891970823091572</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.977598492766786</v>
+        <v>-2.961938891696603</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.700575001671111</v>
+        <v>1.753862620498693</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.160263458131459</v>
+        <v>1.17592305920164</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.588128897970448</v>
+        <v>3.644548437012066</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.01208373230939</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.902816231741773</v>
+        <v>-2.887156630671591</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.850600815298933</v>
+        <v>1.903888434126516</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.235045719156471</v>
+        <v>1.250705320226652</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.753111163803273</v>
+        <v>3.809530702844891</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.003791708323249</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.876732147477965</v>
+        <v>-2.861072546407783</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.852742425018315</v>
+        <v>1.906030043845898</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.235045719156471</v>
+        <v>1.250705320226652</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.744819139817132</v>
+        <v>3.80123867885875</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.001984903907028</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.788854234368845</v>
+        <v>-2.773194633298662</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.886086785845743</v>
+        <v>1.939374404673326</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.350971361579822</v>
+        <v>1.366630962650004</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.812567720854922</v>
+        <v>3.86898725989654</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.019539309633819</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.779961772975561</v>
+        <v>-2.764302171905379</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.907198176129848</v>
+        <v>1.96048579495743</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.350971361579822</v>
+        <v>1.366630962650004</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.830122126581713</v>
+        <v>3.886541665623331</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.011394357038403</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.948437889945439</v>
+        <v>-2.932778288875256</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.83166277674648</v>
+        <v>1.884950395574063</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.323023525863242</v>
+        <v>1.338683126933423</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.805208472556349</v>
+        <v>3.861628011597967</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.992664054226265</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.502181697315999</v>
+        <v>-2.486522096245817</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.991434950986118</v>
+        <v>2.044722569813701</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.228304856193609</v>
+        <v>1.24396445726379</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.729646967942431</v>
+        <v>3.786066506984049</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.98332807672317</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.479460593632847</v>
+        <v>-2.463800992562664</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.991187414956284</v>
+        <v>2.044475033783867</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.228304856193609</v>
+        <v>1.24396445726379</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.720310990439335</v>
+        <v>3.776730529480953</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.142234202574339</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.608662406926889</v>
+        <v>-2.593002805856707</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.098412815489835</v>
+        <v>2.151700434317418</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.099103042899567</v>
+        <v>1.114762643969748</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.801696028314079</v>
+        <v>3.858115567355697</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.179312025067985</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.634536805400915</v>
+        <v>-2.618877204330732</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.125140878593872</v>
+        <v>2.178428497421455</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.144014651611308</v>
+        <v>1.159674252681489</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.86572081603477</v>
+        <v>3.922140355076388</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.175987381057531</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.627482115185741</v>
+        <v>-2.611822514115559</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.124638110669486</v>
+        <v>2.177925729497069</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.151069341826482</v>
+        <v>1.166728942896663</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.86662898615342</v>
+        <v>3.923048525195038</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.185993534702272</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.600530890859253</v>
+        <v>-2.584871289789071</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.145424754044823</v>
+        <v>2.198712372872406</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.165949687854201</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.885563347414793</v>
+        <v>3.941982886456411</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.370096666847232</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.73648389891557</v>
+        <v>-2.720824297845387</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.275146682967256</v>
+        <v>2.328434301794839</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.165949687854201</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.069666479559753</v>
+        <v>4.126086018601371</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.362213361750225</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.758892016720442</v>
+        <v>-2.743232415650259</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.258300130748301</v>
+        <v>2.311587749575883</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.165949687854201</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.061783174462746</v>
+        <v>4.118202713504364</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.364267361299862</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.787116252298042</v>
+        <v>-2.771456651227859</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.249064436066898</v>
+        <v>2.302352054894481</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.183926440305509</v>
+        <v>1.19958604137569</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.074623225483168</v>
+        <v>4.131042764524786</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.42052107902171</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.796557178186572</v>
+        <v>-2.780897577116389</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.301541783433334</v>
+        <v>2.354829402260916</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.306353557848901</v>
+        <v>1.322013158919082</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.204333213731051</v>
+        <v>4.260752752772668</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.42341217356701</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.848830785522213</v>
+        <v>-2.833171184452031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.283523435044378</v>
+        <v>2.33681105387196</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.25407995051326</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.175860143874966</v>
+        <v>4.232279682916585</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.421523986460786</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.925160763123119</v>
+        <v>-2.909501162052937</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.251103256897791</v>
+        <v>2.304390875725373</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.25407995051326</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.173971956768741</v>
+        <v>4.23039149581036</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.416344216063648</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.127414483447473</v>
+        <v>-3.11175488237729</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.165021998370912</v>
+        <v>2.218309617198494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.051826230188906</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.047439954176991</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.4147782262738</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.288982908974728</v>
+        <v>-3.273323307904545</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.098828638370162</v>
+        <v>2.152116257197744</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9250433063910267</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.969804210108417</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.427851633139719</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.421284201072281</v>
+        <v>-3.405624600002098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.058981528397059</v>
+        <v>2.112269147224642</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9250433063910267</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.982877616974335</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.419856829922659</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.607152511911511</v>
+        <v>-3.591492910841328</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.976639400844307</v>
+        <v>2.02992701967189</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.766477713071079</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.879743457765306</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.418380871049661</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.635053299020984</v>
+        <v>-3.619393697950801</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.96400312712752</v>
+        <v>2.017290745955103</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7318807889281442</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.857509344406548</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.41514531502686</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.757579401723878</v>
+        <v>-3.741919800653695</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.911757130023561</v>
+        <v>1.965044748851144</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6093546862252504</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.78075812676201</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.481851274617363</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.988093897909466</v>
+        <v>-3.972434296839284</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.886257291139829</v>
+        <v>1.939544909967412</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3788401900396616</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.709155388641161</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.62216299361921</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.24481471590429</v>
+        <v>-4.229155114834107</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.923880682943747</v>
+        <v>1.97716830177133</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2704256158958468</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.784418363156719</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.69114326276485</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.398801133680431</v>
+        <v>-4.383141532610248</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.93126638497893</v>
+        <v>1.984554003806513</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2704256158958468</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.853398632302358</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.677194464884971</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.348279229852765</v>
+        <v>-4.332619628782582</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.937526348630118</v>
+        <v>1.990813967457701</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2704256158958468</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.839449834422479</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.689064953940385</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.600754383860489</v>
+        <v>-4.585094782790306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.848406776082442</v>
+        <v>1.901694394910025</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2704256158958468</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.851320323477893</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.690275488459329</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.893650140339902</v>
+        <v>-4.877990539269718</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.732459008009621</v>
+        <v>1.785746626837204</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2704256158958468</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.852530857996837</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.69439723068665</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.08031426847471</v>
+        <v>-5.064654667404526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.661915098983019</v>
+        <v>1.715202717810602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2436866450712869</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.840609217729423</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.68947508342284</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.226334955388672</v>
+        <v>-5.210675354318488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.598584676953624</v>
+        <v>1.651872295781207</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2346035532774299</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.830237215389298</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.851679140121884</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.318048964498256</v>
+        <v>-5.302389363428073</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.724103130008834</v>
+        <v>1.777390748836417</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2346035532774299</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.992441272088342</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.846525778085698</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.40276690671921</v>
+        <v>-5.334041022488043</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.685062591084267</v>
+        <v>1.759576723176243</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1494875243493836</v>
+        <v>0.2450946971031708</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.936218292695329</v>
+        <v>4.04060637474711</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.856755195654189</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.484701724988093</v>
+        <v>-5.415975840756926</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.662518081345205</v>
+        <v>1.737032213437181</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1395527787623034</v>
+        <v>0.2351599515160906</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940486862911571</v>
+        <v>4.044874944963353</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.865680834110091</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.5866778472365</v>
+        <v>-5.517951963005333</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.630653270901744</v>
+        <v>1.70516740299372</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.0375766565138958</v>
+        <v>0.133183829267683</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888226828018429</v>
+        <v>3.992614910070211</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.857833721354267</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.476671563759279</v>
+        <v>-5.407945679528112</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.666808671536808</v>
+        <v>1.741322803628784</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.06078122843117101</v>
+        <v>0.1563884011849582</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.89430245841297</v>
+        <v>3.998690540464752</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.862083732076241</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.333611988018353</v>
+        <v>-5.264886103787186</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.728282512555153</v>
+        <v>1.802796644647129</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.06879465502115029</v>
+        <v>0.1644018277749375</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903360525088932</v>
+        <v>4.007748607140713</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.869344614958777</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.032165262546515</v>
+        <v>-4.963439378315348</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.856122085626424</v>
+        <v>1.9306362177184</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3702413804929875</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.09148944325457</v>
+        <v>4.195877525306352</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.870315792711488</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.056755506781699</v>
+        <v>-4.988029622550532</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.847257165685061</v>
+        <v>1.921771297777037</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3702413804929875</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.09246062100728</v>
+        <v>4.196848703059063</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.871158697091243</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.005717130775179</v>
+        <v>-4.936991246544012</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.868515420467424</v>
+        <v>1.9430295525594</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3702413804929875</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093303525387036</v>
+        <v>4.197691607438817</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.890196795965389</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.964577835908548</v>
+        <v>-4.895851951677381</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.904009237288222</v>
+        <v>1.978523369380198</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4113806753596184</v>
+        <v>0.5069878481134056</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.13702520118116</v>
+        <v>4.241413283232942</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.706380792089323</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.867942923889908</v>
+        <v>-4.799217039658741</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.758847198219613</v>
+        <v>1.833361330311589</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5080155873782584</v>
+        <v>0.6036227601320455</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011190144516279</v>
+        <v>4.11557822656806</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.709882836163287</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.99852365842075</v>
+        <v>-4.929797774189583</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.71011694848124</v>
+        <v>1.784631080573216</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3774348528474158</v>
+        <v>0.473042025601203</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936343747871737</v>
+        <v>4.040731829923518</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.69430965523937</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.834027324229789</v>
+        <v>-4.765301439998622</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.760342301233707</v>
+        <v>1.834856433325683</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3774348528474158</v>
+        <v>0.473042025601203</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.920770566947819</v>
+        <v>4.025158648999601</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.6934973656758</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.861397256914221</v>
+        <v>-4.792671372683054</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.748582038596364</v>
+        <v>1.82309617068834</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3774348528474158</v>
+        <v>0.473042025601203</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.919958277384249</v>
+        <v>4.024346359436031</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.703366144800872</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.87178245180411</v>
+        <v>-4.803056567572943</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.754296739765481</v>
+        <v>1.828810871857456</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3670496579575265</v>
+        <v>0.4626568307113137</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.923595939575388</v>
+        <v>4.027984021627169</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.774203150577297</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.890370610526335</v>
+        <v>-4.821644726295168</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.817698482053016</v>
+        <v>1.892212614144992</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3484614992353012</v>
+        <v>0.4440686719890883</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.983280050118478</v>
+        <v>4.087668132170259</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.771072161395596</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.890669157222371</v>
+        <v>-4.821943272991204</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.8144480741929</v>
+        <v>1.888962206284876</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3484614992353012</v>
+        <v>0.4440686719890883</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.980149060936776</v>
+        <v>4.084537142988558</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.775603056334987</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.789846023531943</v>
+        <v>-4.721120139300776</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.859308222608463</v>
+        <v>1.933822354700438</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.360925714719655</v>
+        <v>0.4565328874734422</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.99215848516678</v>
+        <v>4.096546567218561</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.77573230981353</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.599064662779536</v>
+        <v>-4.530338778548369</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.935750020387969</v>
+        <v>2.010264152479944</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5517070754720623</v>
+        <v>0.6473142482258496</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.106756555096768</v>
+        <v>4.211144637148549</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.755569155551127</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.580547808737716</v>
+        <v>-4.511821924506549</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.922993607742293</v>
+        <v>1.997507739834269</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5646372048972705</v>
+        <v>0.6602443776510578</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.094351478489489</v>
+        <v>4.198739560541271</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.790536092163185</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.555354624236398</v>
+        <v>-4.486628740005231</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.968037818154879</v>
+        <v>2.042551950246855</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5898303893985889</v>
+        <v>0.6854375621523762</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.144434325802339</v>
+        <v>4.24882240785412</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.784222660064623</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.543300497323435</v>
+        <v>-4.474574613092268</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.966546036821502</v>
+        <v>2.041060168913477</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6018845163115517</v>
+        <v>0.697491689065339</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.145353369851555</v>
+        <v>4.249741451903335</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.786103290248759</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.549923744013793</v>
+        <v>-4.481197859782626</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.965777368329494</v>
+        <v>2.04029150042147</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5952612696211934</v>
+        <v>0.6908684423749807</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.143260052021476</v>
+        <v>4.247648134073256</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.798954316126641</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.4470431544852</v>
+        <v>-4.378317270254033</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.019780630018814</v>
+        <v>2.094294762110789</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6981418591497863</v>
+        <v>0.7937490319035736</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.217839431616514</v>
+        <v>4.322227513668294</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.819156986300236</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.470485193665287</v>
+        <v>-4.40175930943412</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.030606484520374</v>
+        <v>2.105120616612349</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6981418591497863</v>
+        <v>0.7937490319035736</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.238042101790108</v>
+        <v>4.342430183841889</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.819156986300236</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.488557701956899</v>
+        <v>-4.419831817725732</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.023377481203729</v>
+        <v>2.097891613295705</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6981418591497863</v>
+        <v>0.7937490319035736</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.238042101790108</v>
+        <v>4.342430183841889</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.779408899893702</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.719731495833531</v>
+        <v>-4.651005611602364</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.891159877246543</v>
+        <v>1.965674009338518</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6981418591497863</v>
+        <v>0.7937490319035736</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.198294015383574</v>
+        <v>4.302682097435356</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.786431518890642</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.688445475293076</v>
+        <v>-4.619719591061909</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910696904459665</v>
+        <v>1.98521103655164</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7294278796902417</v>
+        <v>0.825035052444029</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.224088246704787</v>
+        <v>4.328476328756569</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.885602518463547</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.535420083179791</v>
+        <v>-4.466694198948624</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.071078060877883</v>
+        <v>2.145592192969858</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8824532718035258</v>
+        <v>0.9780604445573131</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.415074481545663</v>
+        <v>4.519462563597443</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.073068743371839</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.563727397053062</v>
+        <v>-4.495001512821895</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.247221360236867</v>
+        <v>2.321735492328842</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8824532718035258</v>
+        <v>0.9780604445573131</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.602540706453954</v>
+        <v>4.706928788505736</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.042471694725921</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.730320622166584</v>
+        <v>-4.661594737935417</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14998702154554</v>
+        <v>2.224501153637516</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7158600466900034</v>
+        <v>0.8114672194437906</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.471987722739923</v>
+        <v>4.576375804791704</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.046148097387639</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.557256242784284</v>
+        <v>-4.488530358553117</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.222889175960178</v>
+        <v>2.297403308052154</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7158600466900034</v>
+        <v>0.8114672194437906</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.475664125401641</v>
+        <v>4.580052207453422</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.043766152511134</v>
+        <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.528010262328587</v>
+        <v>-4.45928437809742</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.232205623265952</v>
+        <v>2.306719755357928</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7158600466900034</v>
+        <v>0.8114672194437906</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.473282180525136</v>
+        <v>4.577670262576918</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.041059391668769</v>
+        <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.634935810206438</v>
+        <v>-4.566209925975271</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.186728643272446</v>
+        <v>2.261242775364422</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.608934498812152</v>
+        <v>0.7045416715659393</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.40642009095606</v>
+        <v>4.510808173007842</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983739</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.042488193812003</v>
+        <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.779954368713687</v>
+        <v>-4.71122848448252</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.130150022012781</v>
+        <v>2.204664154104757</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4639159403049035</v>
+        <v>0.5595231130586907</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.320837757994946</v>
+        <v>4.425225840046727</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.142419433069756</v>
+        <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.898296134498405</v>
+        <v>-4.829570250267238</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.182744554956647</v>
+        <v>2.257258687048623</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4746019788677935</v>
+        <v>0.5702091516215808</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.427180620390433</v>
+        <v>4.531568702442214</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.830294423823139</v>
+        <v>3.870626677793667</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.220705456674215</v>
+        <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.907097221562331</v>
+        <v>-4.881361083893951</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.257510143735535</v>
+        <v>2.234328050723876</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4165437287334747</v>
+        <v>0.5702091516215808</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.470631693914299</v>
+        <v>4.529354399568152</v>
       </c>
     </row>
   </sheetData>
